--- a/src/Head.xlsx
+++ b/src/Head.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12450" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12450" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="&lt;head&gt;Index" sheetId="13" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="352">
   <si>
     <t>Título</t>
   </si>
@@ -242,13 +242,13 @@
     <t>&lt;meta name="twitter:card" content="summary" /&gt;</t>
   </si>
   <si>
-    <t>El Módulo datetime - Funciones para Manejo de la Hora y la Fecha en Python  - Ing. Eduardo Herrera Forero.</t>
-  </si>
-  <si>
-    <t>https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html</t>
-  </si>
-  <si>
-    <t>Aprende a manejar fechas y horas en Python con el módulo datetime. Descubre cómo crear, formatear y manipular datos temporales usando sus principales funciones y clases</t>
+    <t>El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  - Ing. Eduardo Herrera Forero.</t>
+  </si>
+  <si>
+    <t>https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html</t>
+  </si>
+  <si>
+    <t>Aprende a utilizar el módulo calendar de Python para manipular fechas, crear calendarios y gestionar eventos. Descubre funciones prácticas para el manejo eficiente del tiempo en tus aplicaciones</t>
   </si>
   <si>
     <t>Comillas</t>
@@ -346,7 +346,7 @@
     <t>Parrafo 1</t>
   </si>
   <si>
-    <t>El módulo &lt;code&gt;datetime&lt;/code&gt; de Python es una herramienta poderosa y versátil que permite a los desarrolladores trabajar con fechas y horas de manera eficiente. Este documento explora las principales funcionalidades del módulo, incluyendo la creación de objetos de fecha y hora, la manipulación de estos objetos y la realización de operaciones comunes como la comparación y el formateo. A través de ejemplos prácticos, se ilustrará cómo utilizar este módulo para resolver problemas cotidianos relacionados con el tiempo.</t>
+    <t>El módulo calendar en Python es una herramienta poderosa que permite trabajar con calendarios de manera sencilla y eficiente. Este módulo proporciona funciones para manipular fechas, generar calendarios en diferentes formatos y realizar cálculos relacionados con el tiempo. En este documento, exploraremos las principales características y funciones del módulo calendar, así como ejemplos prácticos de su uso.</t>
   </si>
   <si>
     <t>Parrafo 2</t>
@@ -361,7 +361,7 @@
     <t>&lt;img</t>
   </si>
   <si>
-    <t>https://images2.imgbox.com/38/c8/WnB7uL66_o.png</t>
+    <t>https://images2.imgbox.com/37/f3/xVxmYAZb_o.png</t>
   </si>
   <si>
     <t>class="img-fluid"</t>
@@ -370,7 +370,7 @@
     <t>width="50%"</t>
   </si>
   <si>
-    <t>Dominando el Módulo datetime de Python</t>
+    <t>Explorando el Módulo de Calendario de Python</t>
   </si>
   <si>
     <t>/&gt;</t>
@@ -385,43 +385,79 @@
     <t>Area de trabajo 1</t>
   </si>
   <si>
+    <t>Introducción</t>
+  </si>
+  <si>
     <t>areaDeTrabajo1</t>
   </si>
   <si>
+    <t>introduccion</t>
+  </si>
+  <si>
     <t>li</t>
   </si>
   <si>
     <t>Area de trabajo 2</t>
   </si>
   <si>
+    <t>Funciones para Obtener el Calendario</t>
+  </si>
+  <si>
     <t>areaDeTrabajo2</t>
   </si>
   <si>
+    <t>funcionesPraObtenerElCalendario</t>
+  </si>
+  <si>
     <t>Area de trabajo 3</t>
   </si>
   <si>
+    <t>Funciones de Días de la Semana</t>
+  </si>
+  <si>
     <t>areaDeTrabajo3</t>
   </si>
   <si>
+    <t>funcionesDeDIasDelaSemana</t>
+  </si>
+  <si>
     <t>class="mt-5 pt-5 "&gt;</t>
   </si>
   <si>
     <t>Area de trabajo 4</t>
   </si>
   <si>
+    <t>Funciones Para Año Bisiesto</t>
+  </si>
+  <si>
     <t>areaDeTrabajo4</t>
   </si>
   <si>
+    <t>funcionesParaAñoBisiesto</t>
+  </si>
+  <si>
     <t>Area de trabajo 5</t>
   </si>
   <si>
+    <t>Funciones para Primer Día de la Semana</t>
+  </si>
+  <si>
     <t>areaDeTrabajo5</t>
   </si>
   <si>
+    <t>funcionesParaPrimerDiaDeLaSemana</t>
+  </si>
+  <si>
     <t>Area de trabajo 6</t>
   </si>
   <si>
+    <t>Funciones de Calendario En Formato De Tabla</t>
+  </si>
+  <si>
     <t>areaDeTrabajo6</t>
+  </si>
+  <si>
+    <t>funcionesDeCalendarioEnFormatoDeTabla</t>
   </si>
   <si>
     <t>Area de trabajo 7</t>
@@ -649,10 +685,10 @@
     <t>&lt;ul&gt;</t>
   </si>
   <si>
-    <t>Usar os.path: Siempre que sea posible, utilice las funciones de os.path para garantizar la compatibilidad multiplataforma.</t>
-  </si>
-  <si>
-    <t>Capturar excepciones: Algunas operaciones, como cambiar de directorio o eliminar archivos, pueden generar errores si la ruta no existe o no se tienen permisos.</t>
+    <t>calendar.prmonth(year, month): Imprime el calendario de un mes específico en formato tabular.</t>
+  </si>
+  <si>
+    <t>calendar.pryear(year): Imprime el calendario completo de un año en formato tabular.</t>
   </si>
   <si>
     <t>BaseException</t>
@@ -4163,7 +4199,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="0.158333333333333" style="88" customWidth="1"/>
-    <col min="2" max="2" width="11" style="88"/>
+    <col min="2" max="2" width="32.6" style="88" customWidth="1"/>
     <col min="3" max="3" width="139.991666666667" style="88" customWidth="1"/>
     <col min="4" max="4" width="11" style="88"/>
     <col min="5" max="5" width="35" style="88" customWidth="1"/>
@@ -4273,7 +4309,7 @@
       </c>
       <c r="B9" s="95" t="str">
         <f>CONCATENATE(E9,$C$3,F9)</f>
-        <v>&lt;meta name="description" content="Aprende a manejar fechas y horas en Python con el módulo datetime. Descubre cómo crear, formatear y manipular datos temporales usando sus principales funciones y clases" /&gt;</v>
+        <v>&lt;meta name="description" content="Aprende a utilizar el módulo calendar de Python para manipular fechas, crear calendarios y gestionar eventos. Descubre funciones prácticas para el manejo eficiente del tiempo en tus aplicaciones" /&gt;</v>
       </c>
       <c r="C9" s="95"/>
       <c r="D9" s="95" t="s">
@@ -4293,7 +4329,7 @@
       </c>
       <c r="B10" s="95" t="str">
         <f>CONCATENATE(E10,$C$1,F10)</f>
-        <v>&lt;meta name="tittle" content="El Módulo datetime - Funciones para Manejo de la Hora y la Fecha en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
+        <v>&lt;meta name="tittle" content="El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="95" t="s">
@@ -4355,7 +4391,7 @@
       </c>
       <c r="B14" s="95" t="str">
         <f>CONCATENATE(E14,$C$2,$F$9)</f>
-        <v>&lt;link rel="canonical" href="https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html" /&gt;</v>
+        <v>&lt;link rel="canonical" href="https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html" /&gt;</v>
       </c>
       <c r="C14" s="95"/>
       <c r="D14" s="95" t="s">
@@ -4424,7 +4460,7 @@
       </c>
       <c r="B19" s="95" t="str">
         <f>CONCATENATE(E19,$C$1,F9)</f>
-        <v>&lt;meta property="og:title" content="El Módulo datetime - Funciones para Manejo de la Hora y la Fecha en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
+        <v>&lt;meta property="og:title" content="El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
       </c>
       <c r="C19" s="95"/>
       <c r="D19" s="95" t="s">
@@ -4441,7 +4477,7 @@
       </c>
       <c r="B20" s="95" t="str">
         <f>CONCATENATE(E20,$C$3,$F$9)</f>
-        <v>&lt;meta property="og:description" content="Aprende a manejar fechas y horas en Python con el módulo datetime. Descubre cómo crear, formatear y manipular datos temporales usando sus principales funciones y clases" /&gt;</v>
+        <v>&lt;meta property="og:description" content="Aprende a utilizar el módulo calendar de Python para manipular fechas, crear calendarios y gestionar eventos. Descubre funciones prácticas para el manejo eficiente del tiempo en tus aplicaciones" /&gt;</v>
       </c>
       <c r="C20" s="95"/>
       <c r="D20" s="95" t="s">
@@ -4486,7 +4522,7 @@
       </c>
       <c r="B23" s="95" t="str">
         <f>CONCATENATE(E23,$C$2,$F$9)</f>
-        <v>&lt;meta property="og:url" content="https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html" /&gt;</v>
+        <v>&lt;meta property="og:url" content="https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html" /&gt;</v>
       </c>
       <c r="C23" s="95"/>
       <c r="D23" s="95" t="s">
@@ -4583,7 +4619,7 @@
       </c>
       <c r="B30" s="95" t="str">
         <f>CONCATENATE(E30,$C$1,$F$9)</f>
-        <v>&lt;meta name="twitter:url" content="El Módulo datetime - Funciones para Manejo de la Hora y la Fecha en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
+        <v>&lt;meta name="twitter:url" content="El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  - Ing. Eduardo Herrera Forero." /&gt;</v>
       </c>
       <c r="C30" s="95"/>
       <c r="D30" s="95" t="s">
@@ -4600,7 +4636,7 @@
       </c>
       <c r="B31" s="95" t="str">
         <f>CONCATENATE(E31,$C$2,$F$9)</f>
-        <v>&lt;meta name="twitter:title" content="https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html" /&gt;</v>
+        <v>&lt;meta name="twitter:title" content="https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html" /&gt;</v>
       </c>
       <c r="C31" s="95"/>
       <c r="D31" s="95" t="s">
@@ -4617,7 +4653,7 @@
       </c>
       <c r="B32" s="95" t="str">
         <f>CONCATENATE(E32,$C$3,$F$9)</f>
-        <v>&lt;meta name="twitter:description" content="Aprende a manejar fechas y horas en Python con el módulo datetime. Descubre cómo crear, formatear y manipular datos temporales usando sus principales funciones y clases" /&gt;</v>
+        <v>&lt;meta name="twitter:description" content="Aprende a utilizar el módulo calendar de Python para manipular fechas, crear calendarios y gestionar eventos. Descubre funciones prácticas para el manejo eficiente del tiempo en tus aplicaciones" /&gt;</v>
       </c>
       <c r="C32" s="95"/>
       <c r="D32" s="95" t="s">
@@ -4850,7 +4886,7 @@
       </c>
       <c r="B49" s="95" t="str">
         <f>C1</f>
-        <v>El Módulo datetime - Funciones para Manejo de la Hora y la Fecha en Python  - Ing. Eduardo Herrera Forero.</v>
+        <v>El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  - Ing. Eduardo Herrera Forero.</v>
       </c>
       <c r="C49" s="95"/>
       <c r="D49" s="95" t="s">
@@ -4939,7 +4975,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html" tooltip="https://eduardoherreraf.github.io/cursoPython3@0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html" tooltip="https://eduardoherreraf.github.io/cursoPython3@0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4955,7 +4991,7 @@
   <cols>
     <col min="1" max="1" width="19.375" style="16" customWidth="1"/>
     <col min="2" max="2" width="0.158333333333333" style="16" customWidth="1"/>
-    <col min="3" max="3" width="63.875" style="54" customWidth="1"/>
+    <col min="3" max="3" width="86" style="54" customWidth="1"/>
     <col min="4" max="4" width="0.158333333333333" style="54" customWidth="1"/>
     <col min="5" max="5" width="104.5" style="55" customWidth="1"/>
     <col min="6" max="9" width="0.158333333333333" style="16" customWidth="1"/>
@@ -5003,7 +5039,7 @@
       <c r="D5" s="16"/>
       <c r="E5" s="55" t="str">
         <f>CONCATENATE("&lt;!--  ",$C$8,"--&gt;")</f>
-        <v>&lt;!--  El Módulo datetime --&gt;</v>
+        <v>&lt;!--  El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  --&gt;</v>
       </c>
     </row>
     <row r="6" spans="3:5">
@@ -5020,7 +5056,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8" s="16" t="s">
         <v>77</v>
       </c>
@@ -5029,14 +5065,14 @@
       </c>
       <c r="C8" s="59" t="str">
         <f>LEFT('&lt;head&gt;'!C1,FIND("-",'&lt;head&gt;'!C1)-1)</f>
-        <v>El Módulo datetime </v>
+        <v>El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  </v>
       </c>
       <c r="D8" s="98" t="s">
         <v>78</v>
       </c>
       <c r="E8" s="55" t="str">
         <f>CONCATENATE("&lt;header&gt;&lt;h1&gt;",C8,"&lt;/h1&gt;&lt;/header&gt;")</f>
-        <v>&lt;header&gt;&lt;h1&gt;El Módulo datetime &lt;/h1&gt;&lt;/header&gt;</v>
+        <v>&lt;header&gt;&lt;h1&gt;El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  &lt;/h1&gt;&lt;/header&gt;</v>
       </c>
     </row>
     <row r="9" spans="3:6">
@@ -5061,7 +5097,7 @@
       </c>
       <c r="E10" s="62" t="str">
         <f>IF(C10&lt;&gt;"",CONCATENATE("&lt;p&gt;",C10,"&lt;/p&gt;"),"")</f>
-        <v>&lt;p&gt;El módulo &lt;code&gt;datetime&lt;/code&gt; de Python es una herramienta poderosa y versátil que permite a los desarrolladores trabajar con fechas y horas de manera eficiente. Este documento explora las principales funcionalidades del módulo, incluyendo la creación de objetos de fecha y hora, la manipulación de estos objetos y la realización de operaciones comunes como la comparación y el formateo. A través de ejemplos prácticos, se ilustrará cómo utilizar este módulo para resolver problemas cotidianos relacionados con el tiempo.&lt;/p&gt;</v>
+        <v>&lt;p&gt;El módulo calendar en Python es una herramienta poderosa que permite trabajar con calendarios de manera sencilla y eficiente. Este módulo proporciona funciones para manipular fechas, generar calendarios en diferentes formatos y realizar cálculos relacionados con el tiempo. En este documento, exploraremos las principales características y funciones del módulo calendar, así como ejemplos prácticos de su uso.&lt;/p&gt;</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>2</v>
@@ -5112,7 +5148,7 @@
       <c r="D15" s="61"/>
       <c r="E15" s="64" t="str">
         <f>CONCATENATE("src=",Comillas,C15,Comillas)</f>
-        <v>src="https://images2.imgbox.com/38/c8/WnB7uL66_o.png"</v>
+        <v>src="https://images2.imgbox.com/37/f3/xVxmYAZb_o.png"</v>
       </c>
     </row>
     <row r="16" spans="3:5">
@@ -5134,7 +5170,7 @@
       <c r="D18" s="61"/>
       <c r="E18" s="55" t="str">
         <f>CONCATENATE("alt=",Comillas,C8,Comillas)</f>
-        <v>alt="El Módulo datetime "</v>
+        <v>alt="El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  "</v>
       </c>
     </row>
     <row r="19" spans="3:5">
@@ -5144,7 +5180,7 @@
       <c r="D19" s="61"/>
       <c r="E19" s="64" t="str">
         <f>CONCATENATE("title=",Comillas,C19,Comillas)</f>
-        <v>title="Dominando el Módulo datetime de Python"</v>
+        <v>title="Explorando el Módulo de Calendario de Python"</v>
       </c>
     </row>
     <row r="20" spans="3:5">
@@ -5159,7 +5195,7 @@
       <c r="D21" s="61"/>
       <c r="E21" s="55" t="str">
         <f>CONCATENATE("&lt;figcaption&gt;",C8,"&lt;/figcaption&gt;")</f>
-        <v>&lt;figcaption&gt;El Módulo datetime &lt;/figcaption&gt;</v>
+        <v>&lt;figcaption&gt;El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  &lt;/figcaption&gt;</v>
       </c>
     </row>
     <row r="22" spans="3:5">
@@ -5183,7 +5219,7 @@
       <c r="D24" s="67"/>
       <c r="E24" s="68" t="str">
         <f>IF(C25&lt;&gt;"",CONCATENATE("&lt;!-- ",C25," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Introducción --&gt;</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5193,25 +5229,29 @@
       <c r="B25" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="70" t="s">
+        <v>93</v>
+      </c>
       <c r="D25" s="61"/>
       <c r="E25" s="71" t="str">
         <f>IF(C25&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="69" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="61"/>
+      <c r="C26" s="61" t="s">
+        <v>95</v>
+      </c>
       <c r="D26" s="61"/>
       <c r="E26" s="72" t="str">
         <f>IF(C25&lt;&gt;"",CONCATENATE("id=",Comillas,C26,Comillas),"")</f>
-        <v/>
+        <v>id="introduccion"</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5223,7 +5263,7 @@
       <c r="D27" s="16"/>
       <c r="E27" s="72" t="str">
         <f>IF(C25&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5235,7 +5275,7 @@
       <c r="D28" s="16"/>
       <c r="E28" s="72" t="str">
         <f>IF(C25&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C25,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Introducción&lt;/h2&gt;</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5247,7 +5287,7 @@
       <c r="D29" s="16"/>
       <c r="E29" s="71" t="str">
         <f>IF(C25&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
     </row>
     <row r="30" ht="15.75" spans="1:7">
@@ -5259,10 +5299,10 @@
       <c r="D30" s="75"/>
       <c r="E30" s="76" t="str">
         <f>IF(C25&lt;&gt;"",CONCATENATE("&lt;!-- ",C25," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Introducción Fin --&gt;</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="15.75" spans="1:7">
@@ -5285,21 +5325,23 @@
       <c r="D32" s="67"/>
       <c r="E32" s="68" t="str">
         <f>IF(C33&lt;&gt;"",CONCATENATE("&lt;!-- ",C33," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones para Obtener el Calendario --&gt;</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="61"/>
+      <c r="C33" s="61" t="s">
+        <v>98</v>
+      </c>
       <c r="D33" s="61"/>
       <c r="E33" s="71" t="str">
         <f>IF(C33&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>2</v>
@@ -5307,16 +5349,18 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="69" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="61"/>
+      <c r="C34" s="61" t="s">
+        <v>100</v>
+      </c>
       <c r="D34" s="61"/>
       <c r="E34" s="72" t="str">
         <f>IF(C33&lt;&gt;"",CONCATENATE("id=",Comillas,C34,Comillas),"")</f>
-        <v/>
+        <v>id="funcionesPraObtenerElCalendario"</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>2</v>
@@ -5331,7 +5375,7 @@
       <c r="D35" s="16"/>
       <c r="E35" s="72" t="str">
         <f>IF(C33&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>2</v>
@@ -5346,7 +5390,7 @@
       <c r="D36" s="16"/>
       <c r="E36" s="72" t="str">
         <f>IF(C33&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C33,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Funciones para Obtener el Calendario&lt;/h2&gt;</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>2</v>
@@ -5361,7 +5405,7 @@
       <c r="D37" s="16"/>
       <c r="E37" s="71" t="str">
         <f>IF(C33&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>2</v>
@@ -5376,7 +5420,7 @@
       <c r="D38" s="75"/>
       <c r="E38" s="76" t="str">
         <f>IF(C33&lt;&gt;"",CONCATENATE("&lt;!-- ",C33," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones para Obtener el Calendario Fin --&gt;</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>2</v>
@@ -5402,21 +5446,23 @@
       <c r="D40" s="67"/>
       <c r="E40" s="68" t="str">
         <f>IF(C41&lt;&gt;"",CONCATENATE("&lt;!-- ",C41," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones de Días de la Semana --&gt;</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="69" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="61"/>
+      <c r="C41" s="61" t="s">
+        <v>102</v>
+      </c>
       <c r="D41" s="61"/>
       <c r="E41" s="71" t="str">
         <f>IF(C41&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>2</v>
@@ -5424,19 +5470,21 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="69" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="61"/>
+      <c r="C42" s="61" t="s">
+        <v>104</v>
+      </c>
       <c r="D42" s="61"/>
       <c r="E42" s="72" t="str">
         <f>IF(C41&lt;&gt;"",CONCATENATE("id=",Comillas,C42,Comillas),"")</f>
-        <v/>
+        <v>id="funcionesDeDIasDelaSemana"</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>2</v>
@@ -5451,7 +5499,7 @@
       <c r="D43" s="16"/>
       <c r="E43" s="72" t="str">
         <f>IF(C41&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>2</v>
@@ -5466,7 +5514,7 @@
       <c r="D44" s="16"/>
       <c r="E44" s="72" t="str">
         <f>IF(C41&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C41,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Funciones de Días de la Semana&lt;/h2&gt;</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>2</v>
@@ -5481,7 +5529,7 @@
       <c r="D45" s="16"/>
       <c r="E45" s="71" t="str">
         <f>IF(C41&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>2</v>
@@ -5496,7 +5544,7 @@
       <c r="D46" s="75"/>
       <c r="E46" s="76" t="str">
         <f>IF(C41&lt;&gt;"",CONCATENATE("&lt;!-- ",C41," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones de Días de la Semana Fin --&gt;</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>2</v>
@@ -5522,21 +5570,23 @@
       <c r="D48" s="67"/>
       <c r="E48" s="68" t="str">
         <f>IF(C49&lt;&gt;"",CONCATENATE("&lt;!-- ",C49," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones Para Año Bisiesto --&gt;</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="69" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="61"/>
+      <c r="C49" s="61" t="s">
+        <v>107</v>
+      </c>
       <c r="D49" s="61"/>
       <c r="E49" s="71" t="str">
         <f>IF(C49&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>2</v>
@@ -5544,19 +5594,21 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="69" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="61"/>
+      <c r="C50" s="61" t="s">
+        <v>109</v>
+      </c>
       <c r="D50" s="61"/>
       <c r="E50" s="72" t="str">
         <f>IF(C49&lt;&gt;"",CONCATENATE("id=",Comillas,C50,Comillas),"")</f>
-        <v/>
+        <v>id="funcionesParaAñoBisiesto"</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>2</v>
@@ -5571,7 +5623,7 @@
       <c r="D51" s="16"/>
       <c r="E51" s="72" t="str">
         <f>IF(C49&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>2</v>
@@ -5586,7 +5638,7 @@
       <c r="D52" s="16"/>
       <c r="E52" s="72" t="str">
         <f>IF(C49&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C49,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Funciones Para Año Bisiesto&lt;/h2&gt;</v>
       </c>
       <c r="F52" s="16" t="s">
         <v>2</v>
@@ -5604,7 +5656,7 @@
       <c r="D53" s="16"/>
       <c r="E53" s="71" t="str">
         <f>IF(C49&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>2</v>
@@ -5619,7 +5671,7 @@
       <c r="D54" s="75"/>
       <c r="E54" s="76" t="str">
         <f>IF(C49&lt;&gt;"",CONCATENATE("&lt;!-- ",C49," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones Para Año Bisiesto Fin --&gt;</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>2</v>
@@ -5632,7 +5684,7 @@
       <c r="D55" s="67"/>
       <c r="E55" s="68" t="str">
         <f>IF(C56&lt;&gt;"",CONCATENATE("&lt;!-- ",C56," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones para Primer Día de la Semana --&gt;</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>2</v>
@@ -5640,16 +5692,18 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="69" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="61"/>
+      <c r="C56" s="61" t="s">
+        <v>111</v>
+      </c>
       <c r="D56" s="61"/>
       <c r="E56" s="71" t="str">
         <f>IF(C56&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>2</v>
@@ -5657,19 +5711,21 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="69" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="61"/>
+      <c r="C57" s="61" t="s">
+        <v>113</v>
+      </c>
       <c r="D57" s="61"/>
       <c r="E57" s="72" t="str">
         <f>IF(C56&lt;&gt;"",CONCATENATE("id=",Comillas,C57,Comillas),"")</f>
-        <v/>
+        <v>id="funcionesParaPrimerDiaDeLaSemana"</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>2</v>
@@ -5684,7 +5740,7 @@
       <c r="D58" s="16"/>
       <c r="E58" s="72" t="str">
         <f>IF(C56&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>2</v>
@@ -5699,7 +5755,7 @@
       <c r="D59" s="16"/>
       <c r="E59" s="72" t="str">
         <f>IF(C56&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C56,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Funciones para Primer Día de la Semana&lt;/h2&gt;</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>2</v>
@@ -5717,7 +5773,7 @@
       <c r="D60" s="16"/>
       <c r="E60" s="71" t="str">
         <f>IF(C56&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>2</v>
@@ -5732,7 +5788,7 @@
       <c r="D61" s="75"/>
       <c r="E61" s="76" t="str">
         <f>IF(C56&lt;&gt;"",CONCATENATE("&lt;!-- ",C56," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones para Primer Día de la Semana Fin --&gt;</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>2</v>
@@ -5745,7 +5801,7 @@
       <c r="D62" s="67"/>
       <c r="E62" s="68" t="str">
         <f>IF(C63&lt;&gt;"",CONCATENATE("&lt;!-- ",C63," --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones de Calendario En Formato De Tabla --&gt;</v>
       </c>
       <c r="F62" s="16" t="s">
         <v>2</v>
@@ -5756,16 +5812,18 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="69" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="70"/>
+      <c r="C63" s="70" t="s">
+        <v>115</v>
+      </c>
       <c r="D63" s="61"/>
       <c r="E63" s="71" t="str">
         <f>IF(C63&lt;&gt;"","&lt;div","")</f>
-        <v/>
+        <v>&lt;div</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>2</v>
@@ -5776,19 +5834,21 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="69" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="61"/>
+      <c r="C64" s="61" t="s">
+        <v>117</v>
+      </c>
       <c r="D64" s="61"/>
       <c r="E64" s="72" t="str">
         <f>IF(C63&lt;&gt;"",CONCATENATE("id=",Comillas,C64,Comillas),"")</f>
-        <v/>
+        <v>id="funcionesDeCalendarioEnFormatoDeTabla"</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>2</v>
@@ -5803,7 +5863,7 @@
       <c r="D65" s="16"/>
       <c r="E65" s="72" t="str">
         <f>IF(C63&lt;&gt;"",$F$42,"")</f>
-        <v/>
+        <v>class="mt-5 pt-5 "&gt;</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>2</v>
@@ -5818,7 +5878,7 @@
       <c r="D66" s="16"/>
       <c r="E66" s="72" t="str">
         <f>IF(C63&lt;&gt;"",CONCATENATE("&lt;h2 class=",Comillas,"mt-1",Comillas,"&gt;",C63,"&lt;/h2&gt;"),"")</f>
-        <v/>
+        <v>&lt;h2 class="mt-1"&gt;Funciones de Calendario En Formato De Tabla&lt;/h2&gt;</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>2</v>
@@ -5833,7 +5893,7 @@
       <c r="D67" s="16"/>
       <c r="E67" s="71" t="str">
         <f>IF(C63&lt;&gt;"","&lt;/div&gt;","")</f>
-        <v/>
+        <v>&lt;/div&gt;</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>2</v>
@@ -5846,7 +5906,7 @@
       <c r="D68" s="75"/>
       <c r="E68" s="76" t="str">
         <f>IF(C63&lt;&gt;"",CONCATENATE("&lt;!-- ",C63," Fin --&gt;"),"")</f>
-        <v/>
+        <v>&lt;!-- Funciones de Calendario En Formato De Tabla Fin --&gt;</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>2</v>
@@ -5869,7 +5929,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="69" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>2</v>
@@ -5881,7 +5941,7 @@
         <v/>
       </c>
       <c r="F70" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G70" s="16" t="s">
         <v>2</v>
@@ -5889,7 +5949,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="69" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>2</v>
@@ -5934,7 +5994,7 @@
         <v/>
       </c>
       <c r="G73" s="16" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5949,7 +6009,7 @@
         <v/>
       </c>
       <c r="G74" s="16" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:7">
@@ -5982,7 +6042,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="69" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B77" s="16" t="s">
         <v>2</v>
@@ -5994,7 +6054,7 @@
         <v/>
       </c>
       <c r="F77" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>2</v>
@@ -6002,7 +6062,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="69" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B78" s="16" t="s">
         <v>2</v>
@@ -6095,7 +6155,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="69" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B84" s="16" t="s">
         <v>2</v>
@@ -6107,7 +6167,7 @@
         <v/>
       </c>
       <c r="F84" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>2</v>
@@ -6115,7 +6175,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="69" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B85" s="16" t="s">
         <v>2</v>
@@ -6208,7 +6268,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="69" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B91" s="16" t="s">
         <v>2</v>
@@ -6220,7 +6280,7 @@
         <v/>
       </c>
       <c r="F91" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>2</v>
@@ -6228,7 +6288,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="69" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B92" s="16" t="s">
         <v>2</v>
@@ -6321,7 +6381,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="69" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B98" s="16" t="s">
         <v>2</v>
@@ -6333,7 +6393,7 @@
         <v/>
       </c>
       <c r="F98" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>2</v>
@@ -6341,7 +6401,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="69" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B99" s="16" t="s">
         <v>2</v>
@@ -6434,7 +6494,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="69" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B105" s="16" t="s">
         <v>2</v>
@@ -6446,7 +6506,7 @@
         <v/>
       </c>
       <c r="F105" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G105" s="16" t="s">
         <v>2</v>
@@ -6454,7 +6514,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="69" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B106" s="16" t="s">
         <v>2</v>
@@ -6543,7 +6603,7 @@
         <v>2</v>
       </c>
       <c r="E112" s="80" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G112" s="16" t="s">
         <v>2</v>
@@ -6555,7 +6615,7 @@
       </c>
       <c r="E113" s="55" t="str">
         <f>CONCATENATE("&lt;!--  ",$C$8,"--&gt;")</f>
-        <v>&lt;!--  El Módulo datetime --&gt;</v>
+        <v>&lt;!--  El módulo calendar, trabajando con funciones relacionadas con el calendario en Python  --&gt;</v>
       </c>
       <c r="G113" s="16" t="s">
         <v>2</v>
@@ -6566,10 +6626,10 @@
         <v>2</v>
       </c>
       <c r="E114" s="55" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G114" s="16" t="s">
         <v>2</v>
@@ -6580,7 +6640,7 @@
         <v>2</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="2:7">
@@ -6588,7 +6648,7 @@
         <v>2</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G116" s="81"/>
     </row>
@@ -6597,7 +6657,7 @@
         <v>2</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G117" s="82"/>
     </row>
@@ -6612,7 +6672,7 @@
         <v>2</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F119" s="16" t="s">
         <v>34</v>
@@ -6620,19 +6680,19 @@
     </row>
     <row r="120" ht="15.75" spans="5:5">
       <c r="E120" s="16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="121" spans="5:5">
       <c r="E121" s="83" t="str">
         <f>IF($C$25&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
     </row>
     <row r="122" spans="5:5">
       <c r="E122" s="84" t="str">
         <f>IF(C25&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C26,Comillas,"&gt;",C25,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#introduccion"&gt;Introducción&lt;/a&gt;</v>
       </c>
     </row>
     <row r="123" ht="15.75" spans="2:6">
@@ -6641,7 +6701,7 @@
       </c>
       <c r="E123" s="85" t="str">
         <f>IF($C$25&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
       <c r="F123" s="16" t="s">
         <v>2</v>
@@ -6653,7 +6713,7 @@
       </c>
       <c r="E124" s="83" t="str">
         <f>IF($C$33&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
       <c r="F124" s="16" t="s">
         <v>2</v>
@@ -6665,7 +6725,7 @@
       </c>
       <c r="E125" s="84" t="str">
         <f>IF(C33&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C34,Comillas,"&gt;",C33,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#funcionesPraObtenerElCalendario"&gt;Funciones para Obtener el Calendario&lt;/a&gt;</v>
       </c>
     </row>
     <row r="126" ht="15.75" spans="2:5">
@@ -6674,73 +6734,73 @@
       </c>
       <c r="E126" s="85" t="str">
         <f>IF($C$33&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
     </row>
     <row r="127" spans="5:5">
       <c r="E127" s="83" t="str">
         <f>IF(C41&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" s="84" t="str">
         <f>IF(C41&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C42,Comillas,"&gt;",C41,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#funcionesDeDIasDelaSemana"&gt;Funciones de Días de la Semana&lt;/a&gt;</v>
       </c>
     </row>
     <row r="129" ht="15.75" spans="5:5">
       <c r="E129" s="85" t="str">
         <f>IF(C41&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
     </row>
     <row r="130" spans="5:5">
       <c r="E130" s="83" t="str">
         <f>IF($C49&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
     </row>
     <row r="131" spans="5:5">
       <c r="E131" s="84" t="str">
         <f>IF(C49&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C50,Comillas,"&gt;",C49,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#funcionesParaAñoBisiesto"&gt;Funciones Para Año Bisiesto&lt;/a&gt;</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="5:5">
       <c r="E132" s="85" t="str">
         <f>IF(C49&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
     </row>
     <row r="133" spans="5:5">
       <c r="E133" s="83" t="str">
         <f>IF($C56&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
     </row>
     <row r="134" spans="5:5">
       <c r="E134" s="84" t="str">
         <f>IF(C56&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C57,Comillas,"&gt;",C56,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#funcionesParaPrimerDiaDeLaSemana"&gt;Funciones para Primer Día de la Semana&lt;/a&gt;</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="5:5">
       <c r="E135" s="85" t="str">
         <f>IF($C$56&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
     </row>
     <row r="136" spans="5:5">
       <c r="E136" s="83" t="str">
         <f>IF(C63&lt;&gt;"",$I$2,"")</f>
-        <v/>
+        <v>&lt;li class="list-group-item"&gt;</v>
       </c>
     </row>
     <row r="137" spans="5:10">
       <c r="E137" s="84" t="str">
         <f>IF(C63&lt;&gt;"",CONCATENATE("&lt;a href=",Comillas,"#",C64,Comillas,"&gt;",C63,"&lt;/a&gt;"),"")</f>
-        <v/>
+        <v>&lt;a href="#funcionesDeCalendarioEnFormatoDeTabla"&gt;Funciones de Calendario En Formato De Tabla&lt;/a&gt;</v>
       </c>
       <c r="H137" s="86"/>
       <c r="I137" s="86"/>
@@ -6749,7 +6809,7 @@
     <row r="138" ht="15.75" spans="5:5">
       <c r="E138" s="85" t="str">
         <f>IF(C63&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
+        <v>&lt;/li&gt;</v>
       </c>
     </row>
     <row r="139" spans="5:12">
@@ -6870,17 +6930,17 @@
     </row>
     <row r="157" spans="5:5">
       <c r="E157" s="16" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="158" spans="5:5">
       <c r="E158" s="16" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="159" spans="5:5">
       <c r="E159" s="16" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="160" spans="5:5">
@@ -6890,7 +6950,7 @@
     </row>
     <row r="161" spans="5:5">
       <c r="E161" s="87" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="162"/>
@@ -6902,7 +6962,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" display="https://images2.imgbox.com/38/c8/WnB7uL66_o.png" tooltip="https://images2.imgbox.com/38/c8/WnB7uL66_o.png"/>
+    <hyperlink ref="C15" r:id="rId1" display="https://images2.imgbox.com/37/f3/xVxmYAZb_o.png" tooltip="https://images2.imgbox.com/37/f3/xVxmYAZb_o.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6933,12 +6993,12 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="26" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="44" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E2" s="43" t="s">
         <v>2</v>
@@ -6949,7 +7009,7 @@
       </c>
       <c r="G2" s="45"/>
       <c r="I2" s="26" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
@@ -6963,13 +7023,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F3" t="str">
         <f>CONCATENATE(B3,D3,C3)</f>
@@ -6977,13 +7037,13 @@
       </c>
       <c r="G3" s="48"/>
       <c r="I3" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J3" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K3" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N3" t="str">
         <f>CONCATENATE(J3,L3,K3)</f>
@@ -7021,7 +7081,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" t="s">
@@ -7036,7 +7096,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L6" s="49"/>
       <c r="M6" t="s">
@@ -7104,12 +7164,12 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="26" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E10" s="43" t="s">
         <v>2</v>
@@ -7120,7 +7180,7 @@
       </c>
       <c r="G10" s="45"/>
       <c r="I10" s="26" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="43"/>
@@ -7136,13 +7196,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F11" t="str">
         <f>CONCATENATE(B11,D11,C11)</f>
@@ -7150,13 +7210,13 @@
       </c>
       <c r="G11" s="48"/>
       <c r="I11" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K11" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N11" t="str">
         <f>CONCATENATE(J11,L11,K11)</f>
@@ -7194,7 +7254,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D14" s="49"/>
       <c r="E14" t="s">
@@ -7209,7 +7269,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L14" s="49"/>
       <c r="M14" t="s">
@@ -7275,12 +7335,12 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="26" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E18" s="43"/>
       <c r="F18" s="43" t="str">
@@ -7289,7 +7349,7 @@
       </c>
       <c r="G18" s="45"/>
       <c r="I18" s="26" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
@@ -7303,13 +7363,13 @@
     </row>
     <row r="19" customFormat="1" spans="1:15">
       <c r="A19" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F19" t="str">
         <f>CONCATENATE(B19,D19,C19)</f>
@@ -7317,13 +7377,13 @@
       </c>
       <c r="G19" s="48"/>
       <c r="I19" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J19" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K19" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N19" t="str">
         <f>CONCATENATE(J19,L19,K19)</f>
@@ -7361,7 +7421,7 @@
     </row>
     <row r="22" customFormat="1" spans="1:15">
       <c r="A22" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D22" s="49"/>
       <c r="E22" t="s">
@@ -7373,7 +7433,7 @@
       </c>
       <c r="G22" s="48"/>
       <c r="I22" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L22" s="49"/>
       <c r="M22" t="s">
@@ -7441,12 +7501,12 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="26" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
       <c r="D26" s="44" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E26" s="43"/>
       <c r="F26" s="43" t="str">
@@ -7455,7 +7515,7 @@
       </c>
       <c r="G26" s="45"/>
       <c r="I26" s="26" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J26" s="43"/>
       <c r="K26" s="43"/>
@@ -7469,13 +7529,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F27" t="str">
         <f>CONCATENATE(B27,D27,C27)</f>
@@ -7483,13 +7543,13 @@
       </c>
       <c r="G27" s="48"/>
       <c r="I27" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J27" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K27" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N27" t="str">
         <f>CONCATENATE(J27,L27,K27)</f>
@@ -7527,7 +7587,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D30" s="49"/>
       <c r="E30" t="s">
@@ -7542,7 +7602,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L30" s="49"/>
       <c r="M30" t="s">
@@ -7610,14 +7670,14 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="26" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B34" s="43"/>
       <c r="C34" s="43" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E34" s="43"/>
       <c r="F34" s="43" t="str">
@@ -7626,7 +7686,7 @@
       </c>
       <c r="G34" s="45"/>
       <c r="I34" s="26" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J34" s="43"/>
       <c r="K34" s="43"/>
@@ -7640,13 +7700,13 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F35" t="str">
         <f>CONCATENATE(B35,D35,C35)</f>
@@ -7654,13 +7714,13 @@
       </c>
       <c r="G35" s="48"/>
       <c r="I35" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J35" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N35" t="str">
         <f>CONCATENATE(J35,L35,K35)</f>
@@ -7698,7 +7758,7 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D38" s="49"/>
       <c r="E38" t="s">
@@ -7710,7 +7770,7 @@
       </c>
       <c r="G38" s="48"/>
       <c r="I38" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L38" s="49"/>
       <c r="M38" t="s">
@@ -7778,12 +7838,12 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="26" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
       <c r="D42" s="44" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E42" s="43"/>
       <c r="F42" s="43" t="str">
@@ -7792,7 +7852,7 @@
       </c>
       <c r="G42" s="45"/>
       <c r="I42" s="26" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J42" s="43"/>
       <c r="K42" s="43"/>
@@ -7806,13 +7866,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F43" t="str">
         <f>CONCATENATE(B43,D43,C43)</f>
@@ -7820,13 +7880,13 @@
       </c>
       <c r="G43" s="48"/>
       <c r="I43" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J43" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K43" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N43" t="str">
         <f>CONCATENATE(J43,L43,K43)</f>
@@ -7864,7 +7924,7 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D46" s="49"/>
       <c r="E46" t="s">
@@ -7876,7 +7936,7 @@
       </c>
       <c r="G46" s="48"/>
       <c r="I46" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L46" s="49"/>
       <c r="M46" t="s">
@@ -7944,12 +8004,12 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="26" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B50" s="43"/>
       <c r="C50" s="43"/>
       <c r="D50" s="44" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E50" s="43"/>
       <c r="F50" s="43" t="str">
@@ -7958,11 +8018,11 @@
       </c>
       <c r="G50" s="45"/>
       <c r="I50" s="26" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J50" s="43"/>
       <c r="K50" s="43" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="L50" s="44"/>
       <c r="M50" s="43"/>
@@ -7974,13 +8034,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F51" t="str">
         <f>CONCATENATE(B51,D51,C51)</f>
@@ -7988,13 +8048,13 @@
       </c>
       <c r="G51" s="48"/>
       <c r="I51" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J51" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K51" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N51" t="str">
         <f>CONCATENATE(J51,L51,K51)</f>
@@ -8032,7 +8092,7 @@
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D54" s="49"/>
       <c r="E54" t="s">
@@ -8044,7 +8104,7 @@
       </c>
       <c r="G54" s="48"/>
       <c r="I54" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L54" s="49"/>
       <c r="M54" t="s">
@@ -8112,12 +8172,12 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="26" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E58" s="43"/>
       <c r="F58" s="43" t="str">
@@ -8126,7 +8186,7 @@
       </c>
       <c r="G58" s="45"/>
       <c r="I58" s="26" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J58" s="43"/>
       <c r="K58" s="43"/>
@@ -8140,13 +8200,13 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F59" t="str">
         <f>CONCATENATE(B59,D59,C59)</f>
@@ -8154,13 +8214,13 @@
       </c>
       <c r="G59" s="48"/>
       <c r="I59" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J59" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K59" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N59" t="str">
         <f>CONCATENATE(J59,L59,K59)</f>
@@ -8198,7 +8258,7 @@
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D62" s="49"/>
       <c r="E62" t="s">
@@ -8210,7 +8270,7 @@
       </c>
       <c r="G62" s="48"/>
       <c r="I62" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L62" s="49"/>
       <c r="M62" t="s">
@@ -8278,12 +8338,12 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="26" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B66" s="43"/>
       <c r="C66" s="43"/>
       <c r="D66" s="44" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E66" s="43"/>
       <c r="F66" s="43" t="str">
@@ -8292,7 +8352,7 @@
       </c>
       <c r="G66" s="45"/>
       <c r="I66" s="26" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J66" s="43"/>
       <c r="K66" s="43"/>
@@ -8306,13 +8366,13 @@
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F67" t="str">
         <f>CONCATENATE(B67,D67,C67)</f>
@@ -8320,13 +8380,13 @@
       </c>
       <c r="G67" s="48"/>
       <c r="I67" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J67" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K67" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N67" t="str">
         <f>CONCATENATE(J67,L67,K67)</f>
@@ -8364,7 +8424,7 @@
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D70" s="49"/>
       <c r="E70" t="s">
@@ -8376,7 +8436,7 @@
       </c>
       <c r="G70" s="48"/>
       <c r="I70" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L70" s="49"/>
       <c r="M70" t="s">
@@ -8444,12 +8504,12 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="26" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B74" s="43"/>
       <c r="C74" s="43"/>
       <c r="D74" s="44" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E74" s="43"/>
       <c r="F74" s="43" t="str">
@@ -8458,7 +8518,7 @@
       </c>
       <c r="G74" s="45"/>
       <c r="I74" s="26" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J74" s="43"/>
       <c r="K74" s="43"/>
@@ -8472,13 +8532,13 @@
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F75" t="str">
         <f>CONCATENATE(B75,D75,C75)</f>
@@ -8486,13 +8546,13 @@
       </c>
       <c r="G75" s="48"/>
       <c r="I75" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J75" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K75" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N75" t="str">
         <f>CONCATENATE(J75,L75,K75)</f>
@@ -8530,7 +8590,7 @@
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D78" s="49"/>
       <c r="E78" t="s">
@@ -8542,7 +8602,7 @@
       </c>
       <c r="G78" s="48"/>
       <c r="I78" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L78" s="49"/>
       <c r="M78" t="s">
@@ -8610,12 +8670,12 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B82" s="43"/>
       <c r="C82" s="43"/>
       <c r="D82" s="44" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E82" s="43"/>
       <c r="F82" s="43" t="str">
@@ -8624,7 +8684,7 @@
       </c>
       <c r="G82" s="45"/>
       <c r="I82" s="26" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J82" s="43"/>
       <c r="K82" s="43"/>
@@ -8638,13 +8698,13 @@
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B83" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F83" t="str">
         <f>CONCATENATE(B83,D83,C83)</f>
@@ -8652,13 +8712,13 @@
       </c>
       <c r="G83" s="48"/>
       <c r="I83" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J83" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K83" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N83" t="str">
         <f>CONCATENATE(J83,L83,K83)</f>
@@ -8696,7 +8756,7 @@
     </row>
     <row r="86" spans="1:15">
       <c r="A86" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D86" s="49"/>
       <c r="E86" t="s">
@@ -8708,7 +8768,7 @@
       </c>
       <c r="G86" s="48"/>
       <c r="I86" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L86" s="49"/>
       <c r="M86" t="s">
@@ -8776,12 +8836,12 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B90" s="43"/>
       <c r="C90" s="43"/>
       <c r="D90" s="44" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E90" s="43"/>
       <c r="F90" s="43" t="str">
@@ -8790,7 +8850,7 @@
       </c>
       <c r="G90" s="45"/>
       <c r="I90" s="26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J90" s="43"/>
       <c r="K90" s="43"/>
@@ -8804,13 +8864,13 @@
     </row>
     <row r="91" spans="1:15">
       <c r="A91" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B91" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C91" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F91" t="str">
         <f>CONCATENATE(B91,D91,C91)</f>
@@ -8818,13 +8878,13 @@
       </c>
       <c r="G91" s="48"/>
       <c r="I91" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J91" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K91" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N91" t="str">
         <f>CONCATENATE(J91,L91,K91)</f>
@@ -8862,7 +8922,7 @@
     </row>
     <row r="94" spans="1:15">
       <c r="A94" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D94" s="49"/>
       <c r="E94" t="s">
@@ -8874,7 +8934,7 @@
       </c>
       <c r="G94" s="48"/>
       <c r="I94" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L94" s="49"/>
       <c r="M94" t="s">
@@ -8942,12 +9002,12 @@
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="26" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B98" s="43"/>
       <c r="C98" s="43"/>
       <c r="D98" s="44" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E98" s="43"/>
       <c r="F98" s="43" t="str">
@@ -8956,7 +9016,7 @@
       </c>
       <c r="G98" s="45"/>
       <c r="I98" s="26" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J98" s="43"/>
       <c r="K98" s="43"/>
@@ -8970,13 +9030,13 @@
     </row>
     <row r="99" spans="1:15">
       <c r="A99" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B99" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F99" t="str">
         <f>CONCATENATE(B99,D99,C99)</f>
@@ -8984,13 +9044,13 @@
       </c>
       <c r="G99" s="48"/>
       <c r="I99" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J99" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K99" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N99" t="str">
         <f>CONCATENATE(J99,L99,K99)</f>
@@ -9028,7 +9088,7 @@
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D102" s="49"/>
       <c r="E102" t="s">
@@ -9040,7 +9100,7 @@
       </c>
       <c r="G102" s="48"/>
       <c r="I102" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L102" s="49"/>
       <c r="M102" t="s">
@@ -9108,12 +9168,12 @@
     </row>
     <row r="106" customFormat="1" spans="1:15">
       <c r="A106" s="26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B106" s="43"/>
       <c r="C106" s="43"/>
       <c r="D106" s="44" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E106" s="43"/>
       <c r="F106" s="43" t="str">
@@ -9122,7 +9182,7 @@
       </c>
       <c r="G106" s="45"/>
       <c r="I106" s="26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J106" s="43"/>
       <c r="K106" s="43"/>
@@ -9136,13 +9196,13 @@
     </row>
     <row r="107" customFormat="1" spans="1:15">
       <c r="A107" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B107" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F107" t="str">
         <f>CONCATENATE(B107,D107,C107)</f>
@@ -9150,13 +9210,13 @@
       </c>
       <c r="G107" s="48"/>
       <c r="I107" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J107" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K107" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N107" t="str">
         <f>CONCATENATE(J107,L107,K107)</f>
@@ -9194,7 +9254,7 @@
     </row>
     <row r="110" customFormat="1" spans="1:15">
       <c r="A110" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D110" s="49"/>
       <c r="E110" t="s">
@@ -9206,7 +9266,7 @@
       </c>
       <c r="G110" s="48"/>
       <c r="I110" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L110" s="49"/>
       <c r="M110" t="s">
@@ -9274,7 +9334,7 @@
     </row>
     <row r="114" customFormat="1" spans="1:15">
       <c r="A114" s="26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B114" s="43"/>
       <c r="C114" s="43"/>
@@ -9286,7 +9346,7 @@
       </c>
       <c r="G114" s="45"/>
       <c r="I114" s="26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J114" s="43"/>
       <c r="K114" s="43"/>
@@ -9300,13 +9360,13 @@
     </row>
     <row r="115" customFormat="1" spans="1:15">
       <c r="A115" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F115" t="str">
         <f>CONCATENATE(B115,D115,C115)</f>
@@ -9314,13 +9374,13 @@
       </c>
       <c r="G115" s="48"/>
       <c r="I115" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J115" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K115" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N115" t="str">
         <f>CONCATENATE(J115,L115,K115)</f>
@@ -9358,7 +9418,7 @@
     </row>
     <row r="118" customFormat="1" spans="1:15">
       <c r="A118" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D118" s="49"/>
       <c r="E118" t="s">
@@ -9370,7 +9430,7 @@
       </c>
       <c r="G118" s="48"/>
       <c r="I118" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L118" s="49"/>
       <c r="M118" t="s">
@@ -9438,7 +9498,7 @@
     </row>
     <row r="122" customFormat="1" spans="1:15">
       <c r="A122" s="26" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B122" s="43"/>
       <c r="C122" s="43"/>
@@ -9450,7 +9510,7 @@
       </c>
       <c r="G122" s="45"/>
       <c r="I122" s="26" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="J122" s="43"/>
       <c r="K122" s="43"/>
@@ -9464,13 +9524,13 @@
     </row>
     <row r="123" customFormat="1" spans="1:15">
       <c r="A123" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B123" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C123" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F123" t="str">
         <f>CONCATENATE(B123,D123,C123)</f>
@@ -9478,13 +9538,13 @@
       </c>
       <c r="G123" s="48"/>
       <c r="I123" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J123" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K123" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N123" t="str">
         <f>CONCATENATE(J123,L123,K123)</f>
@@ -9522,7 +9582,7 @@
     </row>
     <row r="126" customFormat="1" spans="1:15">
       <c r="A126" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D126" s="49"/>
       <c r="E126" t="s">
@@ -9534,7 +9594,7 @@
       </c>
       <c r="G126" s="48"/>
       <c r="I126" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L126" s="49"/>
       <c r="M126" t="s">
@@ -9602,7 +9662,7 @@
     </row>
     <row r="130" customFormat="1" spans="1:15">
       <c r="A130" s="26" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B130" s="43"/>
       <c r="C130" s="43"/>
@@ -9614,7 +9674,7 @@
       </c>
       <c r="G130" s="45"/>
       <c r="I130" s="26" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J130" s="43"/>
       <c r="K130" s="43"/>
@@ -9628,13 +9688,13 @@
     </row>
     <row r="131" customFormat="1" spans="1:15">
       <c r="A131" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B131" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C131" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F131" t="str">
         <f>CONCATENATE(B131,D131,C131)</f>
@@ -9642,13 +9702,13 @@
       </c>
       <c r="G131" s="48"/>
       <c r="I131" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J131" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K131" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N131" t="str">
         <f>CONCATENATE(J131,L131,K131)</f>
@@ -9686,7 +9746,7 @@
     </row>
     <row r="134" customFormat="1" spans="1:15">
       <c r="A134" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D134" s="49"/>
       <c r="E134" t="s">
@@ -9698,7 +9758,7 @@
       </c>
       <c r="G134" s="48"/>
       <c r="I134" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L134" s="49"/>
       <c r="M134" t="s">
@@ -9766,7 +9826,7 @@
     </row>
     <row r="138" customFormat="1" spans="1:15">
       <c r="A138" s="26" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B138" s="43"/>
       <c r="C138" s="43"/>
@@ -9778,7 +9838,7 @@
       </c>
       <c r="G138" s="45"/>
       <c r="I138" s="26" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J138" s="43"/>
       <c r="K138" s="43"/>
@@ -9792,13 +9852,13 @@
     </row>
     <row r="139" customFormat="1" spans="1:15">
       <c r="A139" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B139" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C139" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F139" t="str">
         <f>CONCATENATE(B139,D139,C139)</f>
@@ -9806,13 +9866,13 @@
       </c>
       <c r="G139" s="48"/>
       <c r="I139" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J139" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K139" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N139" t="str">
         <f>CONCATENATE(J139,L139,K139)</f>
@@ -9850,7 +9910,7 @@
     </row>
     <row r="142" customFormat="1" spans="1:15">
       <c r="A142" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D142" s="49"/>
       <c r="E142" t="s">
@@ -9862,7 +9922,7 @@
       </c>
       <c r="G142" s="48"/>
       <c r="I142" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L142" s="49"/>
       <c r="M142" t="s">
@@ -9930,7 +9990,7 @@
     </row>
     <row r="146" customFormat="1" spans="1:15">
       <c r="A146" s="26" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B146" s="43"/>
       <c r="C146" s="43"/>
@@ -9942,7 +10002,7 @@
       </c>
       <c r="G146" s="45"/>
       <c r="I146" s="26" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J146" s="43"/>
       <c r="K146" s="43"/>
@@ -9956,13 +10016,13 @@
     </row>
     <row r="147" customFormat="1" spans="1:15">
       <c r="A147" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C147" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F147" t="str">
         <f>CONCATENATE(B147,D147,C147)</f>
@@ -9970,13 +10030,13 @@
       </c>
       <c r="G147" s="48"/>
       <c r="I147" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J147" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K147" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N147" t="str">
         <f>CONCATENATE(J147,L147,K147)</f>
@@ -10014,7 +10074,7 @@
     </row>
     <row r="150" customFormat="1" spans="1:15">
       <c r="A150" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D150" s="49"/>
       <c r="E150" t="s">
@@ -10026,7 +10086,7 @@
       </c>
       <c r="G150" s="48"/>
       <c r="I150" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L150" s="49"/>
       <c r="M150" t="s">
@@ -10094,7 +10154,7 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B154" s="43"/>
       <c r="C154" s="43"/>
@@ -10106,7 +10166,7 @@
       </c>
       <c r="G154" s="45"/>
       <c r="I154" s="26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="J154" s="43"/>
       <c r="K154" s="43"/>
@@ -10120,13 +10180,13 @@
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C155" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F155" t="str">
         <f>CONCATENATE(B155,D155,C155)</f>
@@ -10134,13 +10194,13 @@
       </c>
       <c r="G155" s="48"/>
       <c r="I155" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J155" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K155" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N155" t="str">
         <f>CONCATENATE(J155,L155,K155)</f>
@@ -10178,7 +10238,7 @@
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D158" s="49"/>
       <c r="E158" t="s">
@@ -10190,7 +10250,7 @@
       </c>
       <c r="G158" s="48"/>
       <c r="I158" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L158" s="49"/>
       <c r="M158" t="s">
@@ -10258,7 +10318,7 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="26" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B162" s="43"/>
       <c r="C162" s="43"/>
@@ -10270,7 +10330,7 @@
       </c>
       <c r="G162" s="45"/>
       <c r="I162" s="26" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J162" s="43"/>
       <c r="K162" s="43"/>
@@ -10284,13 +10344,13 @@
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B163" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C163" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F163" t="str">
         <f>CONCATENATE(B163,D163,C163)</f>
@@ -10298,13 +10358,13 @@
       </c>
       <c r="G163" s="48"/>
       <c r="I163" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J163" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K163" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N163" t="str">
         <f>CONCATENATE(J163,L163,K163)</f>
@@ -10342,7 +10402,7 @@
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D166" s="49"/>
       <c r="E166" t="s">
@@ -10354,7 +10414,7 @@
       </c>
       <c r="G166" s="48"/>
       <c r="I166" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L166" s="49"/>
       <c r="M166" t="s">
@@ -10422,7 +10482,7 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="26" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B170" s="43"/>
       <c r="C170" s="43"/>
@@ -10434,7 +10494,7 @@
       </c>
       <c r="G170" s="45"/>
       <c r="I170" s="26" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J170" s="43"/>
       <c r="K170" s="43"/>
@@ -10448,13 +10508,13 @@
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B171" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C171" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F171" t="str">
         <f>CONCATENATE(B171,D171,C171)</f>
@@ -10462,13 +10522,13 @@
       </c>
       <c r="G171" s="48"/>
       <c r="I171" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J171" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K171" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N171" t="str">
         <f>CONCATENATE(J171,L171,K171)</f>
@@ -10506,7 +10566,7 @@
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D174" s="49"/>
       <c r="E174" t="s">
@@ -10518,7 +10578,7 @@
       </c>
       <c r="G174" s="48"/>
       <c r="I174" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L174" s="49"/>
       <c r="M174" t="s">
@@ -10586,7 +10646,7 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="26" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B178" s="43"/>
       <c r="C178" s="43"/>
@@ -10598,7 +10658,7 @@
       </c>
       <c r="G178" s="45"/>
       <c r="I178" s="26" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J178" s="43"/>
       <c r="K178" s="43"/>
@@ -10612,13 +10672,13 @@
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B179" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C179" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F179" t="str">
         <f>CONCATENATE(B179,D179,C179)</f>
@@ -10626,13 +10686,13 @@
       </c>
       <c r="G179" s="48"/>
       <c r="I179" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J179" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K179" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N179" t="str">
         <f>CONCATENATE(J179,L179,K179)</f>
@@ -10670,7 +10730,7 @@
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D182" s="49"/>
       <c r="E182" t="s">
@@ -10682,7 +10742,7 @@
       </c>
       <c r="G182" s="48"/>
       <c r="I182" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L182" s="49"/>
       <c r="M182" t="s">
@@ -10731,7 +10791,7 @@
     <row r="185" ht="15"/>
     <row r="186" spans="1:15">
       <c r="A186" s="26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B186" s="43"/>
       <c r="C186" s="43"/>
@@ -10743,7 +10803,7 @@
       </c>
       <c r="G186" s="45"/>
       <c r="I186" s="26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J186" s="43"/>
       <c r="K186" s="43"/>
@@ -10757,13 +10817,13 @@
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B187" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C187" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F187" t="str">
         <f>CONCATENATE(B187,D187,C187)</f>
@@ -10771,13 +10831,13 @@
       </c>
       <c r="G187" s="48"/>
       <c r="I187" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J187" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K187" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N187" t="str">
         <f>CONCATENATE(J187,L187,K187)</f>
@@ -10815,7 +10875,7 @@
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D190" s="49"/>
       <c r="E190" t="s">
@@ -10827,7 +10887,7 @@
       </c>
       <c r="G190" s="48"/>
       <c r="I190" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L190" s="49"/>
       <c r="M190" t="s">
@@ -10895,7 +10955,7 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B194" s="43"/>
       <c r="C194" s="43"/>
@@ -10907,7 +10967,7 @@
       </c>
       <c r="G194" s="45"/>
       <c r="I194" s="26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J194" s="43"/>
       <c r="K194" s="43"/>
@@ -10921,13 +10981,13 @@
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B195" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C195" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F195" t="str">
         <f>CONCATENATE(B195,D195,C195)</f>
@@ -10935,13 +10995,13 @@
       </c>
       <c r="G195" s="48"/>
       <c r="I195" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J195" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K195" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N195" t="str">
         <f>CONCATENATE(J195,L195,K195)</f>
@@ -10979,7 +11039,7 @@
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D198" s="49"/>
       <c r="E198" t="s">
@@ -10991,7 +11051,7 @@
       </c>
       <c r="G198" s="48"/>
       <c r="I198" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L198" s="49"/>
       <c r="M198" t="s">
@@ -11059,7 +11119,7 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="26" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B202" s="43"/>
       <c r="C202" s="43"/>
@@ -11071,7 +11131,7 @@
       </c>
       <c r="G202" s="45"/>
       <c r="I202" s="26" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="J202" s="43"/>
       <c r="K202" s="43"/>
@@ -11085,13 +11145,13 @@
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B203" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C203" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F203" t="str">
         <f>CONCATENATE(B203,D203,C203)</f>
@@ -11099,13 +11159,13 @@
       </c>
       <c r="G203" s="48"/>
       <c r="I203" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J203" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K203" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N203" t="str">
         <f>CONCATENATE(J203,L203,K203)</f>
@@ -11143,7 +11203,7 @@
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D206" s="49"/>
       <c r="E206" t="s">
@@ -11155,7 +11215,7 @@
       </c>
       <c r="G206" s="48"/>
       <c r="I206" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L206" s="49"/>
       <c r="M206" t="s">
@@ -11223,7 +11283,7 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="26" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B210" s="43"/>
       <c r="C210" s="43"/>
@@ -11235,7 +11295,7 @@
       </c>
       <c r="G210" s="45"/>
       <c r="I210" s="26" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J210" s="43"/>
       <c r="K210" s="43"/>
@@ -11249,13 +11309,13 @@
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B211" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C211" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F211" t="str">
         <f>CONCATENATE(B211,D211,C211)</f>
@@ -11263,13 +11323,13 @@
       </c>
       <c r="G211" s="48"/>
       <c r="I211" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J211" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K211" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N211" t="str">
         <f>CONCATENATE(J211,L211,K211)</f>
@@ -11307,7 +11367,7 @@
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D214" s="49"/>
       <c r="E214" t="s">
@@ -11319,7 +11379,7 @@
       </c>
       <c r="G214" s="48"/>
       <c r="I214" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L214" s="49"/>
       <c r="M214" t="s">
@@ -11387,7 +11447,7 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="26" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B218" s="43"/>
       <c r="C218" s="43"/>
@@ -11399,7 +11459,7 @@
       </c>
       <c r="G218" s="45"/>
       <c r="I218" s="26" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J218" s="43"/>
       <c r="K218" s="43"/>
@@ -11413,13 +11473,13 @@
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B219" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C219" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F219" t="str">
         <f>CONCATENATE(B219,D219,C219)</f>
@@ -11427,13 +11487,13 @@
       </c>
       <c r="G219" s="48"/>
       <c r="I219" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J219" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K219" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N219" t="str">
         <f>CONCATENATE(J219,L219,K219)</f>
@@ -11471,7 +11531,7 @@
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D222" s="49"/>
       <c r="E222" t="s">
@@ -11483,7 +11543,7 @@
       </c>
       <c r="G222" s="48"/>
       <c r="I222" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L222" s="49"/>
       <c r="M222" t="s">
@@ -11551,7 +11611,7 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="26" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B226" s="43"/>
       <c r="C226" s="43"/>
@@ -11563,7 +11623,7 @@
       </c>
       <c r="G226" s="45"/>
       <c r="I226" s="26" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J226" s="43"/>
       <c r="K226" s="43"/>
@@ -11577,13 +11637,13 @@
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B227" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C227" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F227" t="str">
         <f>CONCATENATE(B227,D227,C227)</f>
@@ -11591,13 +11651,13 @@
       </c>
       <c r="G227" s="48"/>
       <c r="I227" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J227" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K227" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N227" t="str">
         <f>CONCATENATE(J227,L227,K227)</f>
@@ -11635,7 +11695,7 @@
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D230" s="49"/>
       <c r="E230" t="s">
@@ -11647,7 +11707,7 @@
       </c>
       <c r="G230" s="48"/>
       <c r="I230" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L230" s="49"/>
       <c r="M230" t="s">
@@ -11715,7 +11775,7 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B234" s="43"/>
       <c r="C234" s="43"/>
@@ -11727,7 +11787,7 @@
       </c>
       <c r="G234" s="45"/>
       <c r="I234" s="26" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="J234" s="43"/>
       <c r="K234" s="43"/>
@@ -11741,13 +11801,13 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B235" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C235" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F235" t="str">
         <f>CONCATENATE(B235,D235,C235)</f>
@@ -11755,13 +11815,13 @@
       </c>
       <c r="G235" s="48"/>
       <c r="I235" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J235" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K235" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N235" t="str">
         <f>CONCATENATE(J235,L235,K235)</f>
@@ -11799,7 +11859,7 @@
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D238" s="49"/>
       <c r="E238" t="s">
@@ -11811,7 +11871,7 @@
       </c>
       <c r="G238" s="48"/>
       <c r="I238" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L238" s="49"/>
       <c r="M238" t="s">
@@ -11879,7 +11939,7 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="26" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B242" s="43"/>
       <c r="C242" s="43"/>
@@ -11891,7 +11951,7 @@
       </c>
       <c r="G242" s="45"/>
       <c r="I242" s="26" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J242" s="43"/>
       <c r="K242" s="43"/>
@@ -11905,13 +11965,13 @@
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B243" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C243" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F243" t="str">
         <f>CONCATENATE(B243,D243,C243)</f>
@@ -11919,13 +11979,13 @@
       </c>
       <c r="G243" s="48"/>
       <c r="I243" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J243" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K243" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N243" t="str">
         <f>CONCATENATE(J243,L243,K243)</f>
@@ -11963,7 +12023,7 @@
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D246" s="49"/>
       <c r="E246" t="s">
@@ -11975,7 +12035,7 @@
       </c>
       <c r="G246" s="48"/>
       <c r="I246" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L246" s="49"/>
       <c r="M246" t="s">
@@ -12043,7 +12103,7 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="26" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B250" s="43"/>
       <c r="C250" s="43"/>
@@ -12055,7 +12115,7 @@
       </c>
       <c r="G250" s="45"/>
       <c r="I250" s="26" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J250" s="43"/>
       <c r="K250" s="43"/>
@@ -12069,13 +12129,13 @@
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B251" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C251" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F251" t="str">
         <f>CONCATENATE(B251,D251,C251)</f>
@@ -12083,13 +12143,13 @@
       </c>
       <c r="G251" s="48"/>
       <c r="I251" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J251" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K251" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N251" t="str">
         <f>CONCATENATE(J251,L251,K251)</f>
@@ -12127,7 +12187,7 @@
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D254" s="49"/>
       <c r="E254" t="s">
@@ -12139,7 +12199,7 @@
       </c>
       <c r="G254" s="48"/>
       <c r="I254" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L254" s="49"/>
       <c r="M254" t="s">
@@ -12207,7 +12267,7 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="26" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B258" s="43"/>
       <c r="C258" s="43"/>
@@ -12219,7 +12279,7 @@
       </c>
       <c r="G258" s="45"/>
       <c r="I258" s="26" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J258" s="43"/>
       <c r="K258" s="43"/>
@@ -12233,13 +12293,13 @@
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B259" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C259" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F259" t="str">
         <f>CONCATENATE(B259,D259,C259)</f>
@@ -12247,13 +12307,13 @@
       </c>
       <c r="G259" s="48"/>
       <c r="I259" s="28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J259" s="46" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K259" s="47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N259" t="str">
         <f>CONCATENATE(J259,L259,K259)</f>
@@ -12291,7 +12351,7 @@
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D262" s="49"/>
       <c r="E262" t="s">
@@ -12303,7 +12363,7 @@
       </c>
       <c r="G262" s="48"/>
       <c r="I262" s="28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L262" s="49"/>
       <c r="M262" t="s">
@@ -12376,19 +12436,19 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" s="23" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G2" s="23" t="str">
         <f>A2</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="Q2" s="23" t="str">
         <f>K2</f>
@@ -12402,7 +12462,7 @@
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" ref="B3:B19" si="1">IF(F3&lt;&gt;"",LEFT(F3,FIND(":",F3,1)-1),"")</f>
-        <v>Usar os.path</v>
+        <v>calendar.prmonth(year, month)</v>
       </c>
       <c r="C3" s="22" t="str">
         <f t="shared" ref="C3:C19" si="2">IF(F3&lt;&gt;"","&lt;/span&gt;","")</f>
@@ -12410,18 +12470,18 @@
       </c>
       <c r="D3" s="22" t="str">
         <f t="shared" ref="D3:D19" si="3">IF(F3&lt;&gt;"",RIGHT(F3,LEN(F3)-FIND(":",F3,1)),"")</f>
-        <v> Siempre que sea posible, utilice las funciones de os.path para garantizar la compatibilidad multiplataforma.</v>
+        <v> Imprime el calendario de un mes específico en formato tabular.</v>
       </c>
       <c r="E3" s="22" t="str">
         <f t="shared" ref="E3:E19" si="4">IF(F3&lt;&gt;"","&lt;/li&gt;","")</f>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G3" s="23" t="str">
         <f>IF(F3&lt;&gt;"",CONCATENATE(A3,B3,C3,":",D3,E3),IF(F2&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Usar os.path&lt;/span&gt;: Siempre que sea posible, utilice las funciones de os.path para garantizar la compatibilidad multiplataforma.&lt;/li&gt;</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;calendar.prmonth(year, month)&lt;/span&gt;: Imprime el calendario de un mes específico en formato tabular.&lt;/li&gt;</v>
       </c>
       <c r="K3" s="22" t="str">
         <f t="shared" ref="K3:K19" si="5">IF(P3&lt;&gt;"",$A$20,"")</f>
@@ -12456,7 +12516,7 @@
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>Capturar excepciones</v>
+        <v>calendar.pryear(year)</v>
       </c>
       <c r="C4" s="22" t="str">
         <f t="shared" si="2"/>
@@ -12464,18 +12524,18 @@
       </c>
       <c r="D4" s="22" t="str">
         <f t="shared" si="3"/>
-        <v> Algunas operaciones, como cambiar de directorio o eliminar archivos, pueden generar errores si la ruta no existe o no se tienen permisos.</v>
+        <v> Imprime el calendario completo de un año en formato tabular.</v>
       </c>
       <c r="E4" s="22" t="str">
         <f t="shared" si="4"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G4" s="23" t="str">
         <f>IF(F4&lt;&gt;"",CONCATENATE(A4,B4,C4,":",D4,E4),IF(F3&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Capturar excepciones&lt;/span&gt;: Algunas operaciones, como cambiar de directorio o eliminar archivos, pueden generar errores si la ruta no existe o no se tienen permisos.&lt;/li&gt;</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;calendar.pryear(year)&lt;/span&gt;: Imprime el calendario completo de un año en formato tabular.&lt;/li&gt;</v>
       </c>
       <c r="K4" s="22" t="str">
         <f t="shared" si="5"/>
@@ -13206,7 +13266,7 @@
         <v/>
       </c>
       <c r="I18" s="31" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K18" s="22" t="str">
         <f t="shared" si="5"/>
@@ -13289,7 +13349,7 @@
     </row>
     <row r="20" ht="15" spans="1:17">
       <c r="A20" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>2</v>
@@ -13299,10 +13359,10 @@
         <v/>
       </c>
       <c r="I20" s="32" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="L20" s="22" t="s">
         <v>2</v>
@@ -13314,23 +13374,23 @@
     </row>
     <row r="21" ht="15" spans="1:11">
       <c r="A21" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I21" s="32" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="7:7">
       <c r="G22" s="23" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G23" s="23" t="str">
         <f>A23</f>
@@ -13385,7 +13445,7 @@
         <v/>
       </c>
       <c r="P26" s="33" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="Q26" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P26,"&lt;/strong&gt;:")</f>
@@ -13408,7 +13468,7 @@
       </c>
       <c r="P27" s="28"/>
       <c r="Q27" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -13438,7 +13498,7 @@
         <v/>
       </c>
       <c r="P28" s="34" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Q28" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P28,"&lt;/li&gt; ")</f>
@@ -13472,7 +13532,7 @@
         <v/>
       </c>
       <c r="P29" s="34" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="Q29" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P29,"&lt;/li&gt; ")</f>
@@ -13507,7 +13567,7 @@
       </c>
       <c r="P30" s="30"/>
       <c r="Q30" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -13538,7 +13598,7 @@
       </c>
       <c r="P31" s="30"/>
       <c r="Q31" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -13569,7 +13629,7 @@
       </c>
       <c r="P32" s="30"/>
       <c r="Q32" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -13599,7 +13659,7 @@
         <v/>
       </c>
       <c r="P33" s="35" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="Q33" s="39" t="str">
         <f>P33</f>
@@ -13634,15 +13694,15 @@
       </c>
       <c r="P34" s="30"/>
       <c r="Q34" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" ht="15" spans="1:17">
       <c r="A35" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G35" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13650,22 +13710,22 @@
       </c>
       <c r="P35" s="36"/>
       <c r="Q35" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:17">
       <c r="A36" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G36" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P36" s="33" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="Q36" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P36,"&lt;/strong&gt;:")</f>
@@ -13674,10 +13734,10 @@
     </row>
     <row r="37" s="22" customFormat="1" spans="1:17">
       <c r="A37" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G37" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13685,22 +13745,22 @@
       </c>
       <c r="P37" s="28"/>
       <c r="Q37" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G38" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P38" s="34" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="Q38" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P38,"&lt;/li&gt; ")</f>
@@ -13709,17 +13769,17 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G39" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P39" s="34" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Q39" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P39,"&lt;/li&gt; ")</f>
@@ -13728,10 +13788,10 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G40" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13739,15 +13799,15 @@
       </c>
       <c r="P40" s="30"/>
       <c r="Q40" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G41" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13755,15 +13815,15 @@
       </c>
       <c r="P41" s="30"/>
       <c r="Q41" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G42" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13771,22 +13831,22 @@
       </c>
       <c r="P42" s="30"/>
       <c r="Q42" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G43" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P43" s="37" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="Q43" s="39" t="str">
         <f>P43</f>
@@ -13795,10 +13855,10 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="22" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G44" s="23" t="str">
         <f t="shared" si="14"/>
@@ -13806,18 +13866,18 @@
       </c>
       <c r="P44" s="30"/>
       <c r="Q44" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" ht="15" spans="16:17">
       <c r="P45" s="36"/>
       <c r="Q45" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" ht="18" spans="16:17">
       <c r="P46" s="33" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Q46" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P46,"&lt;/strong&gt;:")</f>
@@ -13827,12 +13887,12 @@
     <row r="47" spans="16:17">
       <c r="P47" s="28"/>
       <c r="Q47" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="16:17">
       <c r="P48" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q48" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P48,"&lt;/li&gt; ")</f>
@@ -13841,7 +13901,7 @@
     </row>
     <row r="49" spans="16:17">
       <c r="P49" s="34" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="Q49" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P49,"&lt;/li&gt; ")</f>
@@ -13851,12 +13911,12 @@
     <row r="50" ht="15" spans="16:17">
       <c r="P50" s="30"/>
       <c r="Q50" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F51" s="26"/>
       <c r="G51" s="27" t="str">
@@ -13865,7 +13925,7 @@
       </c>
       <c r="P51" s="30"/>
       <c r="Q51" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -13888,7 +13948,7 @@
       </c>
       <c r="P52" s="30"/>
       <c r="Q52" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -13907,7 +13967,7 @@
       <c r="F53" s="28"/>
       <c r="G53" s="29"/>
       <c r="P53" s="35" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="Q53" s="39" t="str">
         <f>P53</f>
@@ -13939,7 +13999,7 @@
       <c r="G54" s="29"/>
       <c r="P54" s="30"/>
       <c r="Q54" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" ht="15" spans="1:17">
@@ -13967,7 +14027,7 @@
       <c r="G55" s="29"/>
       <c r="P55" s="36"/>
       <c r="Q55" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:17">
@@ -13994,7 +14054,7 @@
       <c r="F56" s="30"/>
       <c r="G56" s="29"/>
       <c r="P56" s="33" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P56,"&lt;/strong&gt;:")</f>
@@ -14026,7 +14086,7 @@
       <c r="G57" s="29"/>
       <c r="P57" s="28"/>
       <c r="Q57" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -14053,7 +14113,7 @@
       <c r="F58" s="30"/>
       <c r="G58" s="29"/>
       <c r="P58" s="34" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P58,"&lt;/li&gt; ")</f>
@@ -14084,7 +14144,7 @@
       <c r="F59" s="30"/>
       <c r="G59" s="29"/>
       <c r="P59" s="34" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P59,"&lt;/li&gt; ")</f>
@@ -14116,7 +14176,7 @@
       <c r="G60" s="29"/>
       <c r="P60" s="30"/>
       <c r="Q60" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -14144,7 +14204,7 @@
       <c r="G61" s="29"/>
       <c r="P61" s="30"/>
       <c r="Q61" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -14172,20 +14232,20 @@
       <c r="G62" s="29"/>
       <c r="P62" s="30"/>
       <c r="Q62" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F63" s="30"/>
       <c r="G63" s="29"/>
       <c r="P63" s="35" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="Q63" s="39" t="str">
         <f>P63</f>
@@ -14197,7 +14257,7 @@
       <c r="G64" s="29"/>
       <c r="P64" s="30"/>
       <c r="Q64" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" ht="15" spans="6:17">
@@ -14205,14 +14265,14 @@
       <c r="G65" s="29"/>
       <c r="P65" s="36"/>
       <c r="Q65" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" ht="18" spans="6:17">
       <c r="F66" s="30"/>
       <c r="G66" s="29"/>
       <c r="P66" s="33" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q66" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P66,"&lt;/strong&gt;:")</f>
@@ -14224,12 +14284,12 @@
       <c r="G67" s="41"/>
       <c r="P67" s="28"/>
       <c r="Q67" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="16:17">
       <c r="P68" s="34" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="Q68" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P68,"&lt;/li&gt; ")</f>
@@ -14238,7 +14298,7 @@
     </row>
     <row r="69" spans="16:17">
       <c r="P69" s="34" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="Q69" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P69,"&lt;/li&gt; ")</f>
@@ -14248,24 +14308,24 @@
     <row r="70" spans="16:17">
       <c r="P70" s="30"/>
       <c r="Q70" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="16:17">
       <c r="P71" s="30"/>
       <c r="Q71" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="16:17">
       <c r="P72" s="30"/>
       <c r="Q72" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" ht="28.5" spans="16:17">
       <c r="P73" s="37" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="Q73" s="39" t="str">
         <f>P73</f>
@@ -14276,18 +14336,18 @@
     <row r="74" spans="16:17">
       <c r="P74" s="30"/>
       <c r="Q74" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" ht="15" spans="16:17">
       <c r="P75" s="36"/>
       <c r="Q75" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" ht="18" spans="16:17">
       <c r="P76" s="33" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="Q76" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P76,"&lt;/strong&gt;:")</f>
@@ -14297,12 +14357,12 @@
     <row r="77" spans="16:17">
       <c r="P77" s="28"/>
       <c r="Q77" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="16:17">
       <c r="P78" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q78" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P78,"&lt;/li&gt; ")</f>
@@ -14311,7 +14371,7 @@
     </row>
     <row r="79" spans="16:17">
       <c r="P79" s="34" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="Q79" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P79,"&lt;/li&gt; ")</f>
@@ -14321,24 +14381,24 @@
     <row r="80" spans="16:17">
       <c r="P80" s="30"/>
       <c r="Q80" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="81" spans="16:17">
       <c r="P81" s="30"/>
       <c r="Q81" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="16:17">
       <c r="P82" s="30"/>
       <c r="Q82" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="16:17">
       <c r="P83" s="35" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="Q83" s="39" t="str">
         <f>P83</f>
@@ -14348,18 +14408,18 @@
     <row r="84" spans="16:17">
       <c r="P84" s="30"/>
       <c r="Q84" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" ht="15" spans="16:17">
       <c r="P85" s="36"/>
       <c r="Q85" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" ht="18" spans="16:17">
       <c r="P86" s="33" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="Q86" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P86,"&lt;/strong&gt;:")</f>
@@ -14369,12 +14429,12 @@
     <row r="87" spans="16:17">
       <c r="P87" s="28"/>
       <c r="Q87" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="16:17">
       <c r="P88" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q88" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P88,"&lt;/li&gt; ")</f>
@@ -14383,7 +14443,7 @@
     </row>
     <row r="89" spans="16:17">
       <c r="P89" s="34" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="Q89" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P89,"&lt;/li&gt; ")</f>
@@ -14393,24 +14453,24 @@
     <row r="90" spans="16:17">
       <c r="P90" s="30"/>
       <c r="Q90" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="16:17">
       <c r="P91" s="30"/>
       <c r="Q91" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="16:17">
       <c r="P92" s="30"/>
       <c r="Q92" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" ht="28.5" spans="16:17">
       <c r="P93" s="37" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="Q93" s="39" t="str">
         <f>P93</f>
@@ -14421,18 +14481,18 @@
     <row r="94" spans="16:17">
       <c r="P94" s="30"/>
       <c r="Q94" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" ht="15" spans="16:17">
       <c r="P95" s="36"/>
       <c r="Q95" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" ht="18" spans="16:17">
       <c r="P96" s="33" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="Q96" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P96,"&lt;/strong&gt;:")</f>
@@ -14442,12 +14502,12 @@
     <row r="97" spans="16:17">
       <c r="P97" s="28"/>
       <c r="Q97" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="98" spans="16:17">
       <c r="P98" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q98" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P98,"&lt;/li&gt; ")</f>
@@ -14456,7 +14516,7 @@
     </row>
     <row r="99" spans="16:17">
       <c r="P99" s="34" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="Q99" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P99,"&lt;/li&gt; ")</f>
@@ -14466,24 +14526,24 @@
     <row r="100" spans="16:17">
       <c r="P100" s="30"/>
       <c r="Q100" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="16:17">
       <c r="P101" s="30"/>
       <c r="Q101" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="16:17">
       <c r="P102" s="30"/>
       <c r="Q102" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="16:17">
       <c r="P103" s="35" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="Q103" s="39" t="str">
         <f>P103</f>
@@ -14493,18 +14553,18 @@
     <row r="104" spans="16:17">
       <c r="P104" s="30"/>
       <c r="Q104" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" ht="15" spans="16:17">
       <c r="P105" s="36"/>
       <c r="Q105" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" ht="18" spans="16:17">
       <c r="P106" s="33" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="Q106" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P106,"&lt;/strong&gt;:")</f>
@@ -14514,12 +14574,12 @@
     <row r="107" spans="16:17">
       <c r="P107" s="28"/>
       <c r="Q107" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="108" spans="16:17">
       <c r="P108" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q108" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P108,"&lt;/li&gt; ")</f>
@@ -14528,7 +14588,7 @@
     </row>
     <row r="109" spans="16:17">
       <c r="P109" s="34" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="Q109" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P109,"&lt;/li&gt; ")</f>
@@ -14538,24 +14598,24 @@
     <row r="110" spans="16:17">
       <c r="P110" s="30"/>
       <c r="Q110" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="16:17">
       <c r="P111" s="30"/>
       <c r="Q111" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="16:17">
       <c r="P112" s="30"/>
       <c r="Q112" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="113" spans="16:17">
       <c r="P113" s="35" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="Q113" s="39" t="str">
         <f>P113</f>
@@ -14565,18 +14625,18 @@
     <row r="114" spans="16:17">
       <c r="P114" s="30"/>
       <c r="Q114" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" ht="15" spans="16:17">
       <c r="P115" s="36"/>
       <c r="Q115" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" ht="18" spans="16:17">
       <c r="P116" s="33" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="Q116" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P116,"&lt;/strong&gt;:")</f>
@@ -14586,12 +14646,12 @@
     <row r="117" spans="16:17">
       <c r="P117" s="28"/>
       <c r="Q117" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="118" spans="16:17">
       <c r="P118" s="34" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="Q118" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P118,"&lt;/li&gt; ")</f>
@@ -14600,7 +14660,7 @@
     </row>
     <row r="119" spans="16:17">
       <c r="P119" s="34" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="Q119" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P119,"&lt;/li&gt; ")</f>
@@ -14610,24 +14670,24 @@
     <row r="120" spans="16:17">
       <c r="P120" s="30"/>
       <c r="Q120" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="16:17">
       <c r="P121" s="30"/>
       <c r="Q121" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="16:17">
       <c r="P122" s="30"/>
       <c r="Q122" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="123" ht="28.5" spans="16:17">
       <c r="P123" s="37" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="Q123" s="39" t="str">
         <f>P123</f>
@@ -14638,18 +14698,18 @@
     <row r="124" spans="16:17">
       <c r="P124" s="30"/>
       <c r="Q124" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" ht="15" spans="16:17">
       <c r="P125" s="36"/>
       <c r="Q125" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" ht="18" spans="16:17">
       <c r="P126" s="33" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="Q126" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P126,"&lt;/strong&gt;:")</f>
@@ -14659,12 +14719,12 @@
     <row r="127" spans="16:17">
       <c r="P127" s="28"/>
       <c r="Q127" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="128" spans="16:17">
       <c r="P128" s="34" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="Q128" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P128,"&lt;/li&gt; ")</f>
@@ -14673,7 +14733,7 @@
     </row>
     <row r="129" spans="16:17">
       <c r="P129" s="34" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="Q129" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P129,"&lt;/li&gt; ")</f>
@@ -14683,24 +14743,24 @@
     <row r="130" spans="16:17">
       <c r="P130" s="30"/>
       <c r="Q130" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131" spans="16:17">
       <c r="P131" s="30"/>
       <c r="Q131" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" spans="16:17">
       <c r="P132" s="30"/>
       <c r="Q132" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="133" ht="28.5" spans="16:17">
       <c r="P133" s="37" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Q133" s="39" t="str">
         <f>P133</f>
@@ -14711,18 +14771,18 @@
     <row r="134" spans="16:17">
       <c r="P134" s="30"/>
       <c r="Q134" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" ht="15" spans="16:17">
       <c r="P135" s="36"/>
       <c r="Q135" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" ht="18" spans="16:17">
       <c r="P136" s="33" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="Q136" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P136,"&lt;/strong&gt;:")</f>
@@ -14732,12 +14792,12 @@
     <row r="137" spans="16:17">
       <c r="P137" s="28"/>
       <c r="Q137" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" spans="16:17">
       <c r="P138" s="34" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="Q138" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P138,"&lt;/li&gt; ")</f>
@@ -14746,7 +14806,7 @@
     </row>
     <row r="139" spans="16:17">
       <c r="P139" s="34" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="Q139" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P139,"&lt;/li&gt; ")</f>
@@ -14756,24 +14816,24 @@
     <row r="140" spans="16:17">
       <c r="P140" s="30"/>
       <c r="Q140" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="16:17">
       <c r="P141" s="30"/>
       <c r="Q141" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="16:17">
       <c r="P142" s="30"/>
       <c r="Q142" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" ht="28.5" spans="16:17">
       <c r="P143" s="37" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="Q143" s="39" t="str">
         <f>P143</f>
@@ -14784,18 +14844,18 @@
     <row r="144" spans="16:17">
       <c r="P144" s="30"/>
       <c r="Q144" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" ht="15" spans="16:17">
       <c r="P145" s="36"/>
       <c r="Q145" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" ht="18" spans="16:17">
       <c r="P146" s="33" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="Q146" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P146,"&lt;/strong&gt;:")</f>
@@ -14805,12 +14865,12 @@
     <row r="147" spans="16:17">
       <c r="P147" s="28"/>
       <c r="Q147" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="148" spans="16:17">
       <c r="P148" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q148" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P148,"&lt;/li&gt; ")</f>
@@ -14819,7 +14879,7 @@
     </row>
     <row r="149" spans="16:17">
       <c r="P149" s="34" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="Q149" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P149,"&lt;/li&gt; ")</f>
@@ -14829,24 +14889,24 @@
     <row r="150" spans="16:17">
       <c r="P150" s="30"/>
       <c r="Q150" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="151" spans="16:17">
       <c r="P151" s="30"/>
       <c r="Q151" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="152" spans="16:17">
       <c r="P152" s="30"/>
       <c r="Q152" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="153" spans="16:17">
       <c r="P153" s="35" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="Q153" s="39" t="str">
         <f>P153</f>
@@ -14856,18 +14916,18 @@
     <row r="154" spans="16:17">
       <c r="P154" s="30"/>
       <c r="Q154" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" ht="15" spans="16:17">
       <c r="P155" s="36"/>
       <c r="Q155" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="156" ht="18" spans="16:17">
       <c r="P156" s="33" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="Q156" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P156,"&lt;/strong&gt;:")</f>
@@ -14877,12 +14937,12 @@
     <row r="157" spans="16:17">
       <c r="P157" s="28"/>
       <c r="Q157" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="158" spans="16:17">
       <c r="P158" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q158" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P158,"&lt;/li&gt; ")</f>
@@ -14891,7 +14951,7 @@
     </row>
     <row r="159" spans="16:17">
       <c r="P159" s="34" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="Q159" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P159,"&lt;/li&gt; ")</f>
@@ -14901,24 +14961,24 @@
     <row r="160" spans="16:17">
       <c r="P160" s="30"/>
       <c r="Q160" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="16:17">
       <c r="P161" s="30"/>
       <c r="Q161" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="162" spans="16:17">
       <c r="P162" s="30"/>
       <c r="Q162" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="163" spans="16:17">
       <c r="P163" s="35" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Q163" s="39" t="str">
         <f>P163</f>
@@ -14928,18 +14988,18 @@
     <row r="164" spans="16:17">
       <c r="P164" s="30"/>
       <c r="Q164" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="165" ht="15" spans="16:17">
       <c r="P165" s="36"/>
       <c r="Q165" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="166" ht="18" spans="16:17">
       <c r="P166" s="33" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="Q166" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P166,"&lt;/strong&gt;:")</f>
@@ -14949,12 +15009,12 @@
     <row r="167" spans="16:17">
       <c r="P167" s="28"/>
       <c r="Q167" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="168" spans="16:17">
       <c r="P168" s="34" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="Q168" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P168,"&lt;/li&gt; ")</f>
@@ -14963,7 +15023,7 @@
     </row>
     <row r="169" spans="16:17">
       <c r="P169" s="34" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="Q169" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P169,"&lt;/li&gt; ")</f>
@@ -14973,24 +15033,24 @@
     <row r="170" spans="16:17">
       <c r="P170" s="30"/>
       <c r="Q170" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="16:17">
       <c r="P171" s="30"/>
       <c r="Q171" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="16:17">
       <c r="P172" s="30"/>
       <c r="Q172" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="173" ht="42.75" spans="16:17">
       <c r="P173" s="37" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="Q173" s="39" t="str">
         <f>P173</f>
@@ -15002,18 +15062,18 @@
     <row r="174" spans="16:17">
       <c r="P174" s="30"/>
       <c r="Q174" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" ht="15" spans="16:17">
       <c r="P175" s="36"/>
       <c r="Q175" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="176" ht="18" spans="16:17">
       <c r="P176" s="33" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="Q176" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P176,"&lt;/strong&gt;:")</f>
@@ -15023,12 +15083,12 @@
     <row r="177" spans="16:17">
       <c r="P177" s="28"/>
       <c r="Q177" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="16:17">
       <c r="P178" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q178" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P178,"&lt;/li&gt; ")</f>
@@ -15037,7 +15097,7 @@
     </row>
     <row r="179" spans="16:17">
       <c r="P179" s="34" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="Q179" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P179,"&lt;/li&gt; ")</f>
@@ -15047,24 +15107,24 @@
     <row r="180" spans="16:17">
       <c r="P180" s="30"/>
       <c r="Q180" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="16:17">
       <c r="P181" s="30"/>
       <c r="Q181" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="16:17">
       <c r="P182" s="30"/>
       <c r="Q182" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" spans="16:17">
       <c r="P183" s="35" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="Q183" s="39" t="str">
         <f>P183</f>
@@ -15074,18 +15134,18 @@
     <row r="184" spans="16:17">
       <c r="P184" s="30"/>
       <c r="Q184" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185" ht="15" spans="16:17">
       <c r="P185" s="36"/>
       <c r="Q185" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="186" ht="18" spans="16:17">
       <c r="P186" s="33" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="Q186" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P186,"&lt;/strong&gt;:")</f>
@@ -15095,12 +15155,12 @@
     <row r="187" spans="16:17">
       <c r="P187" s="28"/>
       <c r="Q187" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="188" spans="16:17">
       <c r="P188" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q188" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P188,"&lt;/li&gt; ")</f>
@@ -15109,7 +15169,7 @@
     </row>
     <row r="189" spans="16:17">
       <c r="P189" s="34" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="Q189" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P189,"&lt;/li&gt; ")</f>
@@ -15119,24 +15179,24 @@
     <row r="190" spans="16:17">
       <c r="P190" s="30"/>
       <c r="Q190" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="16:17">
       <c r="P191" s="30"/>
       <c r="Q191" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="192" spans="16:17">
       <c r="P192" s="30"/>
       <c r="Q192" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="193" spans="16:17">
       <c r="P193" s="35" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="Q193" s="39" t="str">
         <f>P193</f>
@@ -15146,18 +15206,18 @@
     <row r="194" spans="16:17">
       <c r="P194" s="30"/>
       <c r="Q194" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="195" ht="15" spans="16:17">
       <c r="P195" s="36"/>
       <c r="Q195" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="196" ht="18" spans="16:17">
       <c r="P196" s="33" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="Q196" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P196,"&lt;/strong&gt;:")</f>
@@ -15167,12 +15227,12 @@
     <row r="197" spans="16:17">
       <c r="P197" s="28"/>
       <c r="Q197" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="198" spans="16:17">
       <c r="P198" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q198" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P198,"&lt;/li&gt; ")</f>
@@ -15181,7 +15241,7 @@
     </row>
     <row r="199" spans="16:17">
       <c r="P199" s="34" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="Q199" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P199,"&lt;/li&gt; ")</f>
@@ -15191,24 +15251,24 @@
     <row r="200" spans="16:17">
       <c r="P200" s="30"/>
       <c r="Q200" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="16:17">
       <c r="P201" s="30"/>
       <c r="Q201" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="16:17">
       <c r="P202" s="30"/>
       <c r="Q202" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="16:17">
       <c r="P203" s="35" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="Q203" s="39" t="str">
         <f>P203</f>
@@ -15218,18 +15278,18 @@
     <row r="204" spans="16:17">
       <c r="P204" s="30"/>
       <c r="Q204" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="205" ht="15" spans="16:17">
       <c r="P205" s="36"/>
       <c r="Q205" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="206" ht="18" spans="16:17">
       <c r="P206" s="33" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Q206" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P206,"&lt;/strong&gt;:")</f>
@@ -15239,12 +15299,12 @@
     <row r="207" spans="16:17">
       <c r="P207" s="28"/>
       <c r="Q207" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="208" spans="16:17">
       <c r="P208" s="34" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="Q208" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P208,"&lt;/li&gt; ")</f>
@@ -15253,7 +15313,7 @@
     </row>
     <row r="209" spans="16:17">
       <c r="P209" s="34" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Q209" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P209,"&lt;/li&gt; ")</f>
@@ -15263,24 +15323,24 @@
     <row r="210" spans="16:17">
       <c r="P210" s="30"/>
       <c r="Q210" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="16:17">
       <c r="P211" s="30"/>
       <c r="Q211" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="212" spans="16:17">
       <c r="P212" s="30"/>
       <c r="Q212" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="16:17">
       <c r="P213" s="35" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="Q213" s="39" t="str">
         <f>P213</f>
@@ -15290,18 +15350,18 @@
     <row r="214" spans="16:17">
       <c r="P214" s="30"/>
       <c r="Q214" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="215" ht="15" spans="16:17">
       <c r="P215" s="36"/>
       <c r="Q215" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" ht="18" spans="16:17">
       <c r="P216" s="33" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="Q216" s="38" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;",P216,"&lt;/strong&gt;:")</f>
@@ -15311,12 +15371,12 @@
     <row r="217" spans="16:17">
       <c r="P217" s="28"/>
       <c r="Q217" s="39" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="218" spans="16:17">
       <c r="P218" s="34" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Q218" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Ubicación&lt;/strong&gt;: ",P218,"&lt;/li&gt; ")</f>
@@ -15325,7 +15385,7 @@
     </row>
     <row r="219" spans="16:17">
       <c r="P219" s="34" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="Q219" s="39" t="str">
         <f>CONCATENATE("&lt;li&gt;&lt;strong&gt;Descripción&lt;/strong&gt;: ",P219,"&lt;/li&gt; ")</f>
@@ -15335,24 +15395,24 @@
     <row r="220" spans="16:17">
       <c r="P220" s="30"/>
       <c r="Q220" s="39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="221" spans="16:17">
       <c r="P221" s="30"/>
       <c r="Q221" s="39" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="222" spans="16:17">
       <c r="P222" s="30"/>
       <c r="Q222" s="39" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="223" ht="71.25" spans="16:17">
       <c r="P223" s="37" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q223" s="39" t="str">
         <f>P223</f>
@@ -15366,13 +15426,13 @@
     <row r="224" spans="16:17">
       <c r="P224" s="30"/>
       <c r="Q224" s="39" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" ht="15" spans="16:17">
       <c r="P225" s="36"/>
       <c r="Q225" s="40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -15455,7 +15515,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="21" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -15478,30 +15538,30 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:1">
       <c r="A4" s="5" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B5" s="10"/>
     </row>
@@ -15511,7 +15571,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io&lt;/loc&gt;</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15530,7 +15590,7 @@
         <v>&lt;changefreq&gt;weekly&lt;/changefreq&gt;</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15539,24 +15599,24 @@
         <v>&lt;priority&gt;1.0&lt;/priority&gt;</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B10" s="14"/>
     </row>
     <row r="11" ht="15.75" spans="1:2">
       <c r="A11" s="15" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B11" s="15"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="16"/>
@@ -15588,7 +15648,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C15" s="16"/>
     </row>
@@ -15598,20 +15658,20 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C16" s="16"/>
     </row>
     <row r="17" ht="15.75" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="16"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="16"/>
@@ -15622,7 +15682,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io/git.html&lt;/loc&gt;</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C19" s="16"/>
     </row>
@@ -15643,7 +15703,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C21" s="16"/>
     </row>
@@ -15653,20 +15713,20 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C22" s="16"/>
     </row>
     <row r="23" ht="15.75" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="16"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="16"/>
@@ -15677,7 +15737,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io/javascript.html&lt;/loc&gt;</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C25" s="16"/>
     </row>
@@ -15698,7 +15758,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C27" s="16"/>
     </row>
@@ -15708,20 +15768,20 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C28" s="16"/>
     </row>
     <row r="29" ht="15.75" spans="1:3">
       <c r="A29" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="16"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="16"/>
@@ -15732,7 +15792,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io/photoshop.html&lt;/loc&gt;</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C31" s="16"/>
     </row>
@@ -15753,7 +15813,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C33" s="16"/>
     </row>
@@ -15763,20 +15823,20 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C34" s="16"/>
     </row>
     <row r="35" ht="15.75" spans="1:3">
       <c r="A35" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="16"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="16"/>
@@ -15808,7 +15868,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C39" s="16"/>
     </row>
@@ -15818,20 +15878,20 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C40" s="16"/>
     </row>
     <row r="41" ht="15.75" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="16"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B42" s="10"/>
       <c r="C42" s="16"/>
@@ -15846,7 +15906,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3.html</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15866,7 +15926,7 @@
         <v>&lt;changefreq&gt;monthly&lt;/changefreq&gt;</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C45" s="16"/>
     </row>
@@ -15876,26 +15936,26 @@
         <v>&lt;priority&gt;0.7&lt;/priority&gt;</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C46" s="16"/>
     </row>
     <row r="47" ht="15.75" spans="1:3">
       <c r="A47" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="16"/>
     </row>
     <row r="48" ht="15.75" spans="1:2">
       <c r="A48" s="15" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B48" s="15"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B49" s="10"/>
       <c r="C49" s="16"/>
@@ -15906,7 +15966,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io/bootstrap@instalacion_de_bootstrap_v5_con_npm_y_parcel.html&lt;/loc&gt;</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C50" s="16"/>
     </row>
@@ -15927,7 +15987,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C52" s="16"/>
     </row>
@@ -15937,20 +15997,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C53" s="16"/>
     </row>
     <row r="54" ht="15.75" spans="1:3">
       <c r="A54" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="16"/>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="16"/>
@@ -15961,7 +16021,7 @@
         <v>&lt;loc&gt;https://eduardoherreraf.github.io/bootstrap@instalacion_de_bootstrap_v5_con_npm_y_vite.html&lt;/loc&gt;</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C56" s="16"/>
     </row>
@@ -15982,7 +16042,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C58" s="16"/>
     </row>
@@ -15992,27 +16052,27 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C59" s="16"/>
     </row>
     <row r="60" ht="15.75" spans="1:3">
       <c r="A60" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="16"/>
     </row>
     <row r="61" ht="15.75" spans="1:3">
       <c r="A61" s="15" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="16"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B62" s="10"/>
     </row>
@@ -16026,7 +16086,7 @@
         <v>https://eduardoherreraf.github.io/git@configuracion_inicial_GIT.html</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -16046,7 +16106,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C65" s="16"/>
     </row>
@@ -16056,20 +16116,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C66" s="16"/>
     </row>
     <row r="67" ht="15.75" spans="1:3">
       <c r="A67" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="16"/>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="16"/>
@@ -16084,7 +16144,7 @@
         <v>https://eduardoherreraf.github.io/git@introduccion_de_git_para_windows.html</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -16104,7 +16164,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C71" s="16"/>
     </row>
@@ -16114,20 +16174,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C72" s="16"/>
     </row>
     <row r="73" ht="15.75" spans="1:3">
       <c r="A73" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="16"/>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B74" s="10"/>
       <c r="C74" s="16"/>
@@ -16142,7 +16202,7 @@
         <v>https://eduardoherreraf.github.io/git@comandos_basicos_de_consola-Terminal_CLI_para_windows.html</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -16162,7 +16222,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C77" s="16"/>
     </row>
@@ -16172,20 +16232,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C78" s="16"/>
     </row>
     <row r="79" ht="15.75" spans="1:3">
       <c r="A79" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B79" s="14"/>
       <c r="C79" s="16"/>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B80" s="10"/>
       <c r="C80" s="16"/>
@@ -16200,7 +16260,7 @@
         <v>https://eduardoherreraf.github.io/git@como_eliminar_el_ultimo_commit_de_git.html</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -16220,7 +16280,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C83" s="16"/>
     </row>
@@ -16230,27 +16290,27 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C84" s="16"/>
     </row>
     <row r="85" ht="15.75" spans="1:3">
       <c r="A85" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B85" s="14"/>
       <c r="C85" s="16"/>
     </row>
     <row r="86" ht="15.75" spans="1:3">
       <c r="A86" s="15" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="16"/>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="16"/>
@@ -16265,7 +16325,7 @@
         <v>https://eduardoherreraf.github.io/js@como_ejecutar_un_codigo_javascript.html</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -16285,7 +16345,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C90" s="16"/>
     </row>
@@ -16295,20 +16355,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C91" s="16"/>
     </row>
     <row r="92" ht="15.75" spans="1:3">
       <c r="A92" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B92" s="14"/>
       <c r="C92" s="16"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B93" s="10"/>
       <c r="C93" s="16"/>
@@ -16323,7 +16383,7 @@
         <v>https://eduardoherreraf.github.io/js@configurar_el_entorno_de_trabajo_Javascript.html</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -16343,7 +16403,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C96" s="16"/>
     </row>
@@ -16353,27 +16413,27 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C97" s="16"/>
     </row>
     <row r="98" ht="15.75" spans="1:3">
       <c r="A98" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B98" s="14"/>
       <c r="C98" s="16"/>
     </row>
     <row r="99" ht="15.75" spans="1:3">
       <c r="A99" s="15" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="16"/>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="16"/>
@@ -16388,7 +16448,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@metadata_y_exportacion.html</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -16408,7 +16468,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C103" s="16"/>
     </row>
@@ -16418,20 +16478,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C104" s="16"/>
     </row>
     <row r="105" ht="15.75" spans="1:3">
       <c r="A105" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B105" s="14"/>
       <c r="C105" s="16"/>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B106" s="10"/>
       <c r="C106" s="16"/>
@@ -16446,7 +16506,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@filtros_licuar.html</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -16466,7 +16526,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C109" s="16"/>
     </row>
@@ -16476,20 +16536,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C110" s="16"/>
     </row>
     <row r="111" ht="15.75" spans="1:3">
       <c r="A111" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B111" s="14"/>
       <c r="C111" s="16"/>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B112" s="10"/>
       <c r="C112" s="16"/>
@@ -16504,7 +16564,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@filtros_neurales.html</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -16524,7 +16584,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C115" s="16"/>
     </row>
@@ -16534,20 +16594,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C116" s="16"/>
     </row>
     <row r="117" ht="15.75" spans="1:3">
       <c r="A117" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B117" s="14"/>
       <c r="C117" s="16"/>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B118" s="10"/>
       <c r="C118" s="16"/>
@@ -16562,7 +16622,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@filtros.html</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -16582,7 +16642,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C121" s="16"/>
     </row>
@@ -16592,20 +16652,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C122" s="16"/>
     </row>
     <row r="123" ht="15.75" spans="1:3">
       <c r="A123" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B123" s="14"/>
       <c r="C123" s="16"/>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B124" s="10"/>
       <c r="C124" s="16"/>
@@ -16620,7 +16680,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@formas_y_capas.html</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -16640,7 +16700,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C127" s="16"/>
     </row>
@@ -16650,20 +16710,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C128" s="16"/>
     </row>
     <row r="129" ht="15.75" spans="1:3">
       <c r="A129" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B129" s="14"/>
       <c r="C129" s="16"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B130" s="10"/>
       <c r="C130" s="16"/>
@@ -16678,7 +16738,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@textos.html</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -16698,7 +16758,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C133" s="16"/>
     </row>
@@ -16708,20 +16768,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C134" s="16"/>
     </row>
     <row r="135" ht="15.75" spans="1:3">
       <c r="A135" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B135" s="14"/>
       <c r="C135" s="16"/>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B136" s="10"/>
       <c r="C136" s="16"/>
@@ -16736,7 +16796,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@color_y_degradados.html</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -16756,7 +16816,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C139" s="16"/>
     </row>
@@ -16766,20 +16826,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C140" s="16"/>
     </row>
     <row r="141" ht="15.75" spans="1:3">
       <c r="A141" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B141" s="14"/>
       <c r="C141" s="16"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B142" s="10"/>
       <c r="C142" s="16"/>
@@ -16794,7 +16854,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@uso_de_pinceles.html</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -16814,7 +16874,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C145" s="16"/>
     </row>
@@ -16824,20 +16884,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C146" s="16"/>
     </row>
     <row r="147" ht="15.75" spans="1:3">
       <c r="A147" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B147" s="14"/>
       <c r="C147" s="16"/>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B148" s="10"/>
       <c r="C148" s="16"/>
@@ -16852,7 +16912,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@agregar_y_quitar_objetos.html</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -16872,7 +16932,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C151" s="16"/>
     </row>
@@ -16882,20 +16942,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C152" s="16"/>
     </row>
     <row r="153" ht="15.75" spans="1:3">
       <c r="A153" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B153" s="14"/>
       <c r="C153" s="16"/>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B154" s="10"/>
       <c r="C154" s="16"/>
@@ -16910,7 +16970,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@herramientas_de_seleccion.html</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -16930,7 +16990,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C157" s="16"/>
     </row>
@@ -16940,20 +17000,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C158" s="16"/>
     </row>
     <row r="159" ht="15.75" spans="1:3">
       <c r="A159" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B159" s="14"/>
       <c r="C159" s="16"/>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B160" s="10"/>
       <c r="C160" s="16"/>
@@ -16968,7 +17028,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@ajuste_tono_brillo_y_saturacion.html</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -16988,7 +17048,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C163" s="16"/>
     </row>
@@ -16998,20 +17058,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C164" s="16"/>
     </row>
     <row r="165" ht="15.75" spans="1:3">
       <c r="A165" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B165" s="14"/>
       <c r="C165" s="16"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B166" s="10"/>
       <c r="C166" s="16"/>
@@ -17026,7 +17086,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@trabajo_con_capas.html</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -17046,7 +17106,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C169" s="16"/>
     </row>
@@ -17056,20 +17116,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C170" s="16"/>
     </row>
     <row r="171" ht="15.75" spans="1:3">
       <c r="A171" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B171" s="14"/>
       <c r="C171" s="16"/>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B172" s="10"/>
       <c r="C172" s="16"/>
@@ -17084,7 +17144,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@ajuste_lienzo_resolucion.html</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -17104,7 +17164,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C175" s="16"/>
     </row>
@@ -17114,20 +17174,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C176" s="16"/>
     </row>
     <row r="177" ht="15.75" spans="1:3">
       <c r="A177" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B177" s="14"/>
       <c r="C177" s="16"/>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B178" s="10"/>
       <c r="C178" s="16"/>
@@ -17142,7 +17202,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@compartir_y_editar_archivos.html</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -17162,7 +17222,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C181" s="16"/>
     </row>
@@ -17172,20 +17232,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C182" s="16"/>
     </row>
     <row r="183" ht="15.75" spans="1:3">
       <c r="A183" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B183" s="14"/>
       <c r="C183" s="16"/>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B184" s="10"/>
       <c r="C184" s="16"/>
@@ -17200,7 +17260,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@interfaz_y_area_de_trabajo.html</v>
       </c>
       <c r="C185" s="20" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -17220,7 +17280,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C187" s="16"/>
     </row>
@@ -17230,20 +17290,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C188" s="16"/>
     </row>
     <row r="189" ht="15.75" spans="1:3">
       <c r="A189" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B189" s="14"/>
       <c r="C189" s="16"/>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B190" s="10"/>
       <c r="C190" s="16"/>
@@ -17258,7 +17318,7 @@
         <v>https://eduardoherreraf.github.io/photoshop@comenzando_un_proyecto.html</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -17278,7 +17338,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C193" s="16"/>
     </row>
@@ -17288,27 +17348,27 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C194" s="16"/>
     </row>
     <row r="195" ht="15.75" spans="1:3">
       <c r="A195" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B195" s="14"/>
       <c r="C195" s="16"/>
     </row>
     <row r="196" ht="15.75" spans="1:3">
       <c r="A196" s="15" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B196" s="15"/>
       <c r="C196" s="16"/>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B197" s="10"/>
       <c r="C197" s="16"/>
@@ -17323,7 +17383,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas@como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C198" s="20" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -17343,7 +17403,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C200" s="16"/>
     </row>
@@ -17353,20 +17413,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C201" s="16"/>
     </row>
     <row r="202" ht="15.75" spans="1:3">
       <c r="A202" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B202" s="14"/>
       <c r="C202" s="16"/>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B203" s="10"/>
       <c r="C203" s="16"/>
@@ -17381,7 +17441,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas@como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C204" s="20" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -17401,7 +17461,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C206" s="16"/>
     </row>
@@ -17411,27 +17471,27 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C207" s="16"/>
     </row>
     <row r="208" ht="15.75" spans="1:3">
       <c r="A208" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B208" s="14"/>
       <c r="C208" s="16"/>
     </row>
     <row r="209" ht="15.75" spans="1:3">
       <c r="A209" s="15" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="16"/>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B210" s="10"/>
       <c r="C210" s="16"/>
@@ -17446,7 +17506,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@07_interaccion_con_el_usuario.html</v>
       </c>
       <c r="C211" s="20" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -17466,7 +17526,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C213" s="16"/>
     </row>
@@ -17476,20 +17536,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C214" s="16"/>
     </row>
     <row r="215" ht="15.75" spans="1:3">
       <c r="A215" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B215" s="14"/>
       <c r="C215" s="16"/>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B216" s="10"/>
       <c r="C216" s="16"/>
@@ -17504,7 +17564,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@06_comentarios.html</v>
       </c>
       <c r="C217" s="20" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -17524,7 +17584,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C219" s="16"/>
     </row>
@@ -17534,20 +17594,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C220" s="16"/>
     </row>
     <row r="221" ht="15.75" spans="1:3">
       <c r="A221" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B221" s="14"/>
       <c r="C221" s="16"/>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B222" s="10"/>
       <c r="C222" s="16"/>
@@ -17562,7 +17622,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@05_variables.html</v>
       </c>
       <c r="C223" s="20" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -17582,7 +17642,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B225" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C225" s="16"/>
     </row>
@@ -17592,20 +17652,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B226" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C226" s="16"/>
     </row>
     <row r="227" ht="15.75" spans="1:3">
       <c r="A227" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B227" s="14"/>
       <c r="C227" s="16"/>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B228" s="10"/>
       <c r="C228" s="16"/>
@@ -17620,7 +17680,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@04_operadores.html</v>
       </c>
       <c r="C229" s="20" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -17640,7 +17700,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C231" s="16"/>
     </row>
@@ -17650,20 +17710,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C232" s="16"/>
     </row>
     <row r="233" ht="15.75" spans="1:3">
       <c r="A233" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B233" s="14"/>
       <c r="C233" s="16"/>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B234" s="10"/>
       <c r="C234" s="16"/>
@@ -17678,7 +17738,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@03_literales.html</v>
       </c>
       <c r="C235" s="20" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -17698,7 +17758,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C237" s="16"/>
     </row>
@@ -17708,20 +17768,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C238" s="16"/>
     </row>
     <row r="239" ht="15.75" spans="1:3">
       <c r="A239" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B239" s="14"/>
       <c r="C239" s="16"/>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B240" s="10"/>
       <c r="C240" s="16"/>
@@ -17736,7 +17796,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@02_funcion_print.html</v>
       </c>
       <c r="C241" s="20" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -17756,7 +17816,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C243" s="16"/>
     </row>
@@ -17766,20 +17826,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C244" s="16"/>
     </row>
     <row r="245" ht="15.75" spans="1:3">
       <c r="A245" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B245" s="14"/>
       <c r="C245" s="16"/>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" s="9" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B246" s="10"/>
       <c r="C246" s="16"/>
@@ -17794,7 +17854,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3@01_introduccion.html</v>
       </c>
       <c r="C247" s="20" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -17814,7 +17874,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C249" s="16"/>
     </row>
@@ -17824,20 +17884,20 @@
         <v>&lt;priority&gt;0.6&lt;/priority&gt;</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C250" s="16"/>
     </row>
     <row r="251" ht="15.75" spans="1:3">
       <c r="A251" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B251" s="14"/>
       <c r="C251" s="16"/>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" s="5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C252" s="16"/>
     </row>
@@ -17973,13 +18033,13 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -17988,78 +18048,78 @@
         <v>82</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -18068,16 +18128,16 @@
         <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -18086,7 +18146,7 @@
         <v>90</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -18095,51 +18155,51 @@
         <v>91</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4"/>
       <c r="D20" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/src/Head.xlsx
+++ b/src/Head.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12450" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="316">
   <si>
     <t>Título</t>
   </si>
@@ -529,7 +529,10 @@
     <t xml:space="preserve">Título 1 </t>
   </si>
   <si>
-    <t>Eliminar el Historial de Git Localmente</t>
+    <t>Uso de PWD</t>
+  </si>
+  <si>
+    <t>Ejemplo de Salida</t>
   </si>
   <si>
     <t>id</t>
@@ -574,19 +577,19 @@
     <t>Título 2</t>
   </si>
   <si>
-    <t>Volver a Conectar con GitHub</t>
+    <t>Ejemplo de Salida de PWD</t>
   </si>
   <si>
     <t>Título 3</t>
   </si>
   <si>
-    <t>Agregar los Archivos y Hacer un Nuevo Commit</t>
+    <t>Casos de Uso de PWD</t>
   </si>
   <si>
     <t>Título 4</t>
   </si>
   <si>
-    <t>Forzar la Subida del Nuevo Historial a GitHub</t>
+    <t>Opciones útiles de PWD</t>
   </si>
   <si>
     <t>Título 5</t>
@@ -595,61 +598,64 @@
     <t>ff</t>
   </si>
   <si>
-    <t>Verificar que el Repositorio ha Sido Reiniciado</t>
+    <t>Ejemplos de uso ls</t>
   </si>
   <si>
     <t>Título 6</t>
   </si>
   <si>
-    <t>Recopilación de comandos utilizados</t>
+    <t>Ejemplos de uso cd</t>
   </si>
   <si>
     <t>Título 7</t>
   </si>
   <si>
-    <t>Crear un Commit Vacío</t>
+    <t>Ejemplos de Uso mkdir</t>
   </si>
   <si>
     <t>Título 8</t>
   </si>
   <si>
-    <t>Notas Importantes</t>
+    <t>Opciones Útiles de mkdir</t>
   </si>
   <si>
     <t>Título 9</t>
   </si>
   <si>
+    <t>Ejemplos de uso touch</t>
+  </si>
+  <si>
     <t>Título 10</t>
   </si>
   <si>
-    <t>Crear una Nueva Rama Vacía</t>
+    <t>Opciones Útiles de touch</t>
   </si>
   <si>
     <t>Título 11</t>
   </si>
   <si>
-    <t>Eliminar los Archivos Antiguos</t>
+    <t>Ejemplos de Uso rm</t>
   </si>
   <si>
-    <t>Agregar Nuevos Archivos</t>
+    <t>Consejos de Seguridad rm</t>
   </si>
   <si>
     <t>Título 12</t>
   </si>
   <si>
-    <t>Subir la Nueva Rama a GitHub</t>
+    <t>Alternativas a clear</t>
   </si>
   <si>
     <t>Título 13</t>
   </si>
   <si>
-    <t>Establecer la Nueva Rama como Principal</t>
+    <t>Ejemplos de uso history</t>
   </si>
   <si>
     <t>Título 14</t>
   </si>
   <si>
-    <t>Crear una nueva rama Vacía</t>
+    <t>Ubicación del historial</t>
   </si>
   <si>
     <t>Título 15</t>
@@ -682,16 +688,25 @@
     <t>&lt;ul&gt;</t>
   </si>
   <si>
-    <t>Ir al repositorio en GitHub:</t>
+    <t>Mostrar todo el historial de comandos: Muestra una lista numerada con todos los comandos ejecutados en la sesión actual.</t>
   </si>
   <si>
-    <t>Ir a la pestaña Settings.</t>
+    <t>Mostrar solo los últimos n comandos: Muestra los últimos 10 comandos ejecutados.</t>
   </si>
   <si>
-    <t>En la sección Branches, cambiar la rama principal a nueva-rama.</t>
+    <t>Buscar un comando en el historial: Muestra todas las líneas del historial que contienen el comando ls.</t>
   </si>
   <si>
-    <t>(Opcional) Eliminar la rama anterior si ya no se necesita.</t>
+    <t>Reejecutar un comando del historial: Se puede ejecutar un comando directamente usando su número en la lista:</t>
+  </si>
+  <si>
+    <t>Eliminar un comando específico del historial: Elimina el comando número 50 del historial.</t>
+  </si>
+  <si>
+    <t>Limpiar completamente el historial: Borra todos los comandos almacenados en el historial de la sesión actual.</t>
+  </si>
+  <si>
+    <t>Guardar el historial actual en el archivo de historial: Guarda los cambios en el archivo ~/.bash_history, donde se almacena el historial de comandos.</t>
   </si>
   <si>
     <t>&lt;li&gt;&lt;span class="fw-bold"&gt;</t>
@@ -700,7 +715,10 @@
     <t>&lt;li&gt;</t>
   </si>
   <si>
-    <t>Ir al repositorio en GitHub.</t>
+    <t>Si se usa sin argumentos, muestra todos los comandos almacenados en el historial.</t>
+  </si>
+  <si>
+    <t>n permite limitar la cantidad de comandos mostrados.</t>
   </si>
   <si>
     <t>&lt;script&gt;let tema = localStorage.getItem("theme") || "dark";window.onload = function () {if (tema === "dark") temaOscuro();if (tema === "light") temaClaro();};const cambiarTema = () =&gt; {const temaActual = localStorage.getItem("theme") || "dark";if (temaActual === "dark") {temaClaro();} else{temaOscuro();}};const temaOscuro = () =&gt; {document.querySelector("body").setAttribute("data-bs-theme", "dark");document.querySelector("#dl-icon").setAttribute("class","btn text-center d-flex bg-body-tertiary text-light");localStorage.setItem("theme", "dark");};const temaClaro = () =&gt; {document.querySelector("body").setAttribute("data-bs-theme", "light");document.querySelector("#dl-icon").setAttribute("class", "btn text-center d-flex bg-light text-dark");localStorage.setItem("theme", "light");};&lt;/script&gt;&lt;/html&gt;</t>
@@ -2077,7 +2095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2181,7 +2199,7 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2193,7 +2211,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
@@ -2577,7 +2594,7 @@
       <c r="B2" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="83" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="78" t="s">
@@ -21291,7 +21308,7 @@
         <f>LEFT('&lt;head&gt;'!C1,FIND("-",'&lt;head&gt;'!C1)-1)</f>
         <v>Reiniciar Repositorio en GIT / GITHUB </v>
       </c>
-      <c r="D8" s="92" t="s">
+      <c r="D8" s="91" t="s">
         <v>85</v>
       </c>
       <c r="E8" s="45" t="str">
@@ -21316,7 +21333,7 @@
       <c r="C10" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="93" t="s">
+      <c r="D10" s="92" t="s">
         <v>85</v>
       </c>
       <c r="E10" s="52" t="str">
@@ -21335,7 +21352,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="51"/>
-      <c r="D11" s="93" t="s">
+      <c r="D11" s="92" t="s">
         <v>85</v>
       </c>
       <c r="E11" s="52" t="str">
@@ -23183,7 +23200,7 @@
   <dimension ref="A1:O264"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
     <col min="6" max="6" width="27.75" customWidth="1"/>
     <col min="12" max="12" width="18.25" customWidth="1"/>
     <col min="14" max="14" width="27.75" customWidth="1"/>
@@ -23213,7 +23230,7 @@
       </c>
       <c r="F2" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D2," --&gt;")</f>
-        <v>&lt;!-- Eliminar el Historial de Git Localmente --&gt;</v>
+        <v>&lt;!-- Uso de PWD --&gt;</v>
       </c>
       <c r="G2" s="34"/>
       <c r="I2" s="31" t="s">
@@ -23221,23 +23238,25 @@
       </c>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
-      <c r="L2" s="33"/>
+      <c r="L2" s="33" t="s">
+        <v>142</v>
+      </c>
       <c r="M2" s="32"/>
       <c r="N2" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",L2," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Ejemplo de Salida --&gt;</v>
       </c>
       <c r="O2" s="34"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" t="str">
         <f>CONCATENATE(B3,D3,C3)</f>
@@ -23245,13 +23264,13 @@
       </c>
       <c r="G3" s="38"/>
       <c r="I3" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J3" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K3" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N3" t="str">
         <f>CONCATENATE(J3,L3,K3)</f>
@@ -23263,13 +23282,13 @@
       <c r="A4" s="35"/>
       <c r="F4" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D2,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Eliminar el Historial de Git Localmente&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Uso de PWD&lt;/h3&gt;</v>
       </c>
       <c r="G4" s="38"/>
       <c r="I4" s="35"/>
       <c r="N4" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L2,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Ejemplo de Salida&lt;/h4&gt;</v>
       </c>
       <c r="O4" s="38"/>
     </row>
@@ -23289,7 +23308,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="39"/>
       <c r="E6" t="s">
@@ -23304,7 +23323,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L6" s="39"/>
       <c r="M6" t="s">
@@ -23336,7 +23355,7 @@
       <c r="E8" s="30"/>
       <c r="F8" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D2," fin --&gt;")</f>
-        <v>&lt;!-- Eliminar el Historial de Git Localmente fin --&gt;</v>
+        <v>&lt;!-- Uso de PWD fin --&gt;</v>
       </c>
       <c r="G8" s="41"/>
       <c r="I8" s="40"/>
@@ -23346,7 +23365,7 @@
       <c r="M8" s="30"/>
       <c r="N8" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",L2," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Ejemplo de Salida fin --&gt;</v>
       </c>
       <c r="O8" s="41"/>
     </row>
@@ -23372,23 +23391,23 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
       <c r="D10" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>2</v>
       </c>
       <c r="F10" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D10," --&gt;")</f>
-        <v>&lt;!-- Volver a Conectar con GitHub --&gt;</v>
+        <v>&lt;!-- Ejemplo de Salida de PWD --&gt;</v>
       </c>
       <c r="G10" s="34"/>
       <c r="I10" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
@@ -23404,13 +23423,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F11" t="str">
         <f>CONCATENATE(B11,D11,C11)</f>
@@ -23418,13 +23437,13 @@
       </c>
       <c r="G11" s="38"/>
       <c r="I11" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J11" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N11" t="str">
         <f>CONCATENATE(J11,L11,K11)</f>
@@ -23436,7 +23455,7 @@
       <c r="A12" s="35"/>
       <c r="F12" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D10,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Volver a Conectar con GitHub&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplo de Salida de PWD&lt;/h3&gt;</v>
       </c>
       <c r="G12" s="38"/>
       <c r="I12" s="35"/>
@@ -23462,7 +23481,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D14" s="39"/>
       <c r="E14" t="s">
@@ -23477,7 +23496,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L14" s="39"/>
       <c r="M14" t="s">
@@ -23509,7 +23528,7 @@
       <c r="E16" s="30"/>
       <c r="F16" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D10," fin --&gt;")</f>
-        <v>&lt;!-- Volver a Conectar con GitHub fin --&gt;</v>
+        <v>&lt;!-- Ejemplo de Salida de PWD fin --&gt;</v>
       </c>
       <c r="G16" s="41"/>
       <c r="I16" s="40"/>
@@ -23543,21 +23562,21 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
       <c r="D18" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D18," --&gt;")</f>
-        <v>&lt;!-- Agregar los Archivos y Hacer un Nuevo Commit --&gt;</v>
+        <v>&lt;!-- Casos de Uso de PWD --&gt;</v>
       </c>
       <c r="G18" s="34"/>
       <c r="I18" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
@@ -23571,13 +23590,13 @@
     </row>
     <row r="19" customFormat="1" spans="1:15">
       <c r="A19" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" t="str">
         <f>CONCATENATE(B19,D19,C19)</f>
@@ -23585,13 +23604,13 @@
       </c>
       <c r="G19" s="38"/>
       <c r="I19" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J19" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N19" t="str">
         <f>CONCATENATE(J19,L19,K19)</f>
@@ -23603,7 +23622,7 @@
       <c r="A20" s="35"/>
       <c r="F20" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D18,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Agregar los Archivos y Hacer un Nuevo Commit&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Casos de Uso de PWD&lt;/h3&gt;</v>
       </c>
       <c r="G20" s="38"/>
       <c r="I20" s="35"/>
@@ -23629,7 +23648,7 @@
     </row>
     <row r="22" customFormat="1" spans="1:15">
       <c r="A22" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" s="39"/>
       <c r="E22" t="s">
@@ -23641,7 +23660,7 @@
       </c>
       <c r="G22" s="38"/>
       <c r="I22" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L22" s="39"/>
       <c r="M22" t="s">
@@ -23673,7 +23692,7 @@
       <c r="E24" s="30"/>
       <c r="F24" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D18," fin --&gt;")</f>
-        <v>&lt;!-- Agregar los Archivos y Hacer un Nuevo Commit fin --&gt;</v>
+        <v>&lt;!-- Casos de Uso de PWD fin --&gt;</v>
       </c>
       <c r="G24" s="41"/>
       <c r="I24" s="40"/>
@@ -23709,21 +23728,21 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26" s="32"/>
       <c r="F26" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," --&gt;")</f>
-        <v>&lt;!-- Forzar la Subida del Nuevo Historial a GitHub --&gt;</v>
+        <v>&lt;!-- Opciones útiles de PWD --&gt;</v>
       </c>
       <c r="G26" s="34"/>
       <c r="I26" s="31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
@@ -23737,13 +23756,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F27" t="str">
         <f>CONCATENATE(B27,D27,C27)</f>
@@ -23751,13 +23770,13 @@
       </c>
       <c r="G27" s="38"/>
       <c r="I27" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J27" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N27" t="str">
         <f>CONCATENATE(J27,L27,K27)</f>
@@ -23769,7 +23788,7 @@
       <c r="A28" s="35"/>
       <c r="F28" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D26,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Forzar la Subida del Nuevo Historial a GitHub&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Opciones útiles de PWD&lt;/h3&gt;</v>
       </c>
       <c r="G28" s="38"/>
       <c r="I28" s="35"/>
@@ -23795,7 +23814,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" s="39"/>
       <c r="E30" t="s">
@@ -23810,7 +23829,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L30" s="39"/>
       <c r="M30" t="s">
@@ -23842,7 +23861,7 @@
       <c r="E32" s="30"/>
       <c r="F32" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," fin --&gt;")</f>
-        <v>&lt;!-- Forzar la Subida del Nuevo Historial a GitHub fin --&gt;</v>
+        <v>&lt;!-- Opciones útiles de PWD fin --&gt;</v>
       </c>
       <c r="G32" s="41"/>
       <c r="I32" s="40"/>
@@ -23878,23 +23897,23 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," --&gt;")</f>
-        <v>&lt;!-- Verificar que el Repositorio ha Sido Reiniciado --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso ls --&gt;</v>
       </c>
       <c r="G34" s="34"/>
       <c r="I34" s="31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J34" s="32"/>
       <c r="K34" s="32"/>
@@ -23908,13 +23927,13 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F35" t="str">
         <f>CONCATENATE(B35,D35,C35)</f>
@@ -23922,13 +23941,13 @@
       </c>
       <c r="G35" s="38"/>
       <c r="I35" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J35" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K35" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N35" t="str">
         <f>CONCATENATE(J35,L35,K35)</f>
@@ -23940,7 +23959,7 @@
       <c r="A36" s="35"/>
       <c r="F36" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D34,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Verificar que el Repositorio ha Sido Reiniciado&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de uso ls&lt;/h3&gt;</v>
       </c>
       <c r="G36" s="38"/>
       <c r="I36" s="35"/>
@@ -23966,7 +23985,7 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" t="s">
@@ -23978,7 +23997,7 @@
       </c>
       <c r="G38" s="38"/>
       <c r="I38" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L38" s="39"/>
       <c r="M38" t="s">
@@ -24010,7 +24029,7 @@
       <c r="E40" s="30"/>
       <c r="F40" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," fin --&gt;")</f>
-        <v>&lt;!-- Verificar que el Repositorio ha Sido Reiniciado fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso ls fin --&gt;</v>
       </c>
       <c r="G40" s="41"/>
       <c r="I40" s="40"/>
@@ -24046,21 +24065,21 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="32"/>
       <c r="C42" s="32"/>
       <c r="D42" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," --&gt;")</f>
-        <v>&lt;!-- Recopilación de comandos utilizados --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso cd --&gt;</v>
       </c>
       <c r="G42" s="34"/>
       <c r="I42" s="31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J42" s="32"/>
       <c r="K42" s="32"/>
@@ -24074,13 +24093,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F43" t="str">
         <f>CONCATENATE(B43,D43,C43)</f>
@@ -24088,13 +24107,13 @@
       </c>
       <c r="G43" s="38"/>
       <c r="I43" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J43" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N43" t="str">
         <f>CONCATENATE(J43,L43,K43)</f>
@@ -24106,7 +24125,7 @@
       <c r="A44" s="35"/>
       <c r="F44" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D42,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Recopilación de comandos utilizados&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de uso cd&lt;/h3&gt;</v>
       </c>
       <c r="G44" s="38"/>
       <c r="I44" s="35"/>
@@ -24132,7 +24151,7 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D46" s="39"/>
       <c r="E46" t="s">
@@ -24144,7 +24163,7 @@
       </c>
       <c r="G46" s="38"/>
       <c r="I46" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L46" s="39"/>
       <c r="M46" t="s">
@@ -24176,7 +24195,7 @@
       <c r="E48" s="30"/>
       <c r="F48" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," fin --&gt;")</f>
-        <v>&lt;!-- Recopilación de comandos utilizados fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso cd fin --&gt;</v>
       </c>
       <c r="G48" s="41"/>
       <c r="I48" s="40"/>
@@ -24212,25 +24231,25 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B50" s="32"/>
       <c r="C50" s="32"/>
       <c r="D50" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50" s="32"/>
       <c r="F50" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," --&gt;")</f>
-        <v>&lt;!-- Crear un Commit Vacío --&gt;</v>
+        <v>&lt;!-- Ejemplos de Uso mkdir --&gt;</v>
       </c>
       <c r="G50" s="34"/>
       <c r="I50" s="31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J50" s="32"/>
       <c r="K50" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L50" s="33"/>
       <c r="M50" s="32"/>
@@ -24242,13 +24261,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F51" t="str">
         <f>CONCATENATE(B51,D51,C51)</f>
@@ -24256,13 +24275,13 @@
       </c>
       <c r="G51" s="38"/>
       <c r="I51" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J51" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K51" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N51" t="str">
         <f>CONCATENATE(J51,L51,K51)</f>
@@ -24274,7 +24293,7 @@
       <c r="A52" s="35"/>
       <c r="F52" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D50,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Crear un Commit Vacío&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de Uso mkdir&lt;/h3&gt;</v>
       </c>
       <c r="G52" s="38"/>
       <c r="I52" s="35"/>
@@ -24300,7 +24319,7 @@
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D54" s="39"/>
       <c r="E54" t="s">
@@ -24312,7 +24331,7 @@
       </c>
       <c r="G54" s="38"/>
       <c r="I54" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L54" s="39"/>
       <c r="M54" t="s">
@@ -24344,7 +24363,7 @@
       <c r="E56" s="30"/>
       <c r="F56" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," fin --&gt;")</f>
-        <v>&lt;!-- Crear un Commit Vacío fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de Uso mkdir fin --&gt;</v>
       </c>
       <c r="G56" s="41"/>
       <c r="I56" s="40"/>
@@ -24380,21 +24399,21 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="32"/>
       <c r="D58" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58" s="32"/>
       <c r="F58" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D58," --&gt;")</f>
-        <v>&lt;!-- Notas Importantes --&gt;</v>
+        <v>&lt;!-- Opciones Útiles de mkdir --&gt;</v>
       </c>
       <c r="G58" s="34"/>
       <c r="I58" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J58" s="32"/>
       <c r="K58" s="32"/>
@@ -24408,13 +24427,13 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F59" t="str">
         <f>CONCATENATE(B59,D59,C59)</f>
@@ -24422,13 +24441,13 @@
       </c>
       <c r="G59" s="38"/>
       <c r="I59" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J59" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N59" t="str">
         <f>CONCATENATE(J59,L59,K59)</f>
@@ -24440,7 +24459,7 @@
       <c r="A60" s="35"/>
       <c r="F60" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D58,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Notas Importantes&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Opciones Útiles de mkdir&lt;/h3&gt;</v>
       </c>
       <c r="G60" s="38"/>
       <c r="I60" s="35"/>
@@ -24466,7 +24485,7 @@
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D62" s="39"/>
       <c r="E62" t="s">
@@ -24478,7 +24497,7 @@
       </c>
       <c r="G62" s="38"/>
       <c r="I62" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L62" s="39"/>
       <c r="M62" t="s">
@@ -24510,7 +24529,7 @@
       <c r="E64" s="30"/>
       <c r="F64" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D58," fin --&gt;")</f>
-        <v>&lt;!-- Notas Importantes fin --&gt;</v>
+        <v>&lt;!-- Opciones Útiles de mkdir fin --&gt;</v>
       </c>
       <c r="G64" s="41"/>
       <c r="I64" s="40"/>
@@ -24546,19 +24565,21 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="32"/>
-      <c r="D66" s="33"/>
+      <c r="D66" s="33" t="s">
+        <v>163</v>
+      </c>
       <c r="E66" s="32"/>
       <c r="F66" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D66," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso touch --&gt;</v>
       </c>
       <c r="G66" s="34"/>
       <c r="I66" s="31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J66" s="32"/>
       <c r="K66" s="32"/>
@@ -24572,13 +24593,13 @@
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F67" t="str">
         <f>CONCATENATE(B67,D67,C67)</f>
@@ -24586,13 +24607,13 @@
       </c>
       <c r="G67" s="38"/>
       <c r="I67" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J67" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K67" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N67" t="str">
         <f>CONCATENATE(J67,L67,K67)</f>
@@ -24604,7 +24625,7 @@
       <c r="A68" s="35"/>
       <c r="F68" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D66,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de uso touch&lt;/h3&gt;</v>
       </c>
       <c r="G68" s="38"/>
       <c r="I68" s="35"/>
@@ -24630,7 +24651,7 @@
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D70" s="39"/>
       <c r="E70" t="s">
@@ -24642,7 +24663,7 @@
       </c>
       <c r="G70" s="38"/>
       <c r="I70" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L70" s="39"/>
       <c r="M70" t="s">
@@ -24674,7 +24695,7 @@
       <c r="E72" s="30"/>
       <c r="F72" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D66," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso touch fin --&gt;</v>
       </c>
       <c r="G72" s="41"/>
       <c r="I72" s="40"/>
@@ -24710,21 +24731,21 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B74" s="32"/>
       <c r="C74" s="32"/>
       <c r="D74" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E74" s="32"/>
       <c r="F74" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D74," --&gt;")</f>
-        <v>&lt;!-- Crear una Nueva Rama Vacía --&gt;</v>
+        <v>&lt;!-- Opciones Útiles de touch --&gt;</v>
       </c>
       <c r="G74" s="34"/>
       <c r="I74" s="31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J74" s="32"/>
       <c r="K74" s="32"/>
@@ -24738,13 +24759,13 @@
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F75" t="str">
         <f>CONCATENATE(B75,D75,C75)</f>
@@ -24752,13 +24773,13 @@
       </c>
       <c r="G75" s="38"/>
       <c r="I75" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J75" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N75" t="str">
         <f>CONCATENATE(J75,L75,K75)</f>
@@ -24770,7 +24791,7 @@
       <c r="A76" s="35"/>
       <c r="F76" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D74,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Crear una Nueva Rama Vacía&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Opciones Útiles de touch&lt;/h3&gt;</v>
       </c>
       <c r="G76" s="38"/>
       <c r="I76" s="35"/>
@@ -24796,7 +24817,7 @@
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D78" s="39"/>
       <c r="E78" t="s">
@@ -24808,7 +24829,7 @@
       </c>
       <c r="G78" s="38"/>
       <c r="I78" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L78" s="39"/>
       <c r="M78" t="s">
@@ -24840,7 +24861,7 @@
       <c r="E80" s="30"/>
       <c r="F80" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D74," fin --&gt;")</f>
-        <v>&lt;!-- Crear una Nueva Rama Vacía fin --&gt;</v>
+        <v>&lt;!-- Opciones Útiles de touch fin --&gt;</v>
       </c>
       <c r="G80" s="41"/>
       <c r="I80" s="40"/>
@@ -24876,21 +24897,21 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="32"/>
       <c r="D82" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E82" s="32"/>
       <c r="F82" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D82," --&gt;")</f>
-        <v>&lt;!-- Eliminar los Archivos Antiguos --&gt;</v>
+        <v>&lt;!-- Ejemplos de Uso rm --&gt;</v>
       </c>
       <c r="G82" s="34"/>
       <c r="I82" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J82" s="32"/>
       <c r="K82" s="32"/>
@@ -24904,13 +24925,13 @@
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F83" t="str">
         <f>CONCATENATE(B83,D83,C83)</f>
@@ -24918,13 +24939,13 @@
       </c>
       <c r="G83" s="38"/>
       <c r="I83" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J83" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K83" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N83" t="str">
         <f>CONCATENATE(J83,L83,K83)</f>
@@ -24936,7 +24957,7 @@
       <c r="A84" s="35"/>
       <c r="F84" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D82,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Eliminar los Archivos Antiguos&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de Uso rm&lt;/h3&gt;</v>
       </c>
       <c r="G84" s="38"/>
       <c r="I84" s="35"/>
@@ -24962,7 +24983,7 @@
     </row>
     <row r="86" spans="1:15">
       <c r="A86" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D86" s="39"/>
       <c r="E86" t="s">
@@ -24974,7 +24995,7 @@
       </c>
       <c r="G86" s="38"/>
       <c r="I86" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L86" s="39"/>
       <c r="M86" t="s">
@@ -25006,7 +25027,7 @@
       <c r="E88" s="30"/>
       <c r="F88" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D82," fin --&gt;")</f>
-        <v>&lt;!-- Eliminar los Archivos Antiguos fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de Uso rm fin --&gt;</v>
       </c>
       <c r="G88" s="41"/>
       <c r="I88" s="40"/>
@@ -25042,21 +25063,21 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B90" s="32"/>
       <c r="C90" s="32"/>
       <c r="D90" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E90" s="32"/>
       <c r="F90" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D90," --&gt;")</f>
-        <v>&lt;!-- Agregar Nuevos Archivos --&gt;</v>
+        <v>&lt;!-- Consejos de Seguridad rm --&gt;</v>
       </c>
       <c r="G90" s="34"/>
       <c r="I90" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J90" s="32"/>
       <c r="K90" s="32"/>
@@ -25070,13 +25091,13 @@
     </row>
     <row r="91" spans="1:15">
       <c r="A91" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B91" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F91" t="str">
         <f>CONCATENATE(B91,D91,C91)</f>
@@ -25084,13 +25105,13 @@
       </c>
       <c r="G91" s="38"/>
       <c r="I91" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J91" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K91" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N91" t="str">
         <f>CONCATENATE(J91,L91,K91)</f>
@@ -25102,7 +25123,7 @@
       <c r="A92" s="35"/>
       <c r="F92" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D90,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Agregar Nuevos Archivos&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Consejos de Seguridad rm&lt;/h3&gt;</v>
       </c>
       <c r="G92" s="38"/>
       <c r="I92" s="35"/>
@@ -25128,7 +25149,7 @@
     </row>
     <row r="94" spans="1:15">
       <c r="A94" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D94" s="39"/>
       <c r="E94" t="s">
@@ -25140,7 +25161,7 @@
       </c>
       <c r="G94" s="38"/>
       <c r="I94" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L94" s="39"/>
       <c r="M94" t="s">
@@ -25172,7 +25193,7 @@
       <c r="E96" s="30"/>
       <c r="F96" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D90," fin --&gt;")</f>
-        <v>&lt;!-- Agregar Nuevos Archivos fin --&gt;</v>
+        <v>&lt;!-- Consejos de Seguridad rm fin --&gt;</v>
       </c>
       <c r="G96" s="41"/>
       <c r="I96" s="40"/>
@@ -25208,21 +25229,21 @@
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B98" s="32"/>
       <c r="C98" s="32"/>
       <c r="D98" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E98" s="32"/>
       <c r="F98" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D98," --&gt;")</f>
-        <v>&lt;!-- Subir la Nueva Rama a GitHub --&gt;</v>
+        <v>&lt;!-- Alternativas a clear --&gt;</v>
       </c>
       <c r="G98" s="34"/>
       <c r="I98" s="31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J98" s="32"/>
       <c r="K98" s="32"/>
@@ -25236,13 +25257,13 @@
     </row>
     <row r="99" spans="1:15">
       <c r="A99" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B99" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F99" t="str">
         <f>CONCATENATE(B99,D99,C99)</f>
@@ -25250,13 +25271,13 @@
       </c>
       <c r="G99" s="38"/>
       <c r="I99" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J99" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K99" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N99" t="str">
         <f>CONCATENATE(J99,L99,K99)</f>
@@ -25268,7 +25289,7 @@
       <c r="A100" s="35"/>
       <c r="F100" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D98,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Subir la Nueva Rama a GitHub&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Alternativas a clear&lt;/h3&gt;</v>
       </c>
       <c r="G100" s="38"/>
       <c r="I100" s="35"/>
@@ -25294,7 +25315,7 @@
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D102" s="39"/>
       <c r="E102" t="s">
@@ -25306,7 +25327,7 @@
       </c>
       <c r="G102" s="38"/>
       <c r="I102" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L102" s="39"/>
       <c r="M102" t="s">
@@ -25338,7 +25359,7 @@
       <c r="E104" s="30"/>
       <c r="F104" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D98," fin --&gt;")</f>
-        <v>&lt;!-- Subir la Nueva Rama a GitHub fin --&gt;</v>
+        <v>&lt;!-- Alternativas a clear fin --&gt;</v>
       </c>
       <c r="G104" s="41"/>
       <c r="I104" s="40"/>
@@ -25374,21 +25395,21 @@
     </row>
     <row r="106" customFormat="1" spans="1:15">
       <c r="A106" s="31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B106" s="32"/>
       <c r="C106" s="32"/>
       <c r="D106" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E106" s="32"/>
       <c r="F106" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D106," --&gt;")</f>
-        <v>&lt;!-- Establecer la Nueva Rama como Principal --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso history --&gt;</v>
       </c>
       <c r="G106" s="34"/>
       <c r="I106" s="31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J106" s="32"/>
       <c r="K106" s="32"/>
@@ -25402,13 +25423,13 @@
     </row>
     <row r="107" customFormat="1" spans="1:15">
       <c r="A107" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F107" t="str">
         <f>CONCATENATE(B107,D107,C107)</f>
@@ -25416,13 +25437,13 @@
       </c>
       <c r="G107" s="38"/>
       <c r="I107" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J107" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K107" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N107" t="str">
         <f>CONCATENATE(J107,L107,K107)</f>
@@ -25434,7 +25455,7 @@
       <c r="A108" s="35"/>
       <c r="F108" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D106,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Establecer la Nueva Rama como Principal&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ejemplos de uso history&lt;/h3&gt;</v>
       </c>
       <c r="G108" s="38"/>
       <c r="I108" s="35"/>
@@ -25460,7 +25481,7 @@
     </row>
     <row r="110" customFormat="1" spans="1:15">
       <c r="A110" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D110" s="39"/>
       <c r="E110" t="s">
@@ -25472,7 +25493,7 @@
       </c>
       <c r="G110" s="38"/>
       <c r="I110" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L110" s="39"/>
       <c r="M110" t="s">
@@ -25504,7 +25525,7 @@
       <c r="E112" s="30"/>
       <c r="F112" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D106," fin --&gt;")</f>
-        <v>&lt;!-- Establecer la Nueva Rama como Principal fin --&gt;</v>
+        <v>&lt;!-- Ejemplos de uso history fin --&gt;</v>
       </c>
       <c r="G112" s="41"/>
       <c r="I112" s="40"/>
@@ -25540,21 +25561,21 @@
     </row>
     <row r="114" customFormat="1" spans="1:15">
       <c r="A114" s="31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B114" s="32"/>
       <c r="C114" s="32"/>
       <c r="D114" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E114" s="32"/>
       <c r="F114" s="32" t="str">
         <f>CONCATENATE("&lt;!-- ",D114," --&gt;")</f>
-        <v>&lt;!-- Crear una nueva rama Vacía --&gt;</v>
+        <v>&lt;!-- Ubicación del historial --&gt;</v>
       </c>
       <c r="G114" s="34"/>
       <c r="I114" s="31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J114" s="32"/>
       <c r="K114" s="32"/>
@@ -25568,13 +25589,13 @@
     </row>
     <row r="115" customFormat="1" spans="1:15">
       <c r="A115" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F115" t="str">
         <f>CONCATENATE(B115,D115,C115)</f>
@@ -25582,13 +25603,13 @@
       </c>
       <c r="G115" s="38"/>
       <c r="I115" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J115" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K115" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N115" t="str">
         <f>CONCATENATE(J115,L115,K115)</f>
@@ -25600,7 +25621,7 @@
       <c r="A116" s="35"/>
       <c r="F116" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D114,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Crear una nueva rama Vacía&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Ubicación del historial&lt;/h3&gt;</v>
       </c>
       <c r="G116" s="38"/>
       <c r="I116" s="35"/>
@@ -25626,7 +25647,7 @@
     </row>
     <row r="118" customFormat="1" spans="1:15">
       <c r="A118" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D118" s="39"/>
       <c r="E118" t="s">
@@ -25638,7 +25659,7 @@
       </c>
       <c r="G118" s="38"/>
       <c r="I118" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L118" s="39"/>
       <c r="M118" t="s">
@@ -25670,7 +25691,7 @@
       <c r="E120" s="30"/>
       <c r="F120" s="30" t="str">
         <f>CONCATENATE("&lt;!-- ",D114," fin --&gt;")</f>
-        <v>&lt;!-- Crear una nueva rama Vacía fin --&gt;</v>
+        <v>&lt;!-- Ubicación del historial fin --&gt;</v>
       </c>
       <c r="G120" s="41"/>
       <c r="I120" s="40"/>
@@ -25706,7 +25727,7 @@
     </row>
     <row r="122" customFormat="1" spans="1:15">
       <c r="A122" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B122" s="32"/>
       <c r="C122" s="32"/>
@@ -25718,7 +25739,7 @@
       </c>
       <c r="G122" s="34"/>
       <c r="I122" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J122" s="32"/>
       <c r="K122" s="32"/>
@@ -25732,13 +25753,13 @@
     </row>
     <row r="123" customFormat="1" spans="1:15">
       <c r="A123" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F123" t="str">
         <f>CONCATENATE(B123,D123,C123)</f>
@@ -25746,13 +25767,13 @@
       </c>
       <c r="G123" s="38"/>
       <c r="I123" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J123" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K123" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N123" t="str">
         <f>CONCATENATE(J123,L123,K123)</f>
@@ -25790,7 +25811,7 @@
     </row>
     <row r="126" customFormat="1" spans="1:15">
       <c r="A126" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D126" s="39"/>
       <c r="E126" t="s">
@@ -25802,7 +25823,7 @@
       </c>
       <c r="G126" s="38"/>
       <c r="I126" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L126" s="39"/>
       <c r="M126" t="s">
@@ -25870,7 +25891,7 @@
     </row>
     <row r="130" customFormat="1" spans="1:15">
       <c r="A130" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B130" s="32"/>
       <c r="C130" s="32"/>
@@ -25882,7 +25903,7 @@
       </c>
       <c r="G130" s="34"/>
       <c r="I130" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J130" s="32"/>
       <c r="K130" s="32"/>
@@ -25896,13 +25917,13 @@
     </row>
     <row r="131" customFormat="1" spans="1:15">
       <c r="A131" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C131" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F131" t="str">
         <f>CONCATENATE(B131,D131,C131)</f>
@@ -25910,13 +25931,13 @@
       </c>
       <c r="G131" s="38"/>
       <c r="I131" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J131" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K131" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N131" t="str">
         <f>CONCATENATE(J131,L131,K131)</f>
@@ -25954,7 +25975,7 @@
     </row>
     <row r="134" customFormat="1" spans="1:15">
       <c r="A134" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D134" s="39"/>
       <c r="E134" t="s">
@@ -25966,7 +25987,7 @@
       </c>
       <c r="G134" s="38"/>
       <c r="I134" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L134" s="39"/>
       <c r="M134" t="s">
@@ -26034,7 +26055,7 @@
     </row>
     <row r="138" customFormat="1" spans="1:15">
       <c r="A138" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B138" s="32"/>
       <c r="C138" s="32"/>
@@ -26046,7 +26067,7 @@
       </c>
       <c r="G138" s="34"/>
       <c r="I138" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J138" s="32"/>
       <c r="K138" s="32"/>
@@ -26060,13 +26081,13 @@
     </row>
     <row r="139" customFormat="1" spans="1:15">
       <c r="A139" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C139" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F139" t="str">
         <f>CONCATENATE(B139,D139,C139)</f>
@@ -26074,13 +26095,13 @@
       </c>
       <c r="G139" s="38"/>
       <c r="I139" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J139" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K139" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N139" t="str">
         <f>CONCATENATE(J139,L139,K139)</f>
@@ -26118,7 +26139,7 @@
     </row>
     <row r="142" customFormat="1" spans="1:15">
       <c r="A142" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D142" s="39"/>
       <c r="E142" t="s">
@@ -26130,7 +26151,7 @@
       </c>
       <c r="G142" s="38"/>
       <c r="I142" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L142" s="39"/>
       <c r="M142" t="s">
@@ -26198,7 +26219,7 @@
     </row>
     <row r="146" customFormat="1" spans="1:15">
       <c r="A146" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B146" s="32"/>
       <c r="C146" s="32"/>
@@ -26210,7 +26231,7 @@
       </c>
       <c r="G146" s="34"/>
       <c r="I146" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J146" s="32"/>
       <c r="K146" s="32"/>
@@ -26224,13 +26245,13 @@
     </row>
     <row r="147" customFormat="1" spans="1:15">
       <c r="A147" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B147" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C147" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F147" t="str">
         <f>CONCATENATE(B147,D147,C147)</f>
@@ -26238,13 +26259,13 @@
       </c>
       <c r="G147" s="38"/>
       <c r="I147" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J147" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K147" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N147" t="str">
         <f>CONCATENATE(J147,L147,K147)</f>
@@ -26282,7 +26303,7 @@
     </row>
     <row r="150" customFormat="1" spans="1:15">
       <c r="A150" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D150" s="39"/>
       <c r="E150" t="s">
@@ -26294,7 +26315,7 @@
       </c>
       <c r="G150" s="38"/>
       <c r="I150" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L150" s="39"/>
       <c r="M150" t="s">
@@ -26362,7 +26383,7 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B154" s="32"/>
       <c r="C154" s="32"/>
@@ -26374,7 +26395,7 @@
       </c>
       <c r="G154" s="34"/>
       <c r="I154" s="31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J154" s="32"/>
       <c r="K154" s="32"/>
@@ -26388,13 +26409,13 @@
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B155" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C155" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F155" t="str">
         <f>CONCATENATE(B155,D155,C155)</f>
@@ -26402,13 +26423,13 @@
       </c>
       <c r="G155" s="38"/>
       <c r="I155" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J155" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K155" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N155" t="str">
         <f>CONCATENATE(J155,L155,K155)</f>
@@ -26446,7 +26467,7 @@
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D158" s="39"/>
       <c r="E158" t="s">
@@ -26458,7 +26479,7 @@
       </c>
       <c r="G158" s="38"/>
       <c r="I158" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L158" s="39"/>
       <c r="M158" t="s">
@@ -26526,7 +26547,7 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B162" s="32"/>
       <c r="C162" s="32"/>
@@ -26538,7 +26559,7 @@
       </c>
       <c r="G162" s="34"/>
       <c r="I162" s="31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J162" s="32"/>
       <c r="K162" s="32"/>
@@ -26552,13 +26573,13 @@
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C163" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F163" t="str">
         <f>CONCATENATE(B163,D163,C163)</f>
@@ -26566,13 +26587,13 @@
       </c>
       <c r="G163" s="38"/>
       <c r="I163" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J163" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K163" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N163" t="str">
         <f>CONCATENATE(J163,L163,K163)</f>
@@ -26610,7 +26631,7 @@
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D166" s="39"/>
       <c r="E166" t="s">
@@ -26622,7 +26643,7 @@
       </c>
       <c r="G166" s="38"/>
       <c r="I166" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L166" s="39"/>
       <c r="M166" t="s">
@@ -26690,7 +26711,7 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B170" s="32"/>
       <c r="C170" s="32"/>
@@ -26702,7 +26723,7 @@
       </c>
       <c r="G170" s="34"/>
       <c r="I170" s="31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J170" s="32"/>
       <c r="K170" s="32"/>
@@ -26716,13 +26737,13 @@
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C171" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F171" t="str">
         <f>CONCATENATE(B171,D171,C171)</f>
@@ -26730,13 +26751,13 @@
       </c>
       <c r="G171" s="38"/>
       <c r="I171" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J171" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K171" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N171" t="str">
         <f>CONCATENATE(J171,L171,K171)</f>
@@ -26774,7 +26795,7 @@
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D174" s="39"/>
       <c r="E174" t="s">
@@ -26786,7 +26807,7 @@
       </c>
       <c r="G174" s="38"/>
       <c r="I174" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L174" s="39"/>
       <c r="M174" t="s">
@@ -26854,7 +26875,7 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B178" s="32"/>
       <c r="C178" s="32"/>
@@ -26866,7 +26887,7 @@
       </c>
       <c r="G178" s="34"/>
       <c r="I178" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J178" s="32"/>
       <c r="K178" s="32"/>
@@ -26880,13 +26901,13 @@
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B179" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C179" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F179" t="str">
         <f>CONCATENATE(B179,D179,C179)</f>
@@ -26894,13 +26915,13 @@
       </c>
       <c r="G179" s="38"/>
       <c r="I179" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J179" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K179" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N179" t="str">
         <f>CONCATENATE(J179,L179,K179)</f>
@@ -26938,7 +26959,7 @@
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D182" s="39"/>
       <c r="E182" t="s">
@@ -26950,7 +26971,7 @@
       </c>
       <c r="G182" s="38"/>
       <c r="I182" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L182" s="39"/>
       <c r="M182" t="s">
@@ -26999,7 +27020,7 @@
     <row r="185" ht="15"/>
     <row r="186" spans="1:15">
       <c r="A186" s="31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B186" s="32"/>
       <c r="C186" s="32"/>
@@ -27011,7 +27032,7 @@
       </c>
       <c r="G186" s="34"/>
       <c r="I186" s="31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J186" s="32"/>
       <c r="K186" s="32"/>
@@ -27025,13 +27046,13 @@
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B187" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C187" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F187" t="str">
         <f>CONCATENATE(B187,D187,C187)</f>
@@ -27039,13 +27060,13 @@
       </c>
       <c r="G187" s="38"/>
       <c r="I187" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J187" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K187" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N187" t="str">
         <f>CONCATENATE(J187,L187,K187)</f>
@@ -27083,7 +27104,7 @@
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D190" s="39"/>
       <c r="E190" t="s">
@@ -27095,7 +27116,7 @@
       </c>
       <c r="G190" s="38"/>
       <c r="I190" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L190" s="39"/>
       <c r="M190" t="s">
@@ -27163,7 +27184,7 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B194" s="32"/>
       <c r="C194" s="32"/>
@@ -27175,7 +27196,7 @@
       </c>
       <c r="G194" s="34"/>
       <c r="I194" s="31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J194" s="32"/>
       <c r="K194" s="32"/>
@@ -27189,13 +27210,13 @@
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B195" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C195" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F195" t="str">
         <f>CONCATENATE(B195,D195,C195)</f>
@@ -27203,13 +27224,13 @@
       </c>
       <c r="G195" s="38"/>
       <c r="I195" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J195" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K195" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N195" t="str">
         <f>CONCATENATE(J195,L195,K195)</f>
@@ -27247,7 +27268,7 @@
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D198" s="39"/>
       <c r="E198" t="s">
@@ -27259,7 +27280,7 @@
       </c>
       <c r="G198" s="38"/>
       <c r="I198" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L198" s="39"/>
       <c r="M198" t="s">
@@ -27327,7 +27348,7 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B202" s="32"/>
       <c r="C202" s="32"/>
@@ -27339,7 +27360,7 @@
       </c>
       <c r="G202" s="34"/>
       <c r="I202" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J202" s="32"/>
       <c r="K202" s="32"/>
@@ -27353,13 +27374,13 @@
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B203" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C203" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F203" t="str">
         <f>CONCATENATE(B203,D203,C203)</f>
@@ -27367,13 +27388,13 @@
       </c>
       <c r="G203" s="38"/>
       <c r="I203" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J203" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K203" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N203" t="str">
         <f>CONCATENATE(J203,L203,K203)</f>
@@ -27411,7 +27432,7 @@
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D206" s="39"/>
       <c r="E206" t="s">
@@ -27423,7 +27444,7 @@
       </c>
       <c r="G206" s="38"/>
       <c r="I206" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L206" s="39"/>
       <c r="M206" t="s">
@@ -27491,7 +27512,7 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B210" s="32"/>
       <c r="C210" s="32"/>
@@ -27503,7 +27524,7 @@
       </c>
       <c r="G210" s="34"/>
       <c r="I210" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J210" s="32"/>
       <c r="K210" s="32"/>
@@ -27517,13 +27538,13 @@
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B211" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C211" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F211" t="str">
         <f>CONCATENATE(B211,D211,C211)</f>
@@ -27531,13 +27552,13 @@
       </c>
       <c r="G211" s="38"/>
       <c r="I211" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J211" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K211" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N211" t="str">
         <f>CONCATENATE(J211,L211,K211)</f>
@@ -27575,7 +27596,7 @@
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D214" s="39"/>
       <c r="E214" t="s">
@@ -27587,7 +27608,7 @@
       </c>
       <c r="G214" s="38"/>
       <c r="I214" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L214" s="39"/>
       <c r="M214" t="s">
@@ -27655,7 +27676,7 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B218" s="32"/>
       <c r="C218" s="32"/>
@@ -27667,7 +27688,7 @@
       </c>
       <c r="G218" s="34"/>
       <c r="I218" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J218" s="32"/>
       <c r="K218" s="32"/>
@@ -27681,13 +27702,13 @@
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B219" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C219" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F219" t="str">
         <f>CONCATENATE(B219,D219,C219)</f>
@@ -27695,13 +27716,13 @@
       </c>
       <c r="G219" s="38"/>
       <c r="I219" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J219" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K219" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N219" t="str">
         <f>CONCATENATE(J219,L219,K219)</f>
@@ -27739,7 +27760,7 @@
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D222" s="39"/>
       <c r="E222" t="s">
@@ -27751,7 +27772,7 @@
       </c>
       <c r="G222" s="38"/>
       <c r="I222" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L222" s="39"/>
       <c r="M222" t="s">
@@ -27819,7 +27840,7 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B226" s="32"/>
       <c r="C226" s="32"/>
@@ -27831,7 +27852,7 @@
       </c>
       <c r="G226" s="34"/>
       <c r="I226" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J226" s="32"/>
       <c r="K226" s="32"/>
@@ -27845,13 +27866,13 @@
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B227" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C227" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F227" t="str">
         <f>CONCATENATE(B227,D227,C227)</f>
@@ -27859,13 +27880,13 @@
       </c>
       <c r="G227" s="38"/>
       <c r="I227" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J227" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K227" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N227" t="str">
         <f>CONCATENATE(J227,L227,K227)</f>
@@ -27903,7 +27924,7 @@
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D230" s="39"/>
       <c r="E230" t="s">
@@ -27915,7 +27936,7 @@
       </c>
       <c r="G230" s="38"/>
       <c r="I230" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L230" s="39"/>
       <c r="M230" t="s">
@@ -27983,7 +28004,7 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B234" s="32"/>
       <c r="C234" s="32"/>
@@ -27995,7 +28016,7 @@
       </c>
       <c r="G234" s="34"/>
       <c r="I234" s="31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J234" s="32"/>
       <c r="K234" s="32"/>
@@ -28009,13 +28030,13 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B235" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C235" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F235" t="str">
         <f>CONCATENATE(B235,D235,C235)</f>
@@ -28023,13 +28044,13 @@
       </c>
       <c r="G235" s="38"/>
       <c r="I235" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J235" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K235" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N235" t="str">
         <f>CONCATENATE(J235,L235,K235)</f>
@@ -28067,7 +28088,7 @@
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D238" s="39"/>
       <c r="E238" t="s">
@@ -28079,7 +28100,7 @@
       </c>
       <c r="G238" s="38"/>
       <c r="I238" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L238" s="39"/>
       <c r="M238" t="s">
@@ -28147,7 +28168,7 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B242" s="32"/>
       <c r="C242" s="32"/>
@@ -28159,7 +28180,7 @@
       </c>
       <c r="G242" s="34"/>
       <c r="I242" s="31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J242" s="32"/>
       <c r="K242" s="32"/>
@@ -28173,13 +28194,13 @@
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B243" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C243" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F243" t="str">
         <f>CONCATENATE(B243,D243,C243)</f>
@@ -28187,13 +28208,13 @@
       </c>
       <c r="G243" s="38"/>
       <c r="I243" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J243" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K243" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N243" t="str">
         <f>CONCATENATE(J243,L243,K243)</f>
@@ -28231,7 +28252,7 @@
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D246" s="39"/>
       <c r="E246" t="s">
@@ -28243,7 +28264,7 @@
       </c>
       <c r="G246" s="38"/>
       <c r="I246" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L246" s="39"/>
       <c r="M246" t="s">
@@ -28311,7 +28332,7 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B250" s="32"/>
       <c r="C250" s="32"/>
@@ -28323,7 +28344,7 @@
       </c>
       <c r="G250" s="34"/>
       <c r="I250" s="31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J250" s="32"/>
       <c r="K250" s="32"/>
@@ -28337,13 +28358,13 @@
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B251" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C251" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F251" t="str">
         <f>CONCATENATE(B251,D251,C251)</f>
@@ -28351,13 +28372,13 @@
       </c>
       <c r="G251" s="38"/>
       <c r="I251" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J251" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K251" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N251" t="str">
         <f>CONCATENATE(J251,L251,K251)</f>
@@ -28395,7 +28416,7 @@
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D254" s="39"/>
       <c r="E254" t="s">
@@ -28407,7 +28428,7 @@
       </c>
       <c r="G254" s="38"/>
       <c r="I254" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L254" s="39"/>
       <c r="M254" t="s">
@@ -28475,7 +28496,7 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B258" s="32"/>
       <c r="C258" s="32"/>
@@ -28487,7 +28508,7 @@
       </c>
       <c r="G258" s="34"/>
       <c r="I258" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J258" s="32"/>
       <c r="K258" s="32"/>
@@ -28501,13 +28522,13 @@
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B259" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C259" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F259" t="str">
         <f>CONCATENATE(B259,D259,C259)</f>
@@ -28515,13 +28536,13 @@
       </c>
       <c r="G259" s="38"/>
       <c r="I259" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J259" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K259" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N259" t="str">
         <f>CONCATENATE(J259,L259,K259)</f>
@@ -28559,7 +28580,7 @@
     </row>
     <row r="262" spans="1:15">
       <c r="A262" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D262" s="39"/>
       <c r="E262" t="s">
@@ -28571,7 +28592,7 @@
       </c>
       <c r="G262" s="38"/>
       <c r="I262" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L262" s="39"/>
       <c r="M262" t="s">
@@ -28635,7 +28656,7 @@
     <col min="1" max="1" width="36.75" style="24" customWidth="1"/>
     <col min="2" max="5" width="10.625" style="24" customWidth="1"/>
     <col min="6" max="6" width="52.625" style="24" customWidth="1"/>
-    <col min="7" max="7" width="52.625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="108.375" style="25" customWidth="1"/>
     <col min="8" max="16" width="52.625" style="24" customWidth="1"/>
     <col min="17" max="17" width="52.625" style="25" customWidth="1"/>
     <col min="18" max="16384" width="52.625" style="24" customWidth="1"/>
@@ -28643,19 +28664,19 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" s="25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G2" s="25" t="str">
         <f>A2</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q2" s="25" t="str">
         <f>K2</f>
@@ -28669,7 +28690,7 @@
       </c>
       <c r="B3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",LEFT(F3,FIND(":",F3,1)-1),"")</f>
-        <v>Ir al repositorio en GitHub</v>
+        <v>Mostrar todo el historial de comandos</v>
       </c>
       <c r="C3" s="24" t="str">
         <f t="shared" ref="C3:C19" si="1">IF(F3&lt;&gt;"","&lt;/span&gt;","")</f>
@@ -28677,18 +28698,18 @@
       </c>
       <c r="D3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",RIGHT(F3,LEN(F3)-FIND(":",F3,1)),"")</f>
-        <v/>
+        <v> Muestra una lista numerada con todos los comandos ejecutados en la sesión actual.</v>
       </c>
       <c r="E3" s="24" t="str">
         <f t="shared" ref="E3:E19" si="2">IF(F3&lt;&gt;"","&lt;/li&gt;","")</f>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="25" t="str">
         <f>IF(F3&lt;&gt;"",CONCATENATE(A3,B3,C3,":",D3,E3),IF(F2&lt;&gt;"",F3,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Ir al repositorio en GitHub&lt;/span&gt;:&lt;/li&gt;</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Mostrar todo el historial de comandos&lt;/span&gt;: Muestra una lista numerada con todos los comandos ejecutados en la sesión actual.&lt;/li&gt;</v>
       </c>
       <c r="K3" s="24" t="str">
         <f t="shared" ref="K3:K19" si="3">IF(P3&lt;&gt;"",$A$20,"")</f>
@@ -28721,28 +28742,28 @@
         <f t="shared" si="0"/>
         <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
-      <c r="B4" s="24" t="e">
+      <c r="B4" s="24" t="str">
         <f t="shared" ref="B3:B19" si="9">IF(F4&lt;&gt;"",LEFT(F4,FIND(":",F4,1)-1),"")</f>
-        <v>#VALUE!</v>
+        <v>Mostrar solo los últimos n comandos</v>
       </c>
       <c r="C4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>&lt;/span&gt;</v>
       </c>
-      <c r="D4" s="24" t="e">
+      <c r="D4" s="24" t="str">
         <f t="shared" ref="D3:D19" si="10">IF(F4&lt;&gt;"",RIGHT(F4,LEN(F4)-FIND(":",F4,1)),"")</f>
-        <v>#VALUE!</v>
+        <v> Muestra los últimos 10 comandos ejecutados.</v>
       </c>
       <c r="E4" s="24" t="str">
         <f t="shared" si="2"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="G4" s="25" t="e">
+        <v>186</v>
+      </c>
+      <c r="G4" s="25" t="str">
         <f>IF(F4&lt;&gt;"",CONCATENATE(A4,B4,C4,":",D4,E4),IF(F3&lt;&gt;"",$A$21,""))</f>
-        <v>#VALUE!</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Mostrar solo los últimos n comandos&lt;/span&gt;: Muestra los últimos 10 comandos ejecutados.&lt;/li&gt;</v>
       </c>
       <c r="K4" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28775,28 +28796,28 @@
         <f t="shared" si="0"/>
         <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
-      <c r="B5" s="24" t="e">
+      <c r="B5" s="24" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>Buscar un comando en el historial</v>
       </c>
       <c r="C5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>&lt;/span&gt;</v>
       </c>
-      <c r="D5" s="24" t="e">
+      <c r="D5" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <v> Muestra todas las líneas del historial que contienen el comando ls.</v>
       </c>
       <c r="E5" s="24" t="str">
         <f t="shared" si="2"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="G5" s="25" t="e">
+        <v>187</v>
+      </c>
+      <c r="G5" s="25" t="str">
         <f t="shared" ref="G5:G20" si="11">IF(F5&lt;&gt;"",CONCATENATE(A5,B5,C5,":",D5,E5),IF(F4&lt;&gt;"",$A$21,""))</f>
-        <v>#VALUE!</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Buscar un comando en el historial&lt;/span&gt;: Muestra todas las líneas del historial que contienen el comando ls.&lt;/li&gt;</v>
       </c>
       <c r="K5" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28829,28 +28850,28 @@
         <f t="shared" si="0"/>
         <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
-      <c r="B6" s="24" t="e">
+      <c r="B6" s="24" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+        <v>Reejecutar un comando del historial</v>
       </c>
       <c r="C6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>&lt;/span&gt;</v>
       </c>
-      <c r="D6" s="24" t="e">
+      <c r="D6" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <v> Se puede ejecutar un comando directamente usando su número en la lista:</v>
       </c>
       <c r="E6" s="24" t="str">
         <f t="shared" si="2"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" s="25" t="e">
+        <v>188</v>
+      </c>
+      <c r="G6" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Reejecutar un comando del historial&lt;/span&gt;: Se puede ejecutar un comando directamente usando su número en la lista:&lt;/li&gt;</v>
       </c>
       <c r="K6" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28881,28 +28902,30 @@
     <row r="7" spans="1:17">
       <c r="A7" s="24" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Eliminar un comando específico del historial</v>
       </c>
       <c r="C7" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D7" s="24" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v> Elimina el comando número 50 del historial.</v>
       </c>
       <c r="E7" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F7" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>189</v>
+      </c>
       <c r="G7" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>&lt;/ul&gt;</v>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Eliminar un comando específico del historial&lt;/span&gt;: Elimina el comando número 50 del historial.&lt;/li&gt;</v>
       </c>
       <c r="K7" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28933,28 +28956,30 @@
     <row r="8" spans="1:17">
       <c r="A8" s="24" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Limpiar completamente el historial</v>
       </c>
       <c r="C8" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D8" s="24" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v> Borra todos los comandos almacenados en el historial de la sesión actual.</v>
       </c>
       <c r="E8" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F8" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>190</v>
+      </c>
       <c r="G8" s="25" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Limpiar completamente el historial&lt;/span&gt;: Borra todos los comandos almacenados en el historial de la sesión actual.&lt;/li&gt;</v>
       </c>
       <c r="K8" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28985,28 +29010,30 @@
     <row r="9" spans="1:17">
       <c r="A9" s="24" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Guardar el historial actual en el archivo de historial</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D9" s="24" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v> Guarda los cambios en el archivo ~/.bash_history, donde se almacena el historial de comandos.</v>
       </c>
       <c r="E9" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F9" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>191</v>
+      </c>
       <c r="G9" s="25" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Guardar el historial actual en el archivo de historial&lt;/span&gt;: Guarda los cambios en el archivo ~/.bash_history, donde se almacena el historial de comandos.&lt;/li&gt;</v>
       </c>
       <c r="K9" s="24" t="str">
         <f t="shared" si="3"/>
@@ -29058,7 +29085,7 @@
       <c r="F10" s="26"/>
       <c r="G10" s="25" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K10" s="24" t="str">
         <f t="shared" si="3"/>
@@ -29558,7 +29585,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="24" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>2</v>
@@ -29569,7 +29596,7 @@
         <v/>
       </c>
       <c r="K20" s="24" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>2</v>
@@ -29599,19 +29626,19 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="24" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G25" s="25" t="str">
         <f>A25</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q25" s="25" t="str">
         <f>K25</f>
@@ -29625,18 +29652,18 @@
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" ref="B26:B43" si="13">IF(F26&lt;&gt;"",CONCATENATE(A26,F26,C26),"")</f>
-        <v>&lt;li&gt;Ir al repositorio en GitHub.&lt;/li&gt;</v>
+        <v>&lt;li&gt;Si se usa sin argumentos, muestra todos los comandos almacenados en el historial.&lt;/li&gt;</v>
       </c>
       <c r="C26" s="24" t="str">
         <f t="shared" ref="C26:C43" si="14">IF(F26&lt;&gt;"","&lt;/li&gt;","")</f>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G26" s="25" t="str">
         <f t="shared" ref="G26:G44" si="15">IF(F26&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F25&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;Ir al repositorio en GitHub.</v>
+        <v>&lt;li&gt;Si se usa sin argumentos, muestra todos los comandos almacenados en el historial.</v>
       </c>
       <c r="K26" s="24" t="str">
         <f t="shared" ref="K26:K42" si="16">IF(P26&lt;&gt;"",$A$20,"")</f>
@@ -29671,18 +29698,18 @@
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;Ir a la pestaña Settings.&lt;/li&gt;</v>
+        <v>&lt;li&gt;n permite limitar la cantidad de comandos mostrados.&lt;/li&gt;</v>
       </c>
       <c r="C27" s="24" t="str">
         <f t="shared" si="14"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G27" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;li&gt;Ir a la pestaña Settings.</v>
+        <v>&lt;li&gt;n permite limitar la cantidad de comandos mostrados.</v>
       </c>
       <c r="K27" s="24" t="str">
         <f t="shared" si="16"/>
@@ -29713,22 +29740,20 @@
     <row r="28" spans="1:17">
       <c r="A28" s="24" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;li&gt;</v>
+        <v/>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;En la sección Branches, cambiar la rama principal a nueva-rama.&lt;/li&gt;</v>
+        <v/>
       </c>
       <c r="C28" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>&lt;/li&gt;</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>185</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F28" s="26"/>
       <c r="G28" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;li&gt;En la sección Branches, cambiar la rama principal a nueva-rama.</v>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K28" s="24" t="str">
         <f t="shared" si="16"/>
@@ -29759,22 +29784,20 @@
     <row r="29" spans="1:17">
       <c r="A29" s="24" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;li&gt;</v>
+        <v/>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;(Opcional) Eliminar la rama anterior si ya no se necesita.&lt;/li&gt;</v>
+        <v/>
       </c>
       <c r="C29" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>&lt;/li&gt;</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>186</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F29" s="26"/>
       <c r="G29" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;li&gt;(Opcional) Eliminar la rama anterior si ya no se necesita.</v>
+        <v/>
       </c>
       <c r="K29" s="24" t="str">
         <f t="shared" si="16"/>
@@ -29818,7 +29841,7 @@
       <c r="F30" s="26"/>
       <c r="G30" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;/ul&gt;</v>
+        <v/>
       </c>
       <c r="K30" s="24" t="str">
         <f t="shared" si="16"/>
@@ -30419,7 +30442,7 @@
         <v/>
       </c>
       <c r="K43" s="24" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L43" s="24" t="s">
         <v>2</v>
@@ -30499,7 +30522,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="23" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -30526,27 +30549,27 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -30561,7 +30584,7 @@
         <v>https://eduardoherreraf.github.io/</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -30583,7 +30606,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="16"/>
@@ -30603,21 +30626,21 @@
     </row>
     <row r="9" ht="15.75" spans="1:3">
       <c r="A9" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20"/>
     </row>
     <row r="10" ht="16.5" spans="1:3">
       <c r="A10" s="21" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -30632,7 +30655,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap.html</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -30654,7 +30677,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C14" s="17"/>
       <c r="E14" s="16"/>
@@ -30669,19 +30692,19 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
       <c r="A16" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -30696,7 +30719,7 @@
         <v>https://eduardoherreraf.github.io/git.html</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E18" s="16"/>
     </row>
@@ -30718,7 +30741,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C20" s="17"/>
       <c r="E20" s="16"/>
@@ -30733,19 +30756,19 @@
         <v>0.7</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
       <c r="A22" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20"/>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -30760,7 +30783,7 @@
         <v>https://eduardoherreraf.github.io/javascript.html</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E24" s="16"/>
     </row>
@@ -30782,7 +30805,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C26" s="17"/>
       <c r="E26" s="16"/>
@@ -30797,19 +30820,19 @@
         <v>0.7</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
       <c r="A28" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
     </row>
     <row r="29" ht="16.5" spans="1:3">
       <c r="A29" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -30824,7 +30847,7 @@
         <v>https://eduardoherreraf.github.io/photoshop.html</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E30" s="16"/>
     </row>
@@ -30846,7 +30869,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C32" s="17"/>
       <c r="E32" s="16"/>
@@ -30861,19 +30884,19 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
       <c r="A34" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
     </row>
     <row r="35" ht="16.5" spans="1:3">
       <c r="A35" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -30888,7 +30911,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas.html</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E36" s="16"/>
     </row>
@@ -30910,7 +30933,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C38" s="17"/>
       <c r="E38" s="16"/>
@@ -30925,19 +30948,19 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
       <c r="A40" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20"/>
     </row>
     <row r="41" ht="16.5" spans="1:3">
       <c r="A41" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -30952,7 +30975,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3.html</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E42" s="16"/>
     </row>
@@ -30974,7 +30997,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C44" s="17"/>
       <c r="E44" s="16"/>
@@ -30989,19 +31012,19 @@
         <v>0.7</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
       <c r="A46" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="20"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
       <c r="A47" s="21" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31009,7 +31032,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:3">
       <c r="A48" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -31024,7 +31047,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_parcel.html</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E49" s="16"/>
     </row>
@@ -31046,7 +31069,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C51" s="17"/>
       <c r="E51" s="16"/>
@@ -31061,19 +31084,19 @@
         <v>0.6</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
       <c r="A53" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
     </row>
     <row r="54" ht="16.5" spans="1:3">
       <c r="A54" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="12"/>
@@ -31088,7 +31111,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_vite.html</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E55" s="16"/>
     </row>
@@ -31110,7 +31133,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C57" s="17"/>
       <c r="E57" s="16"/>
@@ -31125,19 +31148,19 @@
         <v>0.6</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
       <c r="A59" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="21" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -31145,7 +31168,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:3">
       <c r="A61" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="12"/>
@@ -31160,7 +31183,7 @@
         <v>https://eduardoherreraf.github.io/git-01_como_eliminar_el_ultimo_commit_de_git.html</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E62" s="16"/>
     </row>
@@ -31182,7 +31205,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C64" s="17"/>
       <c r="E64" s="16"/>
@@ -31197,19 +31220,19 @@
         <v>0.6</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
       <c r="A66" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20"/>
     </row>
     <row r="67" ht="16.5" spans="1:3">
       <c r="A67" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="12"/>
@@ -31224,7 +31247,7 @@
         <v>https://eduardoherreraf.github.io/git-02_comandos_basicos_de_consola-terminal_cli_para_windows.html</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E68" s="16"/>
     </row>
@@ -31246,7 +31269,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C70" s="17"/>
       <c r="E70" s="16"/>
@@ -31261,19 +31284,19 @@
         <v>0.6</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
       <c r="A72" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="20"/>
     </row>
     <row r="73" ht="16.5" spans="1:3">
       <c r="A73" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
@@ -31288,7 +31311,7 @@
         <v>https://eduardoherreraf.github.io/git-03_introduccion_de_git_para_windows.html</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E74" s="16"/>
     </row>
@@ -31310,7 +31333,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C76" s="17"/>
       <c r="E76" s="16"/>
@@ -31325,19 +31348,19 @@
         <v>0.6</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
       <c r="A78" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
     </row>
     <row r="79" ht="16.5" spans="1:3">
       <c r="A79" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="12"/>
@@ -31352,7 +31375,7 @@
         <v>https://eduardoherreraf.github.io/git-04_configuracion_inicial_git.html</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E80" s="16"/>
     </row>
@@ -31374,7 +31397,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C82" s="17"/>
       <c r="E82" s="16"/>
@@ -31389,19 +31412,19 @@
         <v>0.6</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
       <c r="A84" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="20"/>
     </row>
     <row r="85" ht="16.5" spans="1:3">
       <c r="A85" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
@@ -31437,7 +31460,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C88" s="17"/>
       <c r="E88" s="16"/>
@@ -31452,27 +31475,27 @@
         <v>0.6</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E89" s="16"/>
     </row>
     <row r="90" ht="15.75" spans="1:3">
       <c r="A90" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20"/>
     </row>
     <row r="91" ht="16.5" spans="1:3">
       <c r="A91" s="21" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B91" s="21"/>
       <c r="C91" s="21"/>
     </row>
     <row r="92" ht="16.5" spans="1:3">
       <c r="A92" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
@@ -31487,7 +31510,7 @@
         <v>https://eduardoherreraf.github.io/javascript-como_ejecutar_un_codigo_javascript.html</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E93" s="16"/>
     </row>
@@ -31509,7 +31532,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C95" s="17"/>
       <c r="E95" s="16"/>
@@ -31524,19 +31547,19 @@
         <v>0.6</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
       <c r="A97" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="20"/>
     </row>
     <row r="98" ht="16.5" spans="1:3">
       <c r="A98" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
@@ -31551,7 +31574,7 @@
         <v>https://eduardoherreraf.github.io/javascript-configurar_el_entorno_de_trabajo_javascript.html</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -31572,7 +31595,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C101" s="17"/>
       <c r="E101" s="16"/>
@@ -31587,27 +31610,27 @@
         <v>0.6</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E102" s="16"/>
     </row>
     <row r="103" ht="15.75" spans="1:3">
       <c r="A103" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20"/>
     </row>
     <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="21" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="21"/>
     </row>
     <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="12"/>
@@ -31622,7 +31645,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-16_metadatos_y_exportacion.html</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E106" s="16"/>
     </row>
@@ -31644,7 +31667,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C108" s="17"/>
       <c r="E108" s="16"/>
@@ -31659,19 +31682,19 @@
         <v>0.6</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" ht="15.75" spans="1:3">
       <c r="A110" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="20"/>
     </row>
     <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="12"/>
@@ -31686,7 +31709,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-15_filtros_licuar.html</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E112" s="16"/>
     </row>
@@ -31708,7 +31731,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C114" s="17"/>
       <c r="E114" s="16"/>
@@ -31723,19 +31746,19 @@
         <v>0.6</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" ht="15.75" spans="1:3">
       <c r="A116" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B116" s="19"/>
       <c r="C116" s="20"/>
     </row>
     <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="12"/>
@@ -31750,7 +31773,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-14_filtros_neurales.html</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E118" s="16"/>
     </row>
@@ -31772,7 +31795,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C120" s="17"/>
       <c r="E120" s="16"/>
@@ -31787,19 +31810,19 @@
         <v>0.6</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" ht="15.75" spans="1:3">
       <c r="A122" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="20"/>
     </row>
     <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="12"/>
@@ -31814,7 +31837,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-13_filtros.html</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E124" s="16"/>
     </row>
@@ -31836,7 +31859,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C126" s="17"/>
       <c r="E126" s="16"/>
@@ -31851,19 +31874,19 @@
         <v>0.6</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" ht="15.75" spans="1:3">
       <c r="A128" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B128" s="19"/>
       <c r="C128" s="20"/>
     </row>
     <row r="129" ht="16.5" spans="1:3">
       <c r="A129" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="12"/>
@@ -31878,7 +31901,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-12_formas_y_capas.html</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E130" s="16"/>
     </row>
@@ -31900,7 +31923,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C132" s="17"/>
       <c r="E132" s="16"/>
@@ -31915,19 +31938,19 @@
         <v>0.6</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:3">
       <c r="A134" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="20"/>
     </row>
     <row r="135" ht="16.5" spans="1:3">
       <c r="A135" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="12"/>
@@ -31942,7 +31965,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-11_textos.html</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E136" s="16"/>
     </row>
@@ -31964,7 +31987,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C138" s="17"/>
       <c r="E138" s="16"/>
@@ -31979,19 +32002,19 @@
         <v>0.6</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:3">
       <c r="A140" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="20"/>
     </row>
     <row r="141" ht="16.5" spans="1:3">
       <c r="A141" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="12"/>
@@ -32006,7 +32029,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-10_color_y_degradados.html</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E142" s="16"/>
     </row>
@@ -32028,7 +32051,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C144" s="17"/>
       <c r="E144" s="16"/>
@@ -32043,19 +32066,19 @@
         <v>0.6</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:3">
       <c r="A146" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B146" s="19"/>
       <c r="C146" s="20"/>
     </row>
     <row r="147" ht="16.5" spans="1:3">
       <c r="A147" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="12"/>
@@ -32070,7 +32093,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-09_uso_de_pinceles.html</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E148" s="16"/>
     </row>
@@ -32092,7 +32115,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C150" s="17"/>
       <c r="E150" s="16"/>
@@ -32107,19 +32130,19 @@
         <v>0.6</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="152" ht="15.75" spans="1:3">
       <c r="A152" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="20"/>
     </row>
     <row r="153" ht="16.5" spans="1:3">
       <c r="A153" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="12"/>
@@ -32134,7 +32157,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-08_agregar_y_quitar_objetos.html</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E154" s="16"/>
     </row>
@@ -32156,7 +32179,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C156" s="17"/>
       <c r="E156" s="16"/>
@@ -32171,19 +32194,19 @@
         <v>0.6</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="158" ht="15.75" spans="1:3">
       <c r="A158" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B158" s="19"/>
       <c r="C158" s="20"/>
     </row>
     <row r="159" ht="16.5" spans="1:3">
       <c r="A159" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="12"/>
@@ -32198,7 +32221,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-07_herramientas_de_seleccion.html</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E160" s="16"/>
     </row>
@@ -32220,7 +32243,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C162" s="17"/>
       <c r="E162" s="16"/>
@@ -32235,19 +32258,19 @@
         <v>0.6</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" ht="15.75" spans="1:3">
       <c r="A164" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="20"/>
     </row>
     <row r="165" ht="16.5" spans="1:3">
       <c r="A165" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="12"/>
@@ -32262,7 +32285,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-06_ajuste_tono_brillo_y_saturacion.html</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E166" s="16"/>
     </row>
@@ -32284,7 +32307,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C168" s="17"/>
       <c r="E168" s="16"/>
@@ -32299,19 +32322,19 @@
         <v>0.6</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" ht="15.75" spans="1:3">
       <c r="A170" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B170" s="19"/>
       <c r="C170" s="20"/>
     </row>
     <row r="171" ht="16.5" spans="1:3">
       <c r="A171" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="12"/>
@@ -32326,7 +32349,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-05_trabajo_con_capas.html</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E172" s="16"/>
     </row>
@@ -32348,7 +32371,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C174" s="17"/>
       <c r="E174" s="16"/>
@@ -32363,19 +32386,19 @@
         <v>0.6</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="176" ht="15.75" spans="1:3">
       <c r="A176" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B176" s="19"/>
       <c r="C176" s="20"/>
     </row>
     <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="12"/>
@@ -32390,7 +32413,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-04_ajuste_lienzo_resolucion.html</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E178" s="16"/>
     </row>
@@ -32412,7 +32435,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C180" s="17"/>
       <c r="E180" s="16"/>
@@ -32427,19 +32450,19 @@
         <v>0.6</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="182" ht="15.75" spans="1:3">
       <c r="A182" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="20"/>
     </row>
     <row r="183" ht="16.5" spans="1:3">
       <c r="A183" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="12"/>
@@ -32454,7 +32477,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-03_compartir_y_editar_archivos.html</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E184" s="16"/>
     </row>
@@ -32476,7 +32499,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C186" s="17"/>
       <c r="E186" s="16"/>
@@ -32491,19 +32514,19 @@
         <v>0.6</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" ht="15.75" spans="1:3">
       <c r="A188" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B188" s="19"/>
       <c r="C188" s="20"/>
     </row>
     <row r="189" ht="16.5" spans="1:3">
       <c r="A189" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="12"/>
@@ -32518,7 +32541,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-02_interfaz_y_area_de_trabajo.html</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E190" s="16"/>
     </row>
@@ -32540,7 +32563,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C192" s="17"/>
       <c r="E192" s="16"/>
@@ -32555,19 +32578,19 @@
         <v>0.6</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" ht="15.75" spans="1:3">
       <c r="A194" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B194" s="19"/>
       <c r="C194" s="20"/>
     </row>
     <row r="195" ht="16.5" spans="1:3">
       <c r="A195" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="12"/>
@@ -32582,7 +32605,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-01_comenzando_un_proyecto.html</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -32603,7 +32626,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C198" s="17"/>
       <c r="E198" s="16"/>
@@ -32618,27 +32641,27 @@
         <v>0.6</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E199" s="16"/>
     </row>
     <row r="200" ht="15.75" spans="1:3">
       <c r="A200" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B200" s="19"/>
       <c r="C200" s="20"/>
     </row>
     <row r="201" ht="16.5" spans="1:3">
       <c r="A201" s="21" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B201" s="21"/>
       <c r="C201" s="21"/>
     </row>
     <row r="202" ht="16.5" spans="1:3">
       <c r="A202" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="12"/>
@@ -32653,7 +32676,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E203" s="16"/>
     </row>
@@ -32675,7 +32698,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C205" s="17"/>
       <c r="E205" s="16"/>
@@ -32690,19 +32713,19 @@
         <v>0.6</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="207" ht="15.75" spans="1:3">
       <c r="A207" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B207" s="19"/>
       <c r="C207" s="20"/>
     </row>
     <row r="208" ht="16.5" spans="1:3">
       <c r="A208" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="12"/>
@@ -32717,7 +32740,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_borrar_la_cache_y_archivos_basura_en_windows.html</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -32738,7 +32761,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C211" s="17"/>
       <c r="E211" s="16"/>
@@ -32753,27 +32776,27 @@
         <v>0.6</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E212" s="16"/>
     </row>
     <row r="213" ht="15.75" spans="1:3">
       <c r="A213" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B213" s="19"/>
       <c r="C213" s="20"/>
     </row>
     <row r="214" ht="16.5" spans="1:3">
       <c r="A214" s="21" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B214" s="21"/>
       <c r="C214" s="21"/>
     </row>
     <row r="215" ht="16.5" spans="1:3">
       <c r="A215" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="12"/>
@@ -32788,7 +32811,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0101_introduccion.html</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E216" s="16"/>
     </row>
@@ -32810,7 +32833,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C218" s="17"/>
       <c r="E218" s="16"/>
@@ -32825,19 +32848,19 @@
         <v>0.6</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="220" ht="15.75" spans="1:3">
       <c r="A220" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B220" s="19"/>
       <c r="C220" s="20"/>
     </row>
     <row r="221" ht="16.5" spans="1:3">
       <c r="A221" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="12"/>
@@ -32852,7 +32875,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0102_instalacion_de_python_localmente.html</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E222" s="16"/>
     </row>
@@ -32874,7 +32897,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C224" s="17"/>
       <c r="E224" s="16"/>
@@ -32889,19 +32912,19 @@
         <v>0.6</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="226" ht="15.75" spans="1:3">
       <c r="A226" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B226" s="19"/>
       <c r="C226" s="20"/>
     </row>
     <row r="227" ht="16.5" spans="1:3">
       <c r="A227" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="12"/>
@@ -32916,7 +32939,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0201_funcion_print.html</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E228" s="16"/>
     </row>
@@ -32938,7 +32961,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C230" s="17"/>
       <c r="E230" s="16"/>
@@ -32953,19 +32976,19 @@
         <v>0.6</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="232" ht="15.75" spans="1:3">
       <c r="A232" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B232" s="19"/>
       <c r="C232" s="20"/>
     </row>
     <row r="233" ht="16.5" spans="1:3">
       <c r="A233" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B233" s="11"/>
       <c r="C233" s="12"/>
@@ -32980,7 +33003,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0202_literales.html</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E234" s="16"/>
     </row>
@@ -33002,7 +33025,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C236" s="17"/>
       <c r="E236" s="16"/>
@@ -33017,19 +33040,19 @@
         <v>0.6</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="238" ht="15.75" spans="1:3">
       <c r="A238" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="20"/>
     </row>
     <row r="239" ht="16.5" spans="1:3">
       <c r="A239" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B239" s="11"/>
       <c r="C239" s="12"/>
@@ -33044,7 +33067,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0203_operadores.html</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E240" s="16"/>
     </row>
@@ -33066,7 +33089,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C242" s="17"/>
       <c r="E242" s="16"/>
@@ -33081,19 +33104,19 @@
         <v>0.6</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="244" ht="15.75" spans="1:3">
       <c r="A244" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B244" s="19"/>
       <c r="C244" s="20"/>
     </row>
     <row r="245" ht="16.5" spans="1:3">
       <c r="A245" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B245" s="11"/>
       <c r="C245" s="12"/>
@@ -33108,7 +33131,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0204_variables.html</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E246" s="16"/>
     </row>
@@ -33130,7 +33153,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C248" s="17"/>
       <c r="E248" s="16"/>
@@ -33145,19 +33168,19 @@
         <v>0.6</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="250" ht="15.75" spans="1:3">
       <c r="A250" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B250" s="19"/>
       <c r="C250" s="20"/>
     </row>
     <row r="251" ht="16.5" spans="1:3">
       <c r="A251" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B251" s="11"/>
       <c r="C251" s="12"/>
@@ -33172,7 +33195,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0205_comentarios.html</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E252" s="16"/>
     </row>
@@ -33194,7 +33217,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C254" s="17"/>
       <c r="E254" s="16"/>
@@ -33209,19 +33232,19 @@
         <v>0.6</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="256" ht="15.75" spans="1:3">
       <c r="A256" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B256" s="19"/>
       <c r="C256" s="20"/>
     </row>
     <row r="257" ht="16.5" spans="1:3">
       <c r="A257" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="12"/>
@@ -33236,7 +33259,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0206_interaccion_con_el_usuario.html</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E258" s="16"/>
     </row>
@@ -33258,7 +33281,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C260" s="17"/>
       <c r="E260" s="16"/>
@@ -33273,19 +33296,19 @@
         <v>0.6</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="262" ht="15.75" spans="1:3">
       <c r="A262" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B262" s="19"/>
       <c r="C262" s="20"/>
     </row>
     <row r="263" ht="16.5" spans="1:3">
       <c r="A263" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="12"/>
@@ -33300,7 +33323,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0301_operadores_de_comparacion_y_logicos_en_python.html</v>
       </c>
       <c r="C264" s="15" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E264" s="16"/>
     </row>
@@ -33322,7 +33345,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B266" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C266" s="17"/>
       <c r="E266" s="16"/>
@@ -33337,19 +33360,19 @@
         <v>0.6</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" ht="15.75" spans="1:3">
       <c r="A268" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B268" s="19"/>
       <c r="C268" s="20"/>
     </row>
     <row r="269" ht="16.5" spans="1:3">
       <c r="A269" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B269" s="11"/>
       <c r="C269" s="12"/>
@@ -33364,7 +33387,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0302_sentencia_if_de_control_de_flujo.html</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E270" s="16"/>
     </row>
@@ -33386,7 +33409,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B272" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C272" s="17"/>
       <c r="E272" s="16"/>
@@ -33401,19 +33424,19 @@
         <v>0.6</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="274" ht="15.75" spans="1:3">
       <c r="A274" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B274" s="19"/>
       <c r="C274" s="20"/>
     </row>
     <row r="275" ht="16.5" spans="1:3">
       <c r="A275" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B275" s="11"/>
       <c r="C275" s="12"/>
@@ -33428,7 +33451,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0303_bucles_en_python_una_guia_completa.html</v>
       </c>
       <c r="C276" s="15" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E276" s="16"/>
     </row>
@@ -33450,7 +33473,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C278" s="17"/>
       <c r="E278" s="16"/>
@@ -33465,19 +33488,19 @@
         <v>0.6</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" ht="15.75" spans="1:3">
       <c r="A280" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B280" s="19"/>
       <c r="C280" s="20"/>
     </row>
     <row r="281" ht="16.5" spans="1:3">
       <c r="A281" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B281" s="11"/>
       <c r="C281" s="12"/>
@@ -33492,7 +33515,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0304_operadores_logicos_y_operaciones_bit_a_bit_en_python.html</v>
       </c>
       <c r="C282" s="15" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E282" s="16"/>
     </row>
@@ -33514,7 +33537,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C284" s="17"/>
       <c r="E284" s="16"/>
@@ -33529,19 +33552,19 @@
         <v>0.6</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="286" ht="15.75" spans="1:3">
       <c r="A286" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B286" s="19"/>
       <c r="C286" s="20"/>
     </row>
     <row r="287" ht="16.5" spans="1:3">
       <c r="A287" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B287" s="11"/>
       <c r="C287" s="12"/>
@@ -33556,7 +33579,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0305_listas.html</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E288" s="16"/>
     </row>
@@ -33578,7 +33601,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B290" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C290" s="17"/>
       <c r="E290" s="16"/>
@@ -33593,19 +33616,19 @@
         <v>0.6</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="292" ht="15.75" spans="1:3">
       <c r="A292" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B292" s="19"/>
       <c r="C292" s="20"/>
     </row>
     <row r="293" ht="16.5" spans="1:3">
       <c r="A293" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B293" s="11"/>
       <c r="C293" s="12"/>
@@ -33620,7 +33643,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0306_ordenamiento_de_listas_metodo_burbuja.html</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E294" s="16"/>
     </row>
@@ -33642,7 +33665,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C296" s="17"/>
       <c r="E296" s="16"/>
@@ -33657,19 +33680,19 @@
         <v>0.6</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="298" ht="15.75" spans="1:3">
       <c r="A298" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B298" s="19"/>
       <c r="C298" s="20"/>
     </row>
     <row r="299" ht="16.5" spans="1:3">
       <c r="A299" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B299" s="11"/>
       <c r="C299" s="12"/>
@@ -33684,7 +33707,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0307_operaciones_con_listas.html</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E300" s="16"/>
     </row>
@@ -33706,7 +33729,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C302" s="17"/>
       <c r="E302" s="16"/>
@@ -33721,19 +33744,19 @@
         <v>0.6</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="304" ht="15.75" spans="1:3">
       <c r="A304" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B304" s="19"/>
       <c r="C304" s="20"/>
     </row>
     <row r="305" ht="16.5" spans="1:3">
       <c r="A305" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B305" s="11"/>
       <c r="C305" s="12"/>
@@ -33748,7 +33771,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0401_introduccion_funciones.html</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E306" s="16"/>
     </row>
@@ -33770,7 +33793,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C308" s="17"/>
       <c r="E308" s="16"/>
@@ -33785,19 +33808,19 @@
         <v>0.6</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="310" ht="15.75" spans="1:3">
       <c r="A310" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B310" s="19"/>
       <c r="C310" s="20"/>
     </row>
     <row r="311" ht="16.5" spans="1:3">
       <c r="A311" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B311" s="11"/>
       <c r="C311" s="12"/>
@@ -33812,7 +33835,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0402_como_las_funciones_se_comunican_con_su_entorno.html</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E312" s="16"/>
     </row>
@@ -33834,7 +33857,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B314" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C314" s="17"/>
       <c r="E314" s="16"/>
@@ -33849,19 +33872,19 @@
         <v>0.6</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="316" ht="15.75" spans="1:3">
       <c r="A316" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B316" s="19"/>
       <c r="C316" s="20"/>
     </row>
     <row r="317" ht="16.5" spans="1:3">
       <c r="A317" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B317" s="11"/>
       <c r="C317" s="12"/>
@@ -33876,7 +33899,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0403_retorno_de_valores_en_funciones.html</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E318" s="16"/>
     </row>
@@ -33898,7 +33921,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B320" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C320" s="17"/>
       <c r="E320" s="16"/>
@@ -33913,19 +33936,19 @@
         <v>0.6</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="322" ht="15.75" spans="1:3">
       <c r="A322" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B322" s="19"/>
       <c r="C322" s="20"/>
     </row>
     <row r="323" ht="16.5" spans="1:3">
       <c r="A323" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B323" s="11"/>
       <c r="C323" s="12"/>
@@ -33940,7 +33963,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0404_el_alcance_de_las_variables.html</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E324" s="16"/>
     </row>
@@ -33962,7 +33985,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B326" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C326" s="17"/>
       <c r="E326" s="16"/>
@@ -33977,19 +34000,19 @@
         <v>0.6</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="328" ht="15.75" spans="1:3">
       <c r="A328" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B328" s="19"/>
       <c r="C328" s="20"/>
     </row>
     <row r="329" ht="16.5" spans="1:3">
       <c r="A329" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="12"/>
@@ -34004,7 +34027,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0405_tuplas_y_diccionarios.html</v>
       </c>
       <c r="C330" s="15" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E330" s="16"/>
     </row>
@@ -34026,7 +34049,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B332" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C332" s="17"/>
       <c r="E332" s="16"/>
@@ -34041,19 +34064,19 @@
         <v>0.6</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="334" ht="15.75" spans="1:3">
       <c r="A334" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B334" s="19"/>
       <c r="C334" s="20"/>
     </row>
     <row r="335" ht="16.5" spans="1:3">
       <c r="A335" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B335" s="11"/>
       <c r="C335" s="12"/>
@@ -34068,7 +34091,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0501_introduccion_a_los_modulos.html</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E336" s="16"/>
     </row>
@@ -34090,7 +34113,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B338" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C338" s="17"/>
       <c r="E338" s="16"/>
@@ -34105,19 +34128,19 @@
         <v>0.6</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="340" ht="15.75" spans="1:3">
       <c r="A340" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B340" s="19"/>
       <c r="C340" s="20"/>
     </row>
     <row r="341" ht="16.5" spans="1:3">
       <c r="A341" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B341" s="11"/>
       <c r="C341" s="12"/>
@@ -34132,7 +34155,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0502_importacion_de_modulos.html</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E342" s="16"/>
     </row>
@@ -34154,7 +34177,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B344" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C344" s="17"/>
       <c r="E344" s="16"/>
@@ -34169,19 +34192,19 @@
         <v>0.6</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="346" ht="15.75" spans="1:3">
       <c r="A346" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B346" s="19"/>
       <c r="C346" s="20"/>
     </row>
     <row r="347" ht="16.5" spans="1:3">
       <c r="A347" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B347" s="11"/>
       <c r="C347" s="12"/>
@@ -34196,7 +34219,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0503_modulos_especializados_de_python-matematico_aleatorio_y_de_sistema.html</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E348" s="16"/>
     </row>
@@ -34218,7 +34241,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B350" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C350" s="17"/>
       <c r="E350" s="16"/>
@@ -34233,19 +34256,19 @@
         <v>0.6</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="352" ht="15.75" spans="1:3">
       <c r="A352" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B352" s="19"/>
       <c r="C352" s="20"/>
     </row>
     <row r="353" ht="16.5" spans="1:3">
       <c r="A353" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B353" s="11"/>
       <c r="C353" s="12"/>
@@ -34260,7 +34283,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0504_modulos_y_paquetes.html</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E354" s="16"/>
     </row>
@@ -34282,7 +34305,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B356" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C356" s="17"/>
       <c r="E356" s="16"/>
@@ -34297,19 +34320,19 @@
         <v>0.6</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="358" ht="15.75" spans="1:3">
       <c r="A358" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B358" s="19"/>
       <c r="C358" s="20"/>
     </row>
     <row r="359" ht="16.5" spans="1:3">
       <c r="A359" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B359" s="11"/>
       <c r="C359" s="12"/>
@@ -34324,7 +34347,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0505_instalador_de_paquetes_PIP.html</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E360" s="16"/>
     </row>
@@ -34346,7 +34369,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B362" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C362" s="17"/>
       <c r="E362" s="16"/>
@@ -34361,19 +34384,19 @@
         <v>0.6</v>
       </c>
       <c r="C363" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="364" ht="15.75" spans="1:3">
       <c r="A364" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B364" s="19"/>
       <c r="C364" s="20"/>
     </row>
     <row r="365" ht="16.5" spans="1:3">
       <c r="A365" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B365" s="11"/>
       <c r="C365" s="12"/>
@@ -34388,7 +34411,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0601_la_naturaleza_de_las_cadenas.html</v>
       </c>
       <c r="C366" s="15" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E366" s="16"/>
     </row>
@@ -34410,7 +34433,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C368" s="17"/>
       <c r="E368" s="16"/>
@@ -34425,19 +34448,19 @@
         <v>0.6</v>
       </c>
       <c r="C369" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="370" ht="15.75" spans="1:3">
       <c r="A370" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B370" s="19"/>
       <c r="C370" s="20"/>
     </row>
     <row r="371" ht="16.5" spans="1:3">
       <c r="A371" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B371" s="11"/>
       <c r="C371" s="12"/>
@@ -34452,7 +34475,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0602_errores-el_pan_diario_del_programador.html</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E372" s="16"/>
     </row>
@@ -34474,7 +34497,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C374" s="17"/>
       <c r="E374" s="16"/>
@@ -34489,19 +34512,19 @@
         <v>0.6</v>
       </c>
       <c r="C375" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="376" ht="15.75" spans="1:3">
       <c r="A376" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B376" s="19"/>
       <c r="C376" s="20"/>
     </row>
     <row r="377" ht="16.5" spans="1:3">
       <c r="A377" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B377" s="11"/>
       <c r="C377" s="12"/>
@@ -34516,7 +34539,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0701_los_fundamentos_de_la_poo.html</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E378" s="16"/>
     </row>
@@ -34538,7 +34561,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C380" s="17"/>
       <c r="E380" s="16"/>
@@ -34553,19 +34576,19 @@
         <v>0.6</v>
       </c>
       <c r="C381" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="382" ht="15.75" spans="1:3">
       <c r="A382" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B382" s="19"/>
       <c r="C382" s="20"/>
     </row>
     <row r="383" ht="16.5" spans="1:3">
       <c r="A383" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B383" s="11"/>
       <c r="C383" s="12"/>
@@ -34580,7 +34603,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0702_comparando_paradigmas_programacion_procedimental_y_orientada_a_objetos.html</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E384" s="16"/>
     </row>
@@ -34602,7 +34625,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C386" s="17"/>
       <c r="E386" s="16"/>
@@ -34617,19 +34640,19 @@
         <v>0.6</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="388" ht="15.75" spans="1:3">
       <c r="A388" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B388" s="19"/>
       <c r="C388" s="20"/>
     </row>
     <row r="389" ht="16.5" spans="1:3">
       <c r="A389" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B389" s="11"/>
       <c r="C389" s="12"/>
@@ -34644,7 +34667,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0703_poo_propiedades.html</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E390" s="16"/>
     </row>
@@ -34666,7 +34689,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C392" s="17"/>
       <c r="E392" s="16"/>
@@ -34681,19 +34704,19 @@
         <v>0.6</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="394" ht="15.75" spans="1:3">
       <c r="A394" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="20"/>
     </row>
     <row r="395" ht="16.5" spans="1:3">
       <c r="A395" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="12"/>
@@ -34708,7 +34731,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0704_poo_metodos.html</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E396" s="16"/>
     </row>
@@ -34730,7 +34753,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C398" s="17"/>
       <c r="E398" s="16"/>
@@ -34745,19 +34768,19 @@
         <v>0.6</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="400" ht="15.75" spans="1:3">
       <c r="A400" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B400" s="19"/>
       <c r="C400" s="20"/>
     </row>
     <row r="401" ht="16.5" spans="1:3">
       <c r="A401" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B401" s="11"/>
       <c r="C401" s="12"/>
@@ -34772,7 +34795,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0705_poo_herencia.html</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E402" s="16"/>
     </row>
@@ -34794,7 +34817,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C404" s="17"/>
       <c r="E404" s="16"/>
@@ -34809,19 +34832,19 @@
         <v>0.6</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="406" ht="15.75" spans="1:3">
       <c r="A406" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B406" s="19"/>
       <c r="C406" s="20"/>
     </row>
     <row r="407" ht="16.5" spans="1:3">
       <c r="A407" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B407" s="11"/>
       <c r="C407" s="12"/>
@@ -34836,7 +34859,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0706_poo_excepciones.html</v>
       </c>
       <c r="C408" s="15" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E408" s="16"/>
     </row>
@@ -34858,7 +34881,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C410" s="17"/>
       <c r="E410" s="16"/>
@@ -34873,19 +34896,19 @@
         <v>0.6</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="412" ht="15.75" spans="1:3">
       <c r="A412" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B412" s="19"/>
       <c r="C412" s="20"/>
     </row>
     <row r="413" ht="16.5" spans="1:3">
       <c r="A413" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="12"/>
@@ -34900,7 +34923,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0801_iteradores,_generadores_y_cierres.html</v>
       </c>
       <c r="C414" s="15" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E414" s="16"/>
     </row>
@@ -34922,7 +34945,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C416" s="17"/>
       <c r="E416" s="16"/>
@@ -34937,19 +34960,19 @@
         <v>0.6</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="418" ht="15.75" spans="1:3">
       <c r="A418" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B418" s="19"/>
       <c r="C418" s="20"/>
     </row>
     <row r="419" ht="16.5" spans="1:3">
       <c r="A419" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="12"/>
@@ -34964,7 +34987,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0802_manejo_de_archivos.html</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E420" s="16"/>
     </row>
@@ -34986,7 +35009,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C422" s="17"/>
       <c r="E422" s="16"/>
@@ -35001,19 +35024,19 @@
         <v>0.6</v>
       </c>
       <c r="C423" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="424" ht="15.75" spans="1:3">
       <c r="A424" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B424" s="19"/>
       <c r="C424" s="20"/>
     </row>
     <row r="425" ht="16.5" spans="1:3">
       <c r="A425" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="12"/>
@@ -35028,7 +35051,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0803_el_modulo_os_interactuando_con_el_sistema_operativo.html</v>
       </c>
       <c r="C426" s="15" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E426" s="16"/>
     </row>
@@ -35050,7 +35073,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C428" s="17"/>
       <c r="E428" s="16"/>
@@ -35065,19 +35088,19 @@
         <v>0.6</v>
       </c>
       <c r="C429" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="430" ht="15.75" spans="1:3">
       <c r="A430" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B430" s="19"/>
       <c r="C430" s="20"/>
     </row>
     <row r="431" ht="16.5" spans="1:3">
       <c r="A431" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="12"/>
@@ -35092,7 +35115,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html</v>
       </c>
       <c r="C432" s="15" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E432" s="16"/>
     </row>
@@ -35114,7 +35137,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C434" s="17"/>
       <c r="E434" s="16"/>
@@ -35129,19 +35152,19 @@
         <v>0.6</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="436" ht="15.75" spans="1:3">
       <c r="A436" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B436" s="19"/>
       <c r="C436" s="20"/>
     </row>
     <row r="437" ht="16.5" spans="1:3">
       <c r="A437" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="12"/>
@@ -35156,7 +35179,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html</v>
       </c>
       <c r="C438" s="15" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -35176,7 +35199,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C440" s="17"/>
     </row>
@@ -35190,19 +35213,19 @@
         <v>0.6</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="442" ht="15.75" spans="1:3">
       <c r="A442" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B442" s="19"/>
       <c r="C442" s="20"/>
     </row>
     <row r="443" ht="15.75" spans="1:3">
       <c r="A443" s="5" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C443" s="22"/>
     </row>
@@ -35492,13 +35515,13 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -35507,78 +35530,78 @@
         <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -35587,16 +35610,16 @@
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -35605,7 +35628,7 @@
         <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -35614,51 +35637,51 @@
         <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4"/>
       <c r="D20" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/src/Head.xlsx
+++ b/src/Head.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12450" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12450" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="312">
   <si>
     <t>Título</t>
   </si>
@@ -595,10 +595,16 @@
     <t>Título 4</t>
   </si>
   <si>
+    <t>Configuraciones Específicas de Color</t>
+  </si>
+  <si>
     <t>Título 5</t>
   </si>
   <si>
     <t>ff</t>
+  </si>
+  <si>
+    <t>Personalización Avanzada de Colores</t>
   </si>
   <si>
     <t>Alias para Manejar Ramas</t>
@@ -607,10 +613,16 @@
     <t>Título 6</t>
   </si>
   <si>
+    <t>Verificación de la Configuración</t>
+  </si>
+  <si>
     <t>Alias para Reiniciar y Limpiar Cambios</t>
   </si>
   <si>
     <t>Título 7</t>
+  </si>
+  <si>
+    <t>¿Cuándo es Necesario Ejecutar estos Comandos?</t>
   </si>
   <si>
     <t>Alias Avanzados</t>
@@ -668,6 +680,15 @@
   </si>
   <si>
     <t>&lt;ul&gt;</t>
+  </si>
+  <si>
+    <t>Después de instalar Git: Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.</t>
+  </si>
+  <si>
+    <t>Cuando se usa una computadora compartida: Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.</t>
+  </si>
+  <si>
+    <t>Al alternar entre identidades: Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.</t>
   </si>
   <si>
     <t>&lt;li&gt;&lt;span class="fw-bold"&gt;</t>
@@ -23707,11 +23728,13 @@
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="34" t="s">
+        <v>154</v>
+      </c>
       <c r="E26" s="33"/>
       <c r="F26" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Configuraciones Específicas de Color --&gt;</v>
       </c>
       <c r="G26" s="35"/>
       <c r="I26" s="32" t="s">
@@ -23761,7 +23784,7 @@
       <c r="A28" s="36"/>
       <c r="F28" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D26,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Configuraciones Específicas de Color&lt;/h3&gt;</v>
       </c>
       <c r="G28" s="39"/>
       <c r="I28" s="36"/>
@@ -23834,7 +23857,7 @@
       <c r="E32" s="31"/>
       <c r="F32" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Configuraciones Específicas de Color fin --&gt;</v>
       </c>
       <c r="G32" s="42"/>
       <c r="I32" s="41"/>
@@ -23870,26 +23893,28 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="34"/>
+        <v>156</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>157</v>
+      </c>
       <c r="E34" s="33"/>
       <c r="F34" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Personalización Avanzada de Colores --&gt;</v>
       </c>
       <c r="G34" s="35"/>
       <c r="I34" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J34" s="33"/>
       <c r="K34" s="33"/>
       <c r="L34" s="34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M34" s="33"/>
       <c r="N34" s="33" t="str">
@@ -23932,7 +23957,7 @@
       <c r="A36" s="36"/>
       <c r="F36" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D34,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Personalización Avanzada de Colores&lt;/h3&gt;</v>
       </c>
       <c r="G36" s="39"/>
       <c r="I36" s="36"/>
@@ -24002,7 +24027,7 @@
       <c r="E40" s="31"/>
       <c r="F40" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Personalización Avanzada de Colores fin --&gt;</v>
       </c>
       <c r="G40" s="42"/>
       <c r="I40" s="41"/>
@@ -24038,24 +24063,26 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B42" s="33"/>
       <c r="C42" s="33"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="34" t="s">
+        <v>160</v>
+      </c>
       <c r="E42" s="33"/>
       <c r="F42" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Verificación de la Configuración --&gt;</v>
       </c>
       <c r="G42" s="35"/>
       <c r="I42" s="32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J42" s="33"/>
       <c r="K42" s="33"/>
       <c r="L42" s="34" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" s="33"/>
       <c r="N42" s="33" t="str">
@@ -24098,7 +24125,7 @@
       <c r="A44" s="36"/>
       <c r="F44" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D42,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Verificación de la Configuración&lt;/h3&gt;</v>
       </c>
       <c r="G44" s="39"/>
       <c r="I44" s="36"/>
@@ -24168,7 +24195,7 @@
       <c r="E48" s="31"/>
       <c r="F48" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Verificación de la Configuración fin --&gt;</v>
       </c>
       <c r="G48" s="42"/>
       <c r="I48" s="41"/>
@@ -24204,26 +24231,28 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="32" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B50" s="33"/>
       <c r="C50" s="33"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="34" t="s">
+        <v>163</v>
+      </c>
       <c r="E50" s="33"/>
       <c r="F50" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- ¿Cuándo es Necesario Ejecutar estos Comandos? --&gt;</v>
       </c>
       <c r="G50" s="35"/>
       <c r="I50" s="32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J50" s="33"/>
       <c r="K50" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M50" s="33"/>
       <c r="N50" s="33" t="str">
@@ -24266,7 +24295,7 @@
       <c r="A52" s="36"/>
       <c r="F52" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D50,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;¿Cuándo es Necesario Ejecutar estos Comandos?&lt;/h3&gt;</v>
       </c>
       <c r="G52" s="39"/>
       <c r="I52" s="36"/>
@@ -24336,7 +24365,7 @@
       <c r="E56" s="31"/>
       <c r="F56" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- ¿Cuándo es Necesario Ejecutar estos Comandos? fin --&gt;</v>
       </c>
       <c r="G56" s="42"/>
       <c r="I56" s="41"/>
@@ -24372,7 +24401,7 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="32" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B58" s="33"/>
       <c r="C58" s="33"/>
@@ -24384,12 +24413,12 @@
       </c>
       <c r="G58" s="35"/>
       <c r="I58" s="32" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J58" s="33"/>
       <c r="K58" s="33"/>
       <c r="L58" s="34" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M58" s="33"/>
       <c r="N58" s="33" t="str">
@@ -24538,7 +24567,7 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="32" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B66" s="33"/>
       <c r="C66" s="33"/>
@@ -24550,7 +24579,7 @@
       </c>
       <c r="G66" s="35"/>
       <c r="I66" s="32" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J66" s="33"/>
       <c r="K66" s="33"/>
@@ -24702,7 +24731,7 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
@@ -24714,7 +24743,7 @@
       </c>
       <c r="G74" s="35"/>
       <c r="I74" s="32" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J74" s="33"/>
       <c r="K74" s="33"/>
@@ -24866,7 +24895,7 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B82" s="33"/>
       <c r="C82" s="33"/>
@@ -24878,7 +24907,7 @@
       </c>
       <c r="G82" s="35"/>
       <c r="I82" s="32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J82" s="33"/>
       <c r="K82" s="33"/>
@@ -25030,7 +25059,7 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -25042,7 +25071,7 @@
       </c>
       <c r="G90" s="35"/>
       <c r="I90" s="32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J90" s="33"/>
       <c r="K90" s="33"/>
@@ -25194,7 +25223,7 @@
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B98" s="33"/>
       <c r="C98" s="33"/>
@@ -25206,7 +25235,7 @@
       </c>
       <c r="G98" s="35"/>
       <c r="I98" s="32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J98" s="33"/>
       <c r="K98" s="33"/>
@@ -25358,7 +25387,7 @@
     </row>
     <row r="106" customFormat="1" spans="1:15">
       <c r="A106" s="32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B106" s="33"/>
       <c r="C106" s="33"/>
@@ -25370,7 +25399,7 @@
       </c>
       <c r="G106" s="35"/>
       <c r="I106" s="32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J106" s="33"/>
       <c r="K106" s="33"/>
@@ -25522,7 +25551,7 @@
     </row>
     <row r="114" customFormat="1" spans="1:15">
       <c r="A114" s="32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B114" s="33"/>
       <c r="C114" s="33"/>
@@ -25534,7 +25563,7 @@
       </c>
       <c r="G114" s="35"/>
       <c r="I114" s="32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J114" s="33"/>
       <c r="K114" s="33"/>
@@ -25686,7 +25715,7 @@
     </row>
     <row r="122" customFormat="1" spans="1:15">
       <c r="A122" s="32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B122" s="33"/>
       <c r="C122" s="33"/>
@@ -25698,7 +25727,7 @@
       </c>
       <c r="G122" s="35"/>
       <c r="I122" s="32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J122" s="33"/>
       <c r="K122" s="33"/>
@@ -25850,7 +25879,7 @@
     </row>
     <row r="130" customFormat="1" spans="1:15">
       <c r="A130" s="32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B130" s="33"/>
       <c r="C130" s="33"/>
@@ -25862,7 +25891,7 @@
       </c>
       <c r="G130" s="35"/>
       <c r="I130" s="32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J130" s="33"/>
       <c r="K130" s="33"/>
@@ -26014,7 +26043,7 @@
     </row>
     <row r="138" customFormat="1" spans="1:15">
       <c r="A138" s="32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B138" s="33"/>
       <c r="C138" s="33"/>
@@ -26026,7 +26055,7 @@
       </c>
       <c r="G138" s="35"/>
       <c r="I138" s="32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J138" s="33"/>
       <c r="K138" s="33"/>
@@ -26178,7 +26207,7 @@
     </row>
     <row r="146" customFormat="1" spans="1:15">
       <c r="A146" s="32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B146" s="33"/>
       <c r="C146" s="33"/>
@@ -26190,7 +26219,7 @@
       </c>
       <c r="G146" s="35"/>
       <c r="I146" s="32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J146" s="33"/>
       <c r="K146" s="33"/>
@@ -26342,7 +26371,7 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="32" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B154" s="33"/>
       <c r="C154" s="33"/>
@@ -26354,7 +26383,7 @@
       </c>
       <c r="G154" s="35"/>
       <c r="I154" s="32" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J154" s="33"/>
       <c r="K154" s="33"/>
@@ -26506,7 +26535,7 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B162" s="33"/>
       <c r="C162" s="33"/>
@@ -26518,7 +26547,7 @@
       </c>
       <c r="G162" s="35"/>
       <c r="I162" s="32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J162" s="33"/>
       <c r="K162" s="33"/>
@@ -26670,7 +26699,7 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B170" s="33"/>
       <c r="C170" s="33"/>
@@ -26682,7 +26711,7 @@
       </c>
       <c r="G170" s="35"/>
       <c r="I170" s="32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J170" s="33"/>
       <c r="K170" s="33"/>
@@ -26834,7 +26863,7 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B178" s="33"/>
       <c r="C178" s="33"/>
@@ -26846,7 +26875,7 @@
       </c>
       <c r="G178" s="35"/>
       <c r="I178" s="32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J178" s="33"/>
       <c r="K178" s="33"/>
@@ -26979,7 +27008,7 @@
     <row r="185" ht="15"/>
     <row r="186" spans="1:15">
       <c r="A186" s="32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B186" s="33"/>
       <c r="C186" s="33"/>
@@ -26991,7 +27020,7 @@
       </c>
       <c r="G186" s="35"/>
       <c r="I186" s="32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J186" s="33"/>
       <c r="K186" s="33"/>
@@ -27143,7 +27172,7 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B194" s="33"/>
       <c r="C194" s="33"/>
@@ -27155,7 +27184,7 @@
       </c>
       <c r="G194" s="35"/>
       <c r="I194" s="32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J194" s="33"/>
       <c r="K194" s="33"/>
@@ -27307,7 +27336,7 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B202" s="33"/>
       <c r="C202" s="33"/>
@@ -27319,7 +27348,7 @@
       </c>
       <c r="G202" s="35"/>
       <c r="I202" s="32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J202" s="33"/>
       <c r="K202" s="33"/>
@@ -27471,7 +27500,7 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B210" s="33"/>
       <c r="C210" s="33"/>
@@ -27483,7 +27512,7 @@
       </c>
       <c r="G210" s="35"/>
       <c r="I210" s="32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J210" s="33"/>
       <c r="K210" s="33"/>
@@ -27635,7 +27664,7 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B218" s="33"/>
       <c r="C218" s="33"/>
@@ -27647,7 +27676,7 @@
       </c>
       <c r="G218" s="35"/>
       <c r="I218" s="32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J218" s="33"/>
       <c r="K218" s="33"/>
@@ -27799,7 +27828,7 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B226" s="33"/>
       <c r="C226" s="33"/>
@@ -27811,7 +27840,7 @@
       </c>
       <c r="G226" s="35"/>
       <c r="I226" s="32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J226" s="33"/>
       <c r="K226" s="33"/>
@@ -27963,7 +27992,7 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="32" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B234" s="33"/>
       <c r="C234" s="33"/>
@@ -27975,7 +28004,7 @@
       </c>
       <c r="G234" s="35"/>
       <c r="I234" s="32" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J234" s="33"/>
       <c r="K234" s="33"/>
@@ -28127,7 +28156,7 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
@@ -28139,7 +28168,7 @@
       </c>
       <c r="G242" s="35"/>
       <c r="I242" s="32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J242" s="33"/>
       <c r="K242" s="33"/>
@@ -28291,7 +28320,7 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B250" s="33"/>
       <c r="C250" s="33"/>
@@ -28303,7 +28332,7 @@
       </c>
       <c r="G250" s="35"/>
       <c r="I250" s="32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J250" s="33"/>
       <c r="K250" s="33"/>
@@ -28455,7 +28484,7 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B258" s="33"/>
       <c r="C258" s="33"/>
@@ -28467,7 +28496,7 @@
       </c>
       <c r="G258" s="35"/>
       <c r="I258" s="32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J258" s="33"/>
       <c r="K258" s="33"/>
@@ -28622,19 +28651,19 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" s="25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G2" s="25" t="str">
         <f>A2</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q2" s="25" t="str">
         <f>K2</f>
@@ -28644,28 +28673,30 @@
     <row r="3" spans="1:17">
       <c r="A3" s="24" t="str">
         <f t="shared" ref="A3:A19" si="0">IF(F3&lt;&gt;"",$A$20,"")</f>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",LEFT(F3,FIND(":",F3,1)-1),"")</f>
-        <v/>
+        <v>Después de instalar Git</v>
       </c>
       <c r="C3" s="24" t="str">
         <f t="shared" ref="C3:C19" si="1">IF(F3&lt;&gt;"","&lt;/span&gt;","")</f>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",RIGHT(F3,LEN(F3)-FIND(":",F3,1)),"")</f>
-        <v/>
+        <v> Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.</v>
       </c>
       <c r="E3" s="24" t="str">
         <f t="shared" ref="E3:E19" si="2">IF(F3&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
-      </c>
-      <c r="F3" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>183</v>
+      </c>
       <c r="G3" s="25" t="str">
         <f>IF(F3&lt;&gt;"",CONCATENATE(A3,B3,C3,":",D3,E3),IF(F2&lt;&gt;"",F3,""))</f>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Después de instalar Git&lt;/span&gt;: Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.&lt;/li&gt;</v>
       </c>
       <c r="K3" s="24" t="str">
         <f t="shared" ref="K3:K19" si="3">IF(P3&lt;&gt;"",$A$20,"")</f>
@@ -28696,28 +28727,30 @@
     <row r="4" spans="1:17">
       <c r="A4" s="24" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" ref="B3:B19" si="9">IF(F4&lt;&gt;"",LEFT(F4,FIND(":",F4,1)-1),"")</f>
-        <v/>
+        <v>Cuando se usa una computadora compartida</v>
       </c>
       <c r="C4" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D4" s="24" t="str">
         <f>IF(F4&lt;&gt;"",RIGHT(F4,LEN(F4)-FIND(":",F4,1)),"")</f>
-        <v/>
+        <v> Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.</v>
       </c>
       <c r="E4" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F4" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="25" t="str">
         <f>IF(F4&lt;&gt;"",CONCATENATE(A4,B4,C4,":",D4,E4),IF(F3&lt;&gt;"",$A$21,""))</f>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Cuando se usa una computadora compartida&lt;/span&gt;: Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.&lt;/li&gt;</v>
       </c>
       <c r="K4" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28748,28 +28781,30 @@
     <row r="5" spans="1:17">
       <c r="A5" s="24" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Al alternar entre identidades</v>
       </c>
       <c r="C5" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>&lt;/span&gt;</v>
       </c>
       <c r="D5" s="24" t="str">
         <f t="shared" ref="D3:D19" si="10">IF(F5&lt;&gt;"",RIGHT(F5,LEN(F5)-FIND(":",F5,1)),"")</f>
-        <v/>
+        <v> Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.</v>
       </c>
       <c r="E5" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F5" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="25" t="str">
         <f t="shared" ref="G5:G20" si="11">IF(F5&lt;&gt;"",CONCATENATE(A5,B5,C5,":",D5,E5),IF(F4&lt;&gt;"",$A$21,""))</f>
-        <v/>
+        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Al alternar entre identidades&lt;/span&gt;: Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.&lt;/li&gt;</v>
       </c>
       <c r="K5" s="24" t="str">
         <f t="shared" si="3"/>
@@ -28821,7 +28856,7 @@
       <c r="F6" s="26"/>
       <c r="G6" s="25" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K6" s="24" t="str">
         <f t="shared" si="3"/>
@@ -29474,7 +29509,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" ht="15" spans="1:17">
       <c r="A19" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -29529,7 +29564,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>2</v>
@@ -29540,14 +29575,14 @@
         <v/>
       </c>
       <c r="K20" s="24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>2</v>
       </c>
       <c r="P20" s="26"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" ht="15" spans="1:16">
       <c r="A21" s="24" t="s">
         <v>136</v>
       </c>
@@ -29570,19 +29605,19 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:17">
       <c r="A25" s="24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G25" s="25" t="str">
         <f>A25</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q25" s="25" t="str">
         <f>K25</f>
@@ -30314,7 +30349,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" ht="15" spans="1:17">
       <c r="A42" s="24" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -30382,14 +30417,14 @@
         <v/>
       </c>
       <c r="K43" s="24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L43" s="24" t="s">
         <v>2</v>
       </c>
       <c r="P43" s="26"/>
     </row>
-    <row r="44" spans="6:16">
+    <row r="44" ht="15" spans="6:16">
       <c r="F44" s="27"/>
       <c r="G44" s="25" t="str">
         <f t="shared" si="21"/>
@@ -30408,10 +30443,10 @@
     </row>
     <row r="48" ht="15" spans="1:7">
       <c r="A48" s="24" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G48" s="25" t="str">
         <f>IF(F48&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F47&lt;&gt;"",$A$21,""))</f>
@@ -30420,7 +30455,7 @@
     </row>
     <row r="49" spans="6:7">
       <c r="F49" s="29" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G49" s="25" t="str">
         <f t="shared" ref="G49:G60" si="23">IF(F49&lt;&gt;"",CONCATENATE($A$48,F49,$B$48),"")</f>
@@ -30429,7 +30464,7 @@
     </row>
     <row r="50" spans="6:7">
       <c r="F50" s="26" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G50" s="25" t="str">
         <f t="shared" si="23"/>
@@ -30524,7 +30559,7 @@
     <row r="66" spans="6:6">
       <c r="F66" s="26"/>
     </row>
-    <row r="67" spans="6:6">
+    <row r="67" ht="15" spans="6:6">
       <c r="F67" s="27"/>
     </row>
   </sheetData>
@@ -30592,7 +30627,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="23" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -30619,27 +30654,27 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="8" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -30654,7 +30689,7 @@
         <v>https://eduardoherreraf.github.io/</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -30676,7 +30711,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="16"/>
@@ -30696,21 +30731,21 @@
     </row>
     <row r="9" ht="15.75" spans="1:3">
       <c r="A9" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20"/>
     </row>
     <row r="10" ht="16.5" spans="1:3">
       <c r="A10" s="21" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -30725,7 +30760,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap.html</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -30747,7 +30782,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C14" s="17"/>
       <c r="E14" s="16"/>
@@ -30762,19 +30797,19 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
       <c r="A16" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -30789,7 +30824,7 @@
         <v>https://eduardoherreraf.github.io/git.html</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E18" s="16"/>
     </row>
@@ -30811,7 +30846,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C20" s="17"/>
       <c r="E20" s="16"/>
@@ -30826,19 +30861,19 @@
         <v>0.7</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
       <c r="A22" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20"/>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -30853,7 +30888,7 @@
         <v>https://eduardoherreraf.github.io/javascript.html</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E24" s="16"/>
     </row>
@@ -30875,7 +30910,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C26" s="17"/>
       <c r="E26" s="16"/>
@@ -30890,19 +30925,19 @@
         <v>0.7</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
       <c r="A28" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
     </row>
     <row r="29" ht="16.5" spans="1:3">
       <c r="A29" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -30917,7 +30952,7 @@
         <v>https://eduardoherreraf.github.io/photoshop.html</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E30" s="16"/>
     </row>
@@ -30939,7 +30974,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C32" s="17"/>
       <c r="E32" s="16"/>
@@ -30954,19 +30989,19 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
       <c r="A34" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
     </row>
     <row r="35" ht="16.5" spans="1:3">
       <c r="A35" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -30981,7 +31016,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas.html</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E36" s="16"/>
     </row>
@@ -31003,7 +31038,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C38" s="17"/>
       <c r="E38" s="16"/>
@@ -31018,19 +31053,19 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
       <c r="A40" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20"/>
     </row>
     <row r="41" ht="16.5" spans="1:3">
       <c r="A41" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -31045,7 +31080,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3.html</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E42" s="16"/>
     </row>
@@ -31067,7 +31102,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C44" s="17"/>
       <c r="E44" s="16"/>
@@ -31082,19 +31117,19 @@
         <v>0.7</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
       <c r="A46" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="20"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
       <c r="A47" s="21" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31102,7 +31137,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:3">
       <c r="A48" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -31117,7 +31152,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_parcel.html</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E49" s="16"/>
     </row>
@@ -31139,7 +31174,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C51" s="17"/>
       <c r="E51" s="16"/>
@@ -31154,19 +31189,19 @@
         <v>0.6</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
       <c r="A53" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
     </row>
     <row r="54" ht="16.5" spans="1:3">
       <c r="A54" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="12"/>
@@ -31181,7 +31216,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_vite.html</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E55" s="16"/>
     </row>
@@ -31203,7 +31238,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C57" s="17"/>
       <c r="E57" s="16"/>
@@ -31218,19 +31253,19 @@
         <v>0.6</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
       <c r="A59" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="21" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -31238,7 +31273,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:3">
       <c r="A61" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="12"/>
@@ -31253,7 +31288,7 @@
         <v>https://eduardoherreraf.github.io/git-01_como_eliminar_el_ultimo_commit_de_git.html</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E62" s="16"/>
     </row>
@@ -31275,7 +31310,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="17"/>
       <c r="E64" s="16"/>
@@ -31290,19 +31325,19 @@
         <v>0.6</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
       <c r="A66" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20"/>
     </row>
     <row r="67" ht="16.5" spans="1:3">
       <c r="A67" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="12"/>
@@ -31317,7 +31352,7 @@
         <v>https://eduardoherreraf.github.io/git-02_comandos_basicos_de_consola-terminal_cli_para_windows.html</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E68" s="16"/>
     </row>
@@ -31339,7 +31374,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C70" s="17"/>
       <c r="E70" s="16"/>
@@ -31354,19 +31389,19 @@
         <v>0.6</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
       <c r="A72" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="20"/>
     </row>
     <row r="73" ht="16.5" spans="1:3">
       <c r="A73" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
@@ -31381,7 +31416,7 @@
         <v>https://eduardoherreraf.github.io/git-03_introduccion_de_git_para_windows.html</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E74" s="16"/>
     </row>
@@ -31403,7 +31438,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C76" s="17"/>
       <c r="E76" s="16"/>
@@ -31418,19 +31453,19 @@
         <v>0.6</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
       <c r="A78" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
     </row>
     <row r="79" ht="16.5" spans="1:3">
       <c r="A79" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="12"/>
@@ -31445,7 +31480,7 @@
         <v>https://eduardoherreraf.github.io/git-04_configuracion_inicial_git.html</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E80" s="16"/>
     </row>
@@ -31467,7 +31502,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C82" s="17"/>
       <c r="E82" s="16"/>
@@ -31482,19 +31517,19 @@
         <v>0.6</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
       <c r="A84" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="20"/>
     </row>
     <row r="85" ht="16.5" spans="1:3">
       <c r="A85" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
@@ -31530,7 +31565,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C88" s="17"/>
       <c r="E88" s="16"/>
@@ -31545,27 +31580,27 @@
         <v>0.6</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E89" s="16"/>
     </row>
     <row r="90" ht="15.75" spans="1:3">
       <c r="A90" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20"/>
     </row>
     <row r="91" ht="16.5" spans="1:3">
       <c r="A91" s="21" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B91" s="21"/>
       <c r="C91" s="21"/>
     </row>
     <row r="92" ht="16.5" spans="1:3">
       <c r="A92" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
@@ -31580,7 +31615,7 @@
         <v>https://eduardoherreraf.github.io/javascript-como_ejecutar_un_codigo_javascript.html</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E93" s="16"/>
     </row>
@@ -31602,7 +31637,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C95" s="17"/>
       <c r="E95" s="16"/>
@@ -31617,19 +31652,19 @@
         <v>0.6</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
       <c r="A97" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="20"/>
     </row>
     <row r="98" ht="16.5" spans="1:3">
       <c r="A98" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
@@ -31644,7 +31679,7 @@
         <v>https://eduardoherreraf.github.io/javascript-configurar_el_entorno_de_trabajo_javascript.html</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -31665,7 +31700,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C101" s="17"/>
       <c r="E101" s="16"/>
@@ -31680,27 +31715,27 @@
         <v>0.6</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E102" s="16"/>
     </row>
     <row r="103" ht="15.75" spans="1:3">
       <c r="A103" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20"/>
     </row>
     <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="21"/>
     </row>
     <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="12"/>
@@ -31715,7 +31750,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-16_metadatos_y_exportacion.html</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E106" s="16"/>
     </row>
@@ -31737,7 +31772,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C108" s="17"/>
       <c r="E108" s="16"/>
@@ -31752,19 +31787,19 @@
         <v>0.6</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" ht="15.75" spans="1:3">
       <c r="A110" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="20"/>
     </row>
     <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="12"/>
@@ -31779,7 +31814,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-15_filtros_licuar.html</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E112" s="16"/>
     </row>
@@ -31801,7 +31836,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C114" s="17"/>
       <c r="E114" s="16"/>
@@ -31816,19 +31851,19 @@
         <v>0.6</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" ht="15.75" spans="1:3">
       <c r="A116" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B116" s="19"/>
       <c r="C116" s="20"/>
     </row>
     <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="12"/>
@@ -31843,7 +31878,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-14_filtros_neurales.html</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E118" s="16"/>
     </row>
@@ -31865,7 +31900,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C120" s="17"/>
       <c r="E120" s="16"/>
@@ -31880,19 +31915,19 @@
         <v>0.6</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" ht="15.75" spans="1:3">
       <c r="A122" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="20"/>
     </row>
     <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="12"/>
@@ -31907,7 +31942,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-13_filtros.html</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E124" s="16"/>
     </row>
@@ -31929,7 +31964,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C126" s="17"/>
       <c r="E126" s="16"/>
@@ -31944,19 +31979,19 @@
         <v>0.6</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" ht="15.75" spans="1:3">
       <c r="A128" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B128" s="19"/>
       <c r="C128" s="20"/>
     </row>
     <row r="129" ht="16.5" spans="1:3">
       <c r="A129" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="12"/>
@@ -31971,7 +32006,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-12_formas_y_capas.html</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E130" s="16"/>
     </row>
@@ -31993,7 +32028,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C132" s="17"/>
       <c r="E132" s="16"/>
@@ -32008,19 +32043,19 @@
         <v>0.6</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:3">
       <c r="A134" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="20"/>
     </row>
     <row r="135" ht="16.5" spans="1:3">
       <c r="A135" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="12"/>
@@ -32035,7 +32070,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-11_textos.html</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E136" s="16"/>
     </row>
@@ -32057,7 +32092,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C138" s="17"/>
       <c r="E138" s="16"/>
@@ -32072,19 +32107,19 @@
         <v>0.6</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:3">
       <c r="A140" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="20"/>
     </row>
     <row r="141" ht="16.5" spans="1:3">
       <c r="A141" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="12"/>
@@ -32099,7 +32134,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-10_color_y_degradados.html</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E142" s="16"/>
     </row>
@@ -32121,7 +32156,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C144" s="17"/>
       <c r="E144" s="16"/>
@@ -32136,19 +32171,19 @@
         <v>0.6</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:3">
       <c r="A146" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B146" s="19"/>
       <c r="C146" s="20"/>
     </row>
     <row r="147" ht="16.5" spans="1:3">
       <c r="A147" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="12"/>
@@ -32163,7 +32198,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-09_uso_de_pinceles.html</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E148" s="16"/>
     </row>
@@ -32185,7 +32220,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C150" s="17"/>
       <c r="E150" s="16"/>
@@ -32200,19 +32235,19 @@
         <v>0.6</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" ht="15.75" spans="1:3">
       <c r="A152" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="20"/>
     </row>
     <row r="153" ht="16.5" spans="1:3">
       <c r="A153" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="12"/>
@@ -32227,7 +32262,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-08_agregar_y_quitar_objetos.html</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E154" s="16"/>
     </row>
@@ -32249,7 +32284,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C156" s="17"/>
       <c r="E156" s="16"/>
@@ -32264,19 +32299,19 @@
         <v>0.6</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" ht="15.75" spans="1:3">
       <c r="A158" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B158" s="19"/>
       <c r="C158" s="20"/>
     </row>
     <row r="159" ht="16.5" spans="1:3">
       <c r="A159" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="12"/>
@@ -32291,7 +32326,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-07_herramientas_de_seleccion.html</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E160" s="16"/>
     </row>
@@ -32313,7 +32348,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C162" s="17"/>
       <c r="E162" s="16"/>
@@ -32328,19 +32363,19 @@
         <v>0.6</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164" ht="15.75" spans="1:3">
       <c r="A164" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="20"/>
     </row>
     <row r="165" ht="16.5" spans="1:3">
       <c r="A165" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="12"/>
@@ -32355,7 +32390,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-06_ajuste_tono_brillo_y_saturacion.html</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E166" s="16"/>
     </row>
@@ -32377,7 +32412,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C168" s="17"/>
       <c r="E168" s="16"/>
@@ -32392,19 +32427,19 @@
         <v>0.6</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="170" ht="15.75" spans="1:3">
       <c r="A170" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B170" s="19"/>
       <c r="C170" s="20"/>
     </row>
     <row r="171" ht="16.5" spans="1:3">
       <c r="A171" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="12"/>
@@ -32419,7 +32454,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-05_trabajo_con_capas.html</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E172" s="16"/>
     </row>
@@ -32441,7 +32476,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C174" s="17"/>
       <c r="E174" s="16"/>
@@ -32456,19 +32491,19 @@
         <v>0.6</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" ht="15.75" spans="1:3">
       <c r="A176" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B176" s="19"/>
       <c r="C176" s="20"/>
     </row>
     <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="12"/>
@@ -32483,7 +32518,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-04_ajuste_lienzo_resolucion.html</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E178" s="16"/>
     </row>
@@ -32505,7 +32540,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C180" s="17"/>
       <c r="E180" s="16"/>
@@ -32520,19 +32555,19 @@
         <v>0.6</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="182" ht="15.75" spans="1:3">
       <c r="A182" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="20"/>
     </row>
     <row r="183" ht="16.5" spans="1:3">
       <c r="A183" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="12"/>
@@ -32547,7 +32582,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-03_compartir_y_editar_archivos.html</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E184" s="16"/>
     </row>
@@ -32569,7 +32604,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C186" s="17"/>
       <c r="E186" s="16"/>
@@ -32584,19 +32619,19 @@
         <v>0.6</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="188" ht="15.75" spans="1:3">
       <c r="A188" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B188" s="19"/>
       <c r="C188" s="20"/>
     </row>
     <row r="189" ht="16.5" spans="1:3">
       <c r="A189" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="12"/>
@@ -32611,7 +32646,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-02_interfaz_y_area_de_trabajo.html</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E190" s="16"/>
     </row>
@@ -32633,7 +32668,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C192" s="17"/>
       <c r="E192" s="16"/>
@@ -32648,19 +32683,19 @@
         <v>0.6</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="194" ht="15.75" spans="1:3">
       <c r="A194" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B194" s="19"/>
       <c r="C194" s="20"/>
     </row>
     <row r="195" ht="16.5" spans="1:3">
       <c r="A195" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="12"/>
@@ -32675,7 +32710,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-01_comenzando_un_proyecto.html</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -32696,7 +32731,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C198" s="17"/>
       <c r="E198" s="16"/>
@@ -32711,27 +32746,27 @@
         <v>0.6</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E199" s="16"/>
     </row>
     <row r="200" ht="15.75" spans="1:3">
       <c r="A200" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B200" s="19"/>
       <c r="C200" s="20"/>
     </row>
     <row r="201" ht="16.5" spans="1:3">
       <c r="A201" s="21" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B201" s="21"/>
       <c r="C201" s="21"/>
     </row>
     <row r="202" ht="16.5" spans="1:3">
       <c r="A202" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="12"/>
@@ -32746,7 +32781,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E203" s="16"/>
     </row>
@@ -32768,7 +32803,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C205" s="17"/>
       <c r="E205" s="16"/>
@@ -32783,19 +32818,19 @@
         <v>0.6</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="207" ht="15.75" spans="1:3">
       <c r="A207" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B207" s="19"/>
       <c r="C207" s="20"/>
     </row>
     <row r="208" ht="16.5" spans="1:3">
       <c r="A208" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="12"/>
@@ -32810,7 +32845,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_borrar_la_cache_y_archivos_basura_en_windows.html</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -32831,7 +32866,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C211" s="17"/>
       <c r="E211" s="16"/>
@@ -32846,27 +32881,27 @@
         <v>0.6</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E212" s="16"/>
     </row>
     <row r="213" ht="15.75" spans="1:3">
       <c r="A213" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B213" s="19"/>
       <c r="C213" s="20"/>
     </row>
     <row r="214" ht="16.5" spans="1:3">
       <c r="A214" s="21" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B214" s="21"/>
       <c r="C214" s="21"/>
     </row>
     <row r="215" ht="16.5" spans="1:3">
       <c r="A215" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="12"/>
@@ -32881,7 +32916,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0101_introduccion.html</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E216" s="16"/>
     </row>
@@ -32903,7 +32938,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C218" s="17"/>
       <c r="E218" s="16"/>
@@ -32918,19 +32953,19 @@
         <v>0.6</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="220" ht="15.75" spans="1:3">
       <c r="A220" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B220" s="19"/>
       <c r="C220" s="20"/>
     </row>
     <row r="221" ht="16.5" spans="1:3">
       <c r="A221" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="12"/>
@@ -32945,7 +32980,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0102_instalacion_de_python_localmente.html</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E222" s="16"/>
     </row>
@@ -32967,7 +33002,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C224" s="17"/>
       <c r="E224" s="16"/>
@@ -32982,19 +33017,19 @@
         <v>0.6</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="226" ht="15.75" spans="1:3">
       <c r="A226" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B226" s="19"/>
       <c r="C226" s="20"/>
     </row>
     <row r="227" ht="16.5" spans="1:3">
       <c r="A227" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="12"/>
@@ -33009,7 +33044,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0201_funcion_print.html</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E228" s="16"/>
     </row>
@@ -33031,7 +33066,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C230" s="17"/>
       <c r="E230" s="16"/>
@@ -33046,19 +33081,19 @@
         <v>0.6</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="232" ht="15.75" spans="1:3">
       <c r="A232" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B232" s="19"/>
       <c r="C232" s="20"/>
     </row>
     <row r="233" ht="16.5" spans="1:3">
       <c r="A233" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B233" s="11"/>
       <c r="C233" s="12"/>
@@ -33073,7 +33108,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0202_literales.html</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E234" s="16"/>
     </row>
@@ -33095,7 +33130,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C236" s="17"/>
       <c r="E236" s="16"/>
@@ -33110,19 +33145,19 @@
         <v>0.6</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="238" ht="15.75" spans="1:3">
       <c r="A238" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="20"/>
     </row>
     <row r="239" ht="16.5" spans="1:3">
       <c r="A239" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B239" s="11"/>
       <c r="C239" s="12"/>
@@ -33137,7 +33172,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0203_operadores.html</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E240" s="16"/>
     </row>
@@ -33159,7 +33194,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C242" s="17"/>
       <c r="E242" s="16"/>
@@ -33174,19 +33209,19 @@
         <v>0.6</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="244" ht="15.75" spans="1:3">
       <c r="A244" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B244" s="19"/>
       <c r="C244" s="20"/>
     </row>
     <row r="245" ht="16.5" spans="1:3">
       <c r="A245" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B245" s="11"/>
       <c r="C245" s="12"/>
@@ -33201,7 +33236,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0204_variables.html</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E246" s="16"/>
     </row>
@@ -33223,7 +33258,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C248" s="17"/>
       <c r="E248" s="16"/>
@@ -33238,19 +33273,19 @@
         <v>0.6</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="250" ht="15.75" spans="1:3">
       <c r="A250" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B250" s="19"/>
       <c r="C250" s="20"/>
     </row>
     <row r="251" ht="16.5" spans="1:3">
       <c r="A251" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B251" s="11"/>
       <c r="C251" s="12"/>
@@ -33265,7 +33300,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0205_comentarios.html</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E252" s="16"/>
     </row>
@@ -33287,7 +33322,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C254" s="17"/>
       <c r="E254" s="16"/>
@@ -33302,19 +33337,19 @@
         <v>0.6</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" ht="15.75" spans="1:3">
       <c r="A256" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B256" s="19"/>
       <c r="C256" s="20"/>
     </row>
     <row r="257" ht="16.5" spans="1:3">
       <c r="A257" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="12"/>
@@ -33329,7 +33364,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0206_interaccion_con_el_usuario.html</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E258" s="16"/>
     </row>
@@ -33351,7 +33386,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C260" s="17"/>
       <c r="E260" s="16"/>
@@ -33366,19 +33401,19 @@
         <v>0.6</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" ht="15.75" spans="1:3">
       <c r="A262" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B262" s="19"/>
       <c r="C262" s="20"/>
     </row>
     <row r="263" ht="16.5" spans="1:3">
       <c r="A263" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="12"/>
@@ -33393,7 +33428,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0301_operadores_de_comparacion_y_logicos_en_python.html</v>
       </c>
       <c r="C264" s="15" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E264" s="16"/>
     </row>
@@ -33415,7 +33450,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B266" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C266" s="17"/>
       <c r="E266" s="16"/>
@@ -33430,19 +33465,19 @@
         <v>0.6</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" ht="15.75" spans="1:3">
       <c r="A268" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B268" s="19"/>
       <c r="C268" s="20"/>
     </row>
     <row r="269" ht="16.5" spans="1:3">
       <c r="A269" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B269" s="11"/>
       <c r="C269" s="12"/>
@@ -33457,7 +33492,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0302_sentencia_if_de_control_de_flujo.html</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E270" s="16"/>
     </row>
@@ -33479,7 +33514,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B272" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C272" s="17"/>
       <c r="E272" s="16"/>
@@ -33494,19 +33529,19 @@
         <v>0.6</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="274" ht="15.75" spans="1:3">
       <c r="A274" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B274" s="19"/>
       <c r="C274" s="20"/>
     </row>
     <row r="275" ht="16.5" spans="1:3">
       <c r="A275" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B275" s="11"/>
       <c r="C275" s="12"/>
@@ -33521,7 +33556,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0303_bucles_en_python_una_guia_completa.html</v>
       </c>
       <c r="C276" s="15" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E276" s="16"/>
     </row>
@@ -33543,7 +33578,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C278" s="17"/>
       <c r="E278" s="16"/>
@@ -33558,19 +33593,19 @@
         <v>0.6</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="280" ht="15.75" spans="1:3">
       <c r="A280" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B280" s="19"/>
       <c r="C280" s="20"/>
     </row>
     <row r="281" ht="16.5" spans="1:3">
       <c r="A281" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B281" s="11"/>
       <c r="C281" s="12"/>
@@ -33585,7 +33620,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0304_operadores_logicos_y_operaciones_bit_a_bit_en_python.html</v>
       </c>
       <c r="C282" s="15" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E282" s="16"/>
     </row>
@@ -33607,7 +33642,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C284" s="17"/>
       <c r="E284" s="16"/>
@@ -33622,19 +33657,19 @@
         <v>0.6</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="286" ht="15.75" spans="1:3">
       <c r="A286" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B286" s="19"/>
       <c r="C286" s="20"/>
     </row>
     <row r="287" ht="16.5" spans="1:3">
       <c r="A287" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B287" s="11"/>
       <c r="C287" s="12"/>
@@ -33649,7 +33684,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0305_listas.html</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E288" s="16"/>
     </row>
@@ -33671,7 +33706,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B290" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C290" s="17"/>
       <c r="E290" s="16"/>
@@ -33686,19 +33721,19 @@
         <v>0.6</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="292" ht="15.75" spans="1:3">
       <c r="A292" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B292" s="19"/>
       <c r="C292" s="20"/>
     </row>
     <row r="293" ht="16.5" spans="1:3">
       <c r="A293" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B293" s="11"/>
       <c r="C293" s="12"/>
@@ -33713,7 +33748,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0306_ordenamiento_de_listas_metodo_burbuja.html</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E294" s="16"/>
     </row>
@@ -33735,7 +33770,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C296" s="17"/>
       <c r="E296" s="16"/>
@@ -33750,19 +33785,19 @@
         <v>0.6</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="298" ht="15.75" spans="1:3">
       <c r="A298" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B298" s="19"/>
       <c r="C298" s="20"/>
     </row>
     <row r="299" ht="16.5" spans="1:3">
       <c r="A299" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B299" s="11"/>
       <c r="C299" s="12"/>
@@ -33777,7 +33812,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0307_operaciones_con_listas.html</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E300" s="16"/>
     </row>
@@ -33799,7 +33834,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C302" s="17"/>
       <c r="E302" s="16"/>
@@ -33814,19 +33849,19 @@
         <v>0.6</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="304" ht="15.75" spans="1:3">
       <c r="A304" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B304" s="19"/>
       <c r="C304" s="20"/>
     </row>
     <row r="305" ht="16.5" spans="1:3">
       <c r="A305" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B305" s="11"/>
       <c r="C305" s="12"/>
@@ -33841,7 +33876,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0401_introduccion_funciones.html</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E306" s="16"/>
     </row>
@@ -33863,7 +33898,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C308" s="17"/>
       <c r="E308" s="16"/>
@@ -33878,19 +33913,19 @@
         <v>0.6</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="310" ht="15.75" spans="1:3">
       <c r="A310" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B310" s="19"/>
       <c r="C310" s="20"/>
     </row>
     <row r="311" ht="16.5" spans="1:3">
       <c r="A311" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B311" s="11"/>
       <c r="C311" s="12"/>
@@ -33905,7 +33940,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0402_como_las_funciones_se_comunican_con_su_entorno.html</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E312" s="16"/>
     </row>
@@ -33927,7 +33962,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B314" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C314" s="17"/>
       <c r="E314" s="16"/>
@@ -33942,19 +33977,19 @@
         <v>0.6</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="316" ht="15.75" spans="1:3">
       <c r="A316" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B316" s="19"/>
       <c r="C316" s="20"/>
     </row>
     <row r="317" ht="16.5" spans="1:3">
       <c r="A317" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B317" s="11"/>
       <c r="C317" s="12"/>
@@ -33969,7 +34004,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0403_retorno_de_valores_en_funciones.html</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E318" s="16"/>
     </row>
@@ -33991,7 +34026,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B320" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C320" s="17"/>
       <c r="E320" s="16"/>
@@ -34006,19 +34041,19 @@
         <v>0.6</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="322" ht="15.75" spans="1:3">
       <c r="A322" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B322" s="19"/>
       <c r="C322" s="20"/>
     </row>
     <row r="323" ht="16.5" spans="1:3">
       <c r="A323" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B323" s="11"/>
       <c r="C323" s="12"/>
@@ -34033,7 +34068,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0404_el_alcance_de_las_variables.html</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E324" s="16"/>
     </row>
@@ -34055,7 +34090,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B326" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C326" s="17"/>
       <c r="E326" s="16"/>
@@ -34070,19 +34105,19 @@
         <v>0.6</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="328" ht="15.75" spans="1:3">
       <c r="A328" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B328" s="19"/>
       <c r="C328" s="20"/>
     </row>
     <row r="329" ht="16.5" spans="1:3">
       <c r="A329" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="12"/>
@@ -34097,7 +34132,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0405_tuplas_y_diccionarios.html</v>
       </c>
       <c r="C330" s="15" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E330" s="16"/>
     </row>
@@ -34119,7 +34154,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B332" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C332" s="17"/>
       <c r="E332" s="16"/>
@@ -34134,19 +34169,19 @@
         <v>0.6</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="334" ht="15.75" spans="1:3">
       <c r="A334" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B334" s="19"/>
       <c r="C334" s="20"/>
     </row>
     <row r="335" ht="16.5" spans="1:3">
       <c r="A335" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B335" s="11"/>
       <c r="C335" s="12"/>
@@ -34161,7 +34196,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0501_introduccion_a_los_modulos.html</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="E336" s="16"/>
     </row>
@@ -34183,7 +34218,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B338" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C338" s="17"/>
       <c r="E338" s="16"/>
@@ -34198,19 +34233,19 @@
         <v>0.6</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="340" ht="15.75" spans="1:3">
       <c r="A340" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B340" s="19"/>
       <c r="C340" s="20"/>
     </row>
     <row r="341" ht="16.5" spans="1:3">
       <c r="A341" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B341" s="11"/>
       <c r="C341" s="12"/>
@@ -34225,7 +34260,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0502_importacion_de_modulos.html</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E342" s="16"/>
     </row>
@@ -34247,7 +34282,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B344" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C344" s="17"/>
       <c r="E344" s="16"/>
@@ -34262,19 +34297,19 @@
         <v>0.6</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="346" ht="15.75" spans="1:3">
       <c r="A346" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B346" s="19"/>
       <c r="C346" s="20"/>
     </row>
     <row r="347" ht="16.5" spans="1:3">
       <c r="A347" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B347" s="11"/>
       <c r="C347" s="12"/>
@@ -34289,7 +34324,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0503_modulos_especializados_de_python-matematico_aleatorio_y_de_sistema.html</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E348" s="16"/>
     </row>
@@ -34311,7 +34346,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B350" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C350" s="17"/>
       <c r="E350" s="16"/>
@@ -34326,19 +34361,19 @@
         <v>0.6</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="352" ht="15.75" spans="1:3">
       <c r="A352" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B352" s="19"/>
       <c r="C352" s="20"/>
     </row>
     <row r="353" ht="16.5" spans="1:3">
       <c r="A353" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B353" s="11"/>
       <c r="C353" s="12"/>
@@ -34353,7 +34388,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0504_modulos_y_paquetes.html</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E354" s="16"/>
     </row>
@@ -34375,7 +34410,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B356" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C356" s="17"/>
       <c r="E356" s="16"/>
@@ -34390,19 +34425,19 @@
         <v>0.6</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="358" ht="15.75" spans="1:3">
       <c r="A358" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B358" s="19"/>
       <c r="C358" s="20"/>
     </row>
     <row r="359" ht="16.5" spans="1:3">
       <c r="A359" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B359" s="11"/>
       <c r="C359" s="12"/>
@@ -34417,7 +34452,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0505_instalador_de_paquetes_PIP.html</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E360" s="16"/>
     </row>
@@ -34439,7 +34474,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B362" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C362" s="17"/>
       <c r="E362" s="16"/>
@@ -34454,19 +34489,19 @@
         <v>0.6</v>
       </c>
       <c r="C363" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="364" ht="15.75" spans="1:3">
       <c r="A364" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B364" s="19"/>
       <c r="C364" s="20"/>
     </row>
     <row r="365" ht="16.5" spans="1:3">
       <c r="A365" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B365" s="11"/>
       <c r="C365" s="12"/>
@@ -34481,7 +34516,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0601_la_naturaleza_de_las_cadenas.html</v>
       </c>
       <c r="C366" s="15" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E366" s="16"/>
     </row>
@@ -34503,7 +34538,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C368" s="17"/>
       <c r="E368" s="16"/>
@@ -34518,19 +34553,19 @@
         <v>0.6</v>
       </c>
       <c r="C369" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="370" ht="15.75" spans="1:3">
       <c r="A370" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B370" s="19"/>
       <c r="C370" s="20"/>
     </row>
     <row r="371" ht="16.5" spans="1:3">
       <c r="A371" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B371" s="11"/>
       <c r="C371" s="12"/>
@@ -34545,7 +34580,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0602_errores-el_pan_diario_del_programador.html</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E372" s="16"/>
     </row>
@@ -34567,7 +34602,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C374" s="17"/>
       <c r="E374" s="16"/>
@@ -34582,19 +34617,19 @@
         <v>0.6</v>
       </c>
       <c r="C375" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="376" ht="15.75" spans="1:3">
       <c r="A376" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B376" s="19"/>
       <c r="C376" s="20"/>
     </row>
     <row r="377" ht="16.5" spans="1:3">
       <c r="A377" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B377" s="11"/>
       <c r="C377" s="12"/>
@@ -34609,7 +34644,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0701_los_fundamentos_de_la_poo.html</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E378" s="16"/>
     </row>
@@ -34631,7 +34666,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C380" s="17"/>
       <c r="E380" s="16"/>
@@ -34646,19 +34681,19 @@
         <v>0.6</v>
       </c>
       <c r="C381" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="382" ht="15.75" spans="1:3">
       <c r="A382" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B382" s="19"/>
       <c r="C382" s="20"/>
     </row>
     <row r="383" ht="16.5" spans="1:3">
       <c r="A383" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B383" s="11"/>
       <c r="C383" s="12"/>
@@ -34673,7 +34708,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0702_comparando_paradigmas_programacion_procedimental_y_orientada_a_objetos.html</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E384" s="16"/>
     </row>
@@ -34695,7 +34730,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C386" s="17"/>
       <c r="E386" s="16"/>
@@ -34710,19 +34745,19 @@
         <v>0.6</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="388" ht="15.75" spans="1:3">
       <c r="A388" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B388" s="19"/>
       <c r="C388" s="20"/>
     </row>
     <row r="389" ht="16.5" spans="1:3">
       <c r="A389" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B389" s="11"/>
       <c r="C389" s="12"/>
@@ -34737,7 +34772,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0703_poo_propiedades.html</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E390" s="16"/>
     </row>
@@ -34759,7 +34794,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C392" s="17"/>
       <c r="E392" s="16"/>
@@ -34774,19 +34809,19 @@
         <v>0.6</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="394" ht="15.75" spans="1:3">
       <c r="A394" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="20"/>
     </row>
     <row r="395" ht="16.5" spans="1:3">
       <c r="A395" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="12"/>
@@ -34801,7 +34836,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0704_poo_metodos.html</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E396" s="16"/>
     </row>
@@ -34823,7 +34858,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C398" s="17"/>
       <c r="E398" s="16"/>
@@ -34838,19 +34873,19 @@
         <v>0.6</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="400" ht="15.75" spans="1:3">
       <c r="A400" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B400" s="19"/>
       <c r="C400" s="20"/>
     </row>
     <row r="401" ht="16.5" spans="1:3">
       <c r="A401" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B401" s="11"/>
       <c r="C401" s="12"/>
@@ -34865,7 +34900,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0705_poo_herencia.html</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E402" s="16"/>
     </row>
@@ -34887,7 +34922,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C404" s="17"/>
       <c r="E404" s="16"/>
@@ -34902,19 +34937,19 @@
         <v>0.6</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="406" ht="15.75" spans="1:3">
       <c r="A406" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B406" s="19"/>
       <c r="C406" s="20"/>
     </row>
     <row r="407" ht="16.5" spans="1:3">
       <c r="A407" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B407" s="11"/>
       <c r="C407" s="12"/>
@@ -34929,7 +34964,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0706_poo_excepciones.html</v>
       </c>
       <c r="C408" s="15" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E408" s="16"/>
     </row>
@@ -34951,7 +34986,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C410" s="17"/>
       <c r="E410" s="16"/>
@@ -34966,19 +35001,19 @@
         <v>0.6</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="412" ht="15.75" spans="1:3">
       <c r="A412" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B412" s="19"/>
       <c r="C412" s="20"/>
     </row>
     <row r="413" ht="16.5" spans="1:3">
       <c r="A413" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="12"/>
@@ -34993,7 +35028,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0801_iteradores,_generadores_y_cierres.html</v>
       </c>
       <c r="C414" s="15" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E414" s="16"/>
     </row>
@@ -35015,7 +35050,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C416" s="17"/>
       <c r="E416" s="16"/>
@@ -35030,19 +35065,19 @@
         <v>0.6</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="418" ht="15.75" spans="1:3">
       <c r="A418" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B418" s="19"/>
       <c r="C418" s="20"/>
     </row>
     <row r="419" ht="16.5" spans="1:3">
       <c r="A419" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="12"/>
@@ -35057,7 +35092,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0802_manejo_de_archivos.html</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E420" s="16"/>
     </row>
@@ -35079,7 +35114,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C422" s="17"/>
       <c r="E422" s="16"/>
@@ -35094,19 +35129,19 @@
         <v>0.6</v>
       </c>
       <c r="C423" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="424" ht="15.75" spans="1:3">
       <c r="A424" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B424" s="19"/>
       <c r="C424" s="20"/>
     </row>
     <row r="425" ht="16.5" spans="1:3">
       <c r="A425" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="12"/>
@@ -35121,7 +35156,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0803_el_modulo_os_interactuando_con_el_sistema_operativo.html</v>
       </c>
       <c r="C426" s="15" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E426" s="16"/>
     </row>
@@ -35143,7 +35178,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C428" s="17"/>
       <c r="E428" s="16"/>
@@ -35158,19 +35193,19 @@
         <v>0.6</v>
       </c>
       <c r="C429" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="430" ht="15.75" spans="1:3">
       <c r="A430" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B430" s="19"/>
       <c r="C430" s="20"/>
     </row>
     <row r="431" ht="16.5" spans="1:3">
       <c r="A431" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="12"/>
@@ -35185,7 +35220,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html</v>
       </c>
       <c r="C432" s="15" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E432" s="16"/>
     </row>
@@ -35207,7 +35242,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C434" s="17"/>
       <c r="E434" s="16"/>
@@ -35222,19 +35257,19 @@
         <v>0.6</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="436" ht="15.75" spans="1:3">
       <c r="A436" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B436" s="19"/>
       <c r="C436" s="20"/>
     </row>
     <row r="437" ht="16.5" spans="1:3">
       <c r="A437" s="10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="12"/>
@@ -35249,7 +35284,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html</v>
       </c>
       <c r="C438" s="15" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -35269,7 +35304,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C440" s="17"/>
     </row>
@@ -35283,19 +35318,19 @@
         <v>0.6</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="442" ht="15.75" spans="1:3">
       <c r="A442" s="18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B442" s="19"/>
       <c r="C442" s="20"/>
     </row>
     <row r="443" ht="15.75" spans="1:3">
       <c r="A443" s="5" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C443" s="22"/>
     </row>
@@ -35585,13 +35620,13 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -35600,78 +35635,78 @@
         <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -35680,16 +35715,16 @@
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -35698,7 +35733,7 @@
         <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -35707,51 +35742,51 @@
         <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4"/>
       <c r="D20" s="1" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="1" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/src/Head.xlsx
+++ b/src/Head.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="316">
   <si>
     <t>Título</t>
   </si>
@@ -695,6 +695,18 @@
   </si>
   <si>
     <t>&lt;li&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.</t>
+  </si>
+  <si>
+    <t>Si se han realizado cambios que no se quieren conservar.</t>
+  </si>
+  <si>
+    <t>Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.</t>
+  </si>
+  <si>
+    <t>En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.</t>
   </si>
   <si>
     <t>&lt;p&gt;</t>
@@ -29627,20 +29639,22 @@
     <row r="26" spans="1:17">
       <c r="A26" s="24" t="str">
         <f t="shared" ref="A26:A43" si="12">IF(F26&lt;&gt;"",$A$24,"")</f>
-        <v/>
+        <v>&lt;li&gt;</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" ref="B26:B43" si="13">IF(F26&lt;&gt;"",CONCATENATE(A26,F26,C26),"")</f>
-        <v/>
+        <v>&lt;li&gt; Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.&lt;/li&gt;</v>
       </c>
       <c r="C26" s="24" t="str">
         <f t="shared" ref="C26:C43" si="14">IF(F26&lt;&gt;"","&lt;/li&gt;","")</f>
-        <v/>
-      </c>
-      <c r="F26" s="29"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>188</v>
+      </c>
       <c r="G26" s="25" t="str">
         <f>IF(F26&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F25&lt;&gt;"",$A$21,""))</f>
-        <v/>
+        <v>&lt;li&gt; Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.</v>
       </c>
       <c r="K26" s="24" t="str">
         <f t="shared" ref="K26:K42" si="15">IF(P26&lt;&gt;"",$A$20,"")</f>
@@ -29671,20 +29685,22 @@
     <row r="27" spans="1:17">
       <c r="A27" s="24" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>&lt;li&gt;</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>&lt;li&gt;Si se han realizado cambios que no se quieren conservar.&lt;/li&gt;</v>
       </c>
       <c r="C27" s="24" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F27" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>189</v>
+      </c>
       <c r="G27" s="25" t="str">
         <f t="shared" ref="G26:G44" si="21">IF(F27&lt;&gt;"",CONCATENATE(A27,F27,E27),IF(F26&lt;&gt;"",$A$21,""))</f>
-        <v/>
+        <v>&lt;li&gt;Si se han realizado cambios que no se quieren conservar.</v>
       </c>
       <c r="K27" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29715,20 +29731,22 @@
     <row r="28" spans="1:17">
       <c r="A28" s="24" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>&lt;li&gt;</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>&lt;li&gt;Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.&lt;/li&gt;</v>
       </c>
       <c r="C28" s="24" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F28" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>190</v>
+      </c>
       <c r="G28" s="25" t="str">
         <f t="shared" si="21"/>
-        <v/>
+        <v>&lt;li&gt;Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.</v>
       </c>
       <c r="K28" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29759,20 +29777,22 @@
     <row r="29" spans="1:17">
       <c r="A29" s="24" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>&lt;li&gt;</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>&lt;li&gt;En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.&lt;/li&gt;</v>
       </c>
       <c r="C29" s="24" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F29" s="26"/>
+        <v>&lt;/li&gt;</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>191</v>
+      </c>
       <c r="G29" s="25" t="str">
         <f t="shared" si="21"/>
-        <v/>
+        <v>&lt;li&gt;En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.</v>
       </c>
       <c r="K29" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29816,7 +29836,7 @@
       <c r="F30" s="26"/>
       <c r="G30" s="25" t="str">
         <f t="shared" si="21"/>
-        <v/>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K30" s="24" t="str">
         <f t="shared" si="15"/>
@@ -30443,10 +30463,10 @@
     </row>
     <row r="48" ht="15" spans="1:7">
       <c r="A48" s="24" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G48" s="25" t="str">
         <f>IF(F48&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F47&lt;&gt;"",$A$21,""))</f>
@@ -30455,7 +30475,7 @@
     </row>
     <row r="49" spans="6:7">
       <c r="F49" s="29" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G49" s="25" t="str">
         <f t="shared" ref="G49:G60" si="23">IF(F49&lt;&gt;"",CONCATENATE($A$48,F49,$B$48),"")</f>
@@ -30464,7 +30484,7 @@
     </row>
     <row r="50" spans="6:7">
       <c r="F50" s="26" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G50" s="25" t="str">
         <f t="shared" si="23"/>
@@ -30627,7 +30647,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="23" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -30654,27 +30674,27 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -30689,7 +30709,7 @@
         <v>https://eduardoherreraf.github.io/</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -30711,7 +30731,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="16"/>
@@ -30731,21 +30751,21 @@
     </row>
     <row r="9" ht="15.75" spans="1:3">
       <c r="A9" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20"/>
     </row>
     <row r="10" ht="16.5" spans="1:3">
       <c r="A10" s="21" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -30760,7 +30780,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap.html</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -30782,7 +30802,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C14" s="17"/>
       <c r="E14" s="16"/>
@@ -30797,19 +30817,19 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
       <c r="A16" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -30824,7 +30844,7 @@
         <v>https://eduardoherreraf.github.io/git.html</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E18" s="16"/>
     </row>
@@ -30846,7 +30866,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C20" s="17"/>
       <c r="E20" s="16"/>
@@ -30861,19 +30881,19 @@
         <v>0.7</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
       <c r="A22" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20"/>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -30888,7 +30908,7 @@
         <v>https://eduardoherreraf.github.io/javascript.html</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E24" s="16"/>
     </row>
@@ -30910,7 +30930,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C26" s="17"/>
       <c r="E26" s="16"/>
@@ -30925,19 +30945,19 @@
         <v>0.7</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
       <c r="A28" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
     </row>
     <row r="29" ht="16.5" spans="1:3">
       <c r="A29" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -30952,7 +30972,7 @@
         <v>https://eduardoherreraf.github.io/photoshop.html</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E30" s="16"/>
     </row>
@@ -30974,7 +30994,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C32" s="17"/>
       <c r="E32" s="16"/>
@@ -30989,19 +31009,19 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
       <c r="A34" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
     </row>
     <row r="35" ht="16.5" spans="1:3">
       <c r="A35" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -31016,7 +31036,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas.html</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E36" s="16"/>
     </row>
@@ -31038,7 +31058,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C38" s="17"/>
       <c r="E38" s="16"/>
@@ -31053,19 +31073,19 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
       <c r="A40" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20"/>
     </row>
     <row r="41" ht="16.5" spans="1:3">
       <c r="A41" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -31080,7 +31100,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3.html</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E42" s="16"/>
     </row>
@@ -31102,7 +31122,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C44" s="17"/>
       <c r="E44" s="16"/>
@@ -31117,19 +31137,19 @@
         <v>0.7</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
       <c r="A46" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="20"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
       <c r="A47" s="21" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31137,7 +31157,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:3">
       <c r="A48" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -31152,7 +31172,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_parcel.html</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E49" s="16"/>
     </row>
@@ -31174,7 +31194,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C51" s="17"/>
       <c r="E51" s="16"/>
@@ -31189,19 +31209,19 @@
         <v>0.6</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
       <c r="A53" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
     </row>
     <row r="54" ht="16.5" spans="1:3">
       <c r="A54" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="12"/>
@@ -31216,7 +31236,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_vite.html</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E55" s="16"/>
     </row>
@@ -31238,7 +31258,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C57" s="17"/>
       <c r="E57" s="16"/>
@@ -31253,19 +31273,19 @@
         <v>0.6</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
       <c r="A59" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="21" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -31273,7 +31293,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:3">
       <c r="A61" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="12"/>
@@ -31288,7 +31308,7 @@
         <v>https://eduardoherreraf.github.io/git-01_como_eliminar_el_ultimo_commit_de_git.html</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E62" s="16"/>
     </row>
@@ -31310,7 +31330,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C64" s="17"/>
       <c r="E64" s="16"/>
@@ -31325,19 +31345,19 @@
         <v>0.6</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
       <c r="A66" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20"/>
     </row>
     <row r="67" ht="16.5" spans="1:3">
       <c r="A67" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="12"/>
@@ -31352,7 +31372,7 @@
         <v>https://eduardoherreraf.github.io/git-02_comandos_basicos_de_consola-terminal_cli_para_windows.html</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E68" s="16"/>
     </row>
@@ -31374,7 +31394,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C70" s="17"/>
       <c r="E70" s="16"/>
@@ -31389,19 +31409,19 @@
         <v>0.6</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
       <c r="A72" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="20"/>
     </row>
     <row r="73" ht="16.5" spans="1:3">
       <c r="A73" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
@@ -31416,7 +31436,7 @@
         <v>https://eduardoherreraf.github.io/git-03_introduccion_de_git_para_windows.html</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E74" s="16"/>
     </row>
@@ -31438,7 +31458,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C76" s="17"/>
       <c r="E76" s="16"/>
@@ -31453,19 +31473,19 @@
         <v>0.6</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
       <c r="A78" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
     </row>
     <row r="79" ht="16.5" spans="1:3">
       <c r="A79" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="12"/>
@@ -31480,7 +31500,7 @@
         <v>https://eduardoherreraf.github.io/git-04_configuracion_inicial_git.html</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E80" s="16"/>
     </row>
@@ -31502,7 +31522,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C82" s="17"/>
       <c r="E82" s="16"/>
@@ -31517,19 +31537,19 @@
         <v>0.6</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
       <c r="A84" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="20"/>
     </row>
     <row r="85" ht="16.5" spans="1:3">
       <c r="A85" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
@@ -31565,7 +31585,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C88" s="17"/>
       <c r="E88" s="16"/>
@@ -31580,27 +31600,27 @@
         <v>0.6</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E89" s="16"/>
     </row>
     <row r="90" ht="15.75" spans="1:3">
       <c r="A90" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20"/>
     </row>
     <row r="91" ht="16.5" spans="1:3">
       <c r="A91" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B91" s="21"/>
       <c r="C91" s="21"/>
     </row>
     <row r="92" ht="16.5" spans="1:3">
       <c r="A92" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
@@ -31615,7 +31635,7 @@
         <v>https://eduardoherreraf.github.io/javascript-como_ejecutar_un_codigo_javascript.html</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E93" s="16"/>
     </row>
@@ -31637,7 +31657,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C95" s="17"/>
       <c r="E95" s="16"/>
@@ -31652,19 +31672,19 @@
         <v>0.6</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
       <c r="A97" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="20"/>
     </row>
     <row r="98" ht="16.5" spans="1:3">
       <c r="A98" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
@@ -31679,7 +31699,7 @@
         <v>https://eduardoherreraf.github.io/javascript-configurar_el_entorno_de_trabajo_javascript.html</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -31700,7 +31720,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C101" s="17"/>
       <c r="E101" s="16"/>
@@ -31715,27 +31735,27 @@
         <v>0.6</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E102" s="16"/>
     </row>
     <row r="103" ht="15.75" spans="1:3">
       <c r="A103" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20"/>
     </row>
     <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="21"/>
     </row>
     <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="12"/>
@@ -31750,7 +31770,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-16_metadatos_y_exportacion.html</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E106" s="16"/>
     </row>
@@ -31772,7 +31792,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C108" s="17"/>
       <c r="E108" s="16"/>
@@ -31787,19 +31807,19 @@
         <v>0.6</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" ht="15.75" spans="1:3">
       <c r="A110" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="20"/>
     </row>
     <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="12"/>
@@ -31814,7 +31834,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-15_filtros_licuar.html</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E112" s="16"/>
     </row>
@@ -31836,7 +31856,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C114" s="17"/>
       <c r="E114" s="16"/>
@@ -31851,19 +31871,19 @@
         <v>0.6</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" ht="15.75" spans="1:3">
       <c r="A116" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B116" s="19"/>
       <c r="C116" s="20"/>
     </row>
     <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="12"/>
@@ -31878,7 +31898,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-14_filtros_neurales.html</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E118" s="16"/>
     </row>
@@ -31900,7 +31920,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C120" s="17"/>
       <c r="E120" s="16"/>
@@ -31915,19 +31935,19 @@
         <v>0.6</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" ht="15.75" spans="1:3">
       <c r="A122" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="20"/>
     </row>
     <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="12"/>
@@ -31942,7 +31962,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-13_filtros.html</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E124" s="16"/>
     </row>
@@ -31964,7 +31984,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C126" s="17"/>
       <c r="E126" s="16"/>
@@ -31979,19 +31999,19 @@
         <v>0.6</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" ht="15.75" spans="1:3">
       <c r="A128" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B128" s="19"/>
       <c r="C128" s="20"/>
     </row>
     <row r="129" ht="16.5" spans="1:3">
       <c r="A129" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="12"/>
@@ -32006,7 +32026,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-12_formas_y_capas.html</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E130" s="16"/>
     </row>
@@ -32028,7 +32048,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C132" s="17"/>
       <c r="E132" s="16"/>
@@ -32043,19 +32063,19 @@
         <v>0.6</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:3">
       <c r="A134" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="20"/>
     </row>
     <row r="135" ht="16.5" spans="1:3">
       <c r="A135" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="12"/>
@@ -32070,7 +32090,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-11_textos.html</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E136" s="16"/>
     </row>
@@ -32092,7 +32112,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C138" s="17"/>
       <c r="E138" s="16"/>
@@ -32107,19 +32127,19 @@
         <v>0.6</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:3">
       <c r="A140" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="20"/>
     </row>
     <row r="141" ht="16.5" spans="1:3">
       <c r="A141" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="12"/>
@@ -32134,7 +32154,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-10_color_y_degradados.html</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E142" s="16"/>
     </row>
@@ -32156,7 +32176,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C144" s="17"/>
       <c r="E144" s="16"/>
@@ -32171,19 +32191,19 @@
         <v>0.6</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:3">
       <c r="A146" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B146" s="19"/>
       <c r="C146" s="20"/>
     </row>
     <row r="147" ht="16.5" spans="1:3">
       <c r="A147" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="12"/>
@@ -32198,7 +32218,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-09_uso_de_pinceles.html</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E148" s="16"/>
     </row>
@@ -32220,7 +32240,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C150" s="17"/>
       <c r="E150" s="16"/>
@@ -32235,19 +32255,19 @@
         <v>0.6</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="152" ht="15.75" spans="1:3">
       <c r="A152" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="20"/>
     </row>
     <row r="153" ht="16.5" spans="1:3">
       <c r="A153" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="12"/>
@@ -32262,7 +32282,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-08_agregar_y_quitar_objetos.html</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E154" s="16"/>
     </row>
@@ -32284,7 +32304,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C156" s="17"/>
       <c r="E156" s="16"/>
@@ -32299,19 +32319,19 @@
         <v>0.6</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="158" ht="15.75" spans="1:3">
       <c r="A158" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B158" s="19"/>
       <c r="C158" s="20"/>
     </row>
     <row r="159" ht="16.5" spans="1:3">
       <c r="A159" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="12"/>
@@ -32326,7 +32346,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-07_herramientas_de_seleccion.html</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E160" s="16"/>
     </row>
@@ -32348,7 +32368,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C162" s="17"/>
       <c r="E162" s="16"/>
@@ -32363,19 +32383,19 @@
         <v>0.6</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" ht="15.75" spans="1:3">
       <c r="A164" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="20"/>
     </row>
     <row r="165" ht="16.5" spans="1:3">
       <c r="A165" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="12"/>
@@ -32390,7 +32410,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-06_ajuste_tono_brillo_y_saturacion.html</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E166" s="16"/>
     </row>
@@ -32412,7 +32432,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C168" s="17"/>
       <c r="E168" s="16"/>
@@ -32427,19 +32447,19 @@
         <v>0.6</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" ht="15.75" spans="1:3">
       <c r="A170" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B170" s="19"/>
       <c r="C170" s="20"/>
     </row>
     <row r="171" ht="16.5" spans="1:3">
       <c r="A171" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="12"/>
@@ -32454,7 +32474,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-05_trabajo_con_capas.html</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E172" s="16"/>
     </row>
@@ -32476,7 +32496,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C174" s="17"/>
       <c r="E174" s="16"/>
@@ -32491,19 +32511,19 @@
         <v>0.6</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="176" ht="15.75" spans="1:3">
       <c r="A176" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B176" s="19"/>
       <c r="C176" s="20"/>
     </row>
     <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="12"/>
@@ -32518,7 +32538,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-04_ajuste_lienzo_resolucion.html</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E178" s="16"/>
     </row>
@@ -32540,7 +32560,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C180" s="17"/>
       <c r="E180" s="16"/>
@@ -32555,19 +32575,19 @@
         <v>0.6</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="182" ht="15.75" spans="1:3">
       <c r="A182" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="20"/>
     </row>
     <row r="183" ht="16.5" spans="1:3">
       <c r="A183" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="12"/>
@@ -32582,7 +32602,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-03_compartir_y_editar_archivos.html</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E184" s="16"/>
     </row>
@@ -32604,7 +32624,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C186" s="17"/>
       <c r="E186" s="16"/>
@@ -32619,19 +32639,19 @@
         <v>0.6</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" ht="15.75" spans="1:3">
       <c r="A188" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B188" s="19"/>
       <c r="C188" s="20"/>
     </row>
     <row r="189" ht="16.5" spans="1:3">
       <c r="A189" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="12"/>
@@ -32646,7 +32666,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-02_interfaz_y_area_de_trabajo.html</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E190" s="16"/>
     </row>
@@ -32668,7 +32688,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C192" s="17"/>
       <c r="E192" s="16"/>
@@ -32683,19 +32703,19 @@
         <v>0.6</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" ht="15.75" spans="1:3">
       <c r="A194" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B194" s="19"/>
       <c r="C194" s="20"/>
     </row>
     <row r="195" ht="16.5" spans="1:3">
       <c r="A195" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="12"/>
@@ -32710,7 +32730,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-01_comenzando_un_proyecto.html</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -32731,7 +32751,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C198" s="17"/>
       <c r="E198" s="16"/>
@@ -32746,27 +32766,27 @@
         <v>0.6</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E199" s="16"/>
     </row>
     <row r="200" ht="15.75" spans="1:3">
       <c r="A200" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B200" s="19"/>
       <c r="C200" s="20"/>
     </row>
     <row r="201" ht="16.5" spans="1:3">
       <c r="A201" s="21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B201" s="21"/>
       <c r="C201" s="21"/>
     </row>
     <row r="202" ht="16.5" spans="1:3">
       <c r="A202" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="12"/>
@@ -32781,7 +32801,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E203" s="16"/>
     </row>
@@ -32803,7 +32823,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C205" s="17"/>
       <c r="E205" s="16"/>
@@ -32818,19 +32838,19 @@
         <v>0.6</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="207" ht="15.75" spans="1:3">
       <c r="A207" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B207" s="19"/>
       <c r="C207" s="20"/>
     </row>
     <row r="208" ht="16.5" spans="1:3">
       <c r="A208" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="12"/>
@@ -32845,7 +32865,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_borrar_la_cache_y_archivos_basura_en_windows.html</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -32866,7 +32886,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C211" s="17"/>
       <c r="E211" s="16"/>
@@ -32881,27 +32901,27 @@
         <v>0.6</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E212" s="16"/>
     </row>
     <row r="213" ht="15.75" spans="1:3">
       <c r="A213" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B213" s="19"/>
       <c r="C213" s="20"/>
     </row>
     <row r="214" ht="16.5" spans="1:3">
       <c r="A214" s="21" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B214" s="21"/>
       <c r="C214" s="21"/>
     </row>
     <row r="215" ht="16.5" spans="1:3">
       <c r="A215" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="12"/>
@@ -32916,7 +32936,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0101_introduccion.html</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E216" s="16"/>
     </row>
@@ -32938,7 +32958,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C218" s="17"/>
       <c r="E218" s="16"/>
@@ -32953,19 +32973,19 @@
         <v>0.6</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="220" ht="15.75" spans="1:3">
       <c r="A220" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B220" s="19"/>
       <c r="C220" s="20"/>
     </row>
     <row r="221" ht="16.5" spans="1:3">
       <c r="A221" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="12"/>
@@ -32980,7 +33000,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0102_instalacion_de_python_localmente.html</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E222" s="16"/>
     </row>
@@ -33002,7 +33022,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C224" s="17"/>
       <c r="E224" s="16"/>
@@ -33017,19 +33037,19 @@
         <v>0.6</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="226" ht="15.75" spans="1:3">
       <c r="A226" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B226" s="19"/>
       <c r="C226" s="20"/>
     </row>
     <row r="227" ht="16.5" spans="1:3">
       <c r="A227" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="12"/>
@@ -33044,7 +33064,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0201_funcion_print.html</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E228" s="16"/>
     </row>
@@ -33066,7 +33086,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C230" s="17"/>
       <c r="E230" s="16"/>
@@ -33081,19 +33101,19 @@
         <v>0.6</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="232" ht="15.75" spans="1:3">
       <c r="A232" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B232" s="19"/>
       <c r="C232" s="20"/>
     </row>
     <row r="233" ht="16.5" spans="1:3">
       <c r="A233" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B233" s="11"/>
       <c r="C233" s="12"/>
@@ -33108,7 +33128,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0202_literales.html</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E234" s="16"/>
     </row>
@@ -33130,7 +33150,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C236" s="17"/>
       <c r="E236" s="16"/>
@@ -33145,19 +33165,19 @@
         <v>0.6</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="238" ht="15.75" spans="1:3">
       <c r="A238" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="20"/>
     </row>
     <row r="239" ht="16.5" spans="1:3">
       <c r="A239" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B239" s="11"/>
       <c r="C239" s="12"/>
@@ -33172,7 +33192,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0203_operadores.html</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E240" s="16"/>
     </row>
@@ -33194,7 +33214,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C242" s="17"/>
       <c r="E242" s="16"/>
@@ -33209,19 +33229,19 @@
         <v>0.6</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="244" ht="15.75" spans="1:3">
       <c r="A244" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B244" s="19"/>
       <c r="C244" s="20"/>
     </row>
     <row r="245" ht="16.5" spans="1:3">
       <c r="A245" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B245" s="11"/>
       <c r="C245" s="12"/>
@@ -33236,7 +33256,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0204_variables.html</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E246" s="16"/>
     </row>
@@ -33258,7 +33278,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C248" s="17"/>
       <c r="E248" s="16"/>
@@ -33273,19 +33293,19 @@
         <v>0.6</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="250" ht="15.75" spans="1:3">
       <c r="A250" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B250" s="19"/>
       <c r="C250" s="20"/>
     </row>
     <row r="251" ht="16.5" spans="1:3">
       <c r="A251" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B251" s="11"/>
       <c r="C251" s="12"/>
@@ -33300,7 +33320,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0205_comentarios.html</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E252" s="16"/>
     </row>
@@ -33322,7 +33342,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C254" s="17"/>
       <c r="E254" s="16"/>
@@ -33337,19 +33357,19 @@
         <v>0.6</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="256" ht="15.75" spans="1:3">
       <c r="A256" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B256" s="19"/>
       <c r="C256" s="20"/>
     </row>
     <row r="257" ht="16.5" spans="1:3">
       <c r="A257" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="12"/>
@@ -33364,7 +33384,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0206_interaccion_con_el_usuario.html</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E258" s="16"/>
     </row>
@@ -33386,7 +33406,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C260" s="17"/>
       <c r="E260" s="16"/>
@@ -33401,19 +33421,19 @@
         <v>0.6</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="262" ht="15.75" spans="1:3">
       <c r="A262" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B262" s="19"/>
       <c r="C262" s="20"/>
     </row>
     <row r="263" ht="16.5" spans="1:3">
       <c r="A263" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="12"/>
@@ -33428,7 +33448,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0301_operadores_de_comparacion_y_logicos_en_python.html</v>
       </c>
       <c r="C264" s="15" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E264" s="16"/>
     </row>
@@ -33450,7 +33470,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B266" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C266" s="17"/>
       <c r="E266" s="16"/>
@@ -33465,19 +33485,19 @@
         <v>0.6</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" ht="15.75" spans="1:3">
       <c r="A268" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B268" s="19"/>
       <c r="C268" s="20"/>
     </row>
     <row r="269" ht="16.5" spans="1:3">
       <c r="A269" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B269" s="11"/>
       <c r="C269" s="12"/>
@@ -33492,7 +33512,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0302_sentencia_if_de_control_de_flujo.html</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E270" s="16"/>
     </row>
@@ -33514,7 +33534,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B272" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C272" s="17"/>
       <c r="E272" s="16"/>
@@ -33529,19 +33549,19 @@
         <v>0.6</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="274" ht="15.75" spans="1:3">
       <c r="A274" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B274" s="19"/>
       <c r="C274" s="20"/>
     </row>
     <row r="275" ht="16.5" spans="1:3">
       <c r="A275" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B275" s="11"/>
       <c r="C275" s="12"/>
@@ -33556,7 +33576,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0303_bucles_en_python_una_guia_completa.html</v>
       </c>
       <c r="C276" s="15" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E276" s="16"/>
     </row>
@@ -33578,7 +33598,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C278" s="17"/>
       <c r="E278" s="16"/>
@@ -33593,19 +33613,19 @@
         <v>0.6</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="280" ht="15.75" spans="1:3">
       <c r="A280" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B280" s="19"/>
       <c r="C280" s="20"/>
     </row>
     <row r="281" ht="16.5" spans="1:3">
       <c r="A281" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B281" s="11"/>
       <c r="C281" s="12"/>
@@ -33620,7 +33640,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0304_operadores_logicos_y_operaciones_bit_a_bit_en_python.html</v>
       </c>
       <c r="C282" s="15" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E282" s="16"/>
     </row>
@@ -33642,7 +33662,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C284" s="17"/>
       <c r="E284" s="16"/>
@@ -33657,19 +33677,19 @@
         <v>0.6</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="286" ht="15.75" spans="1:3">
       <c r="A286" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B286" s="19"/>
       <c r="C286" s="20"/>
     </row>
     <row r="287" ht="16.5" spans="1:3">
       <c r="A287" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B287" s="11"/>
       <c r="C287" s="12"/>
@@ -33684,7 +33704,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0305_listas.html</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E288" s="16"/>
     </row>
@@ -33706,7 +33726,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B290" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C290" s="17"/>
       <c r="E290" s="16"/>
@@ -33721,19 +33741,19 @@
         <v>0.6</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="292" ht="15.75" spans="1:3">
       <c r="A292" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B292" s="19"/>
       <c r="C292" s="20"/>
     </row>
     <row r="293" ht="16.5" spans="1:3">
       <c r="A293" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B293" s="11"/>
       <c r="C293" s="12"/>
@@ -33748,7 +33768,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0306_ordenamiento_de_listas_metodo_burbuja.html</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E294" s="16"/>
     </row>
@@ -33770,7 +33790,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C296" s="17"/>
       <c r="E296" s="16"/>
@@ -33785,19 +33805,19 @@
         <v>0.6</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="298" ht="15.75" spans="1:3">
       <c r="A298" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B298" s="19"/>
       <c r="C298" s="20"/>
     </row>
     <row r="299" ht="16.5" spans="1:3">
       <c r="A299" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B299" s="11"/>
       <c r="C299" s="12"/>
@@ -33812,7 +33832,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0307_operaciones_con_listas.html</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E300" s="16"/>
     </row>
@@ -33834,7 +33854,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C302" s="17"/>
       <c r="E302" s="16"/>
@@ -33849,19 +33869,19 @@
         <v>0.6</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="304" ht="15.75" spans="1:3">
       <c r="A304" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B304" s="19"/>
       <c r="C304" s="20"/>
     </row>
     <row r="305" ht="16.5" spans="1:3">
       <c r="A305" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B305" s="11"/>
       <c r="C305" s="12"/>
@@ -33876,7 +33896,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0401_introduccion_funciones.html</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E306" s="16"/>
     </row>
@@ -33898,7 +33918,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C308" s="17"/>
       <c r="E308" s="16"/>
@@ -33913,19 +33933,19 @@
         <v>0.6</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="310" ht="15.75" spans="1:3">
       <c r="A310" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B310" s="19"/>
       <c r="C310" s="20"/>
     </row>
     <row r="311" ht="16.5" spans="1:3">
       <c r="A311" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B311" s="11"/>
       <c r="C311" s="12"/>
@@ -33940,7 +33960,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0402_como_las_funciones_se_comunican_con_su_entorno.html</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E312" s="16"/>
     </row>
@@ -33962,7 +33982,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B314" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C314" s="17"/>
       <c r="E314" s="16"/>
@@ -33977,19 +33997,19 @@
         <v>0.6</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="316" ht="15.75" spans="1:3">
       <c r="A316" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B316" s="19"/>
       <c r="C316" s="20"/>
     </row>
     <row r="317" ht="16.5" spans="1:3">
       <c r="A317" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B317" s="11"/>
       <c r="C317" s="12"/>
@@ -34004,7 +34024,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0403_retorno_de_valores_en_funciones.html</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E318" s="16"/>
     </row>
@@ -34026,7 +34046,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B320" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C320" s="17"/>
       <c r="E320" s="16"/>
@@ -34041,19 +34061,19 @@
         <v>0.6</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="322" ht="15.75" spans="1:3">
       <c r="A322" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B322" s="19"/>
       <c r="C322" s="20"/>
     </row>
     <row r="323" ht="16.5" spans="1:3">
       <c r="A323" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B323" s="11"/>
       <c r="C323" s="12"/>
@@ -34068,7 +34088,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0404_el_alcance_de_las_variables.html</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E324" s="16"/>
     </row>
@@ -34090,7 +34110,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B326" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C326" s="17"/>
       <c r="E326" s="16"/>
@@ -34105,19 +34125,19 @@
         <v>0.6</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="328" ht="15.75" spans="1:3">
       <c r="A328" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B328" s="19"/>
       <c r="C328" s="20"/>
     </row>
     <row r="329" ht="16.5" spans="1:3">
       <c r="A329" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="12"/>
@@ -34132,7 +34152,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0405_tuplas_y_diccionarios.html</v>
       </c>
       <c r="C330" s="15" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E330" s="16"/>
     </row>
@@ -34154,7 +34174,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B332" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C332" s="17"/>
       <c r="E332" s="16"/>
@@ -34169,19 +34189,19 @@
         <v>0.6</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="334" ht="15.75" spans="1:3">
       <c r="A334" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B334" s="19"/>
       <c r="C334" s="20"/>
     </row>
     <row r="335" ht="16.5" spans="1:3">
       <c r="A335" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B335" s="11"/>
       <c r="C335" s="12"/>
@@ -34196,7 +34216,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0501_introduccion_a_los_modulos.html</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E336" s="16"/>
     </row>
@@ -34218,7 +34238,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B338" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C338" s="17"/>
       <c r="E338" s="16"/>
@@ -34233,19 +34253,19 @@
         <v>0.6</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="340" ht="15.75" spans="1:3">
       <c r="A340" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B340" s="19"/>
       <c r="C340" s="20"/>
     </row>
     <row r="341" ht="16.5" spans="1:3">
       <c r="A341" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B341" s="11"/>
       <c r="C341" s="12"/>
@@ -34260,7 +34280,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0502_importacion_de_modulos.html</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E342" s="16"/>
     </row>
@@ -34282,7 +34302,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B344" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C344" s="17"/>
       <c r="E344" s="16"/>
@@ -34297,19 +34317,19 @@
         <v>0.6</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="346" ht="15.75" spans="1:3">
       <c r="A346" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B346" s="19"/>
       <c r="C346" s="20"/>
     </row>
     <row r="347" ht="16.5" spans="1:3">
       <c r="A347" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B347" s="11"/>
       <c r="C347" s="12"/>
@@ -34324,7 +34344,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0503_modulos_especializados_de_python-matematico_aleatorio_y_de_sistema.html</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E348" s="16"/>
     </row>
@@ -34346,7 +34366,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B350" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C350" s="17"/>
       <c r="E350" s="16"/>
@@ -34361,19 +34381,19 @@
         <v>0.6</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="352" ht="15.75" spans="1:3">
       <c r="A352" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B352" s="19"/>
       <c r="C352" s="20"/>
     </row>
     <row r="353" ht="16.5" spans="1:3">
       <c r="A353" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B353" s="11"/>
       <c r="C353" s="12"/>
@@ -34388,7 +34408,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0504_modulos_y_paquetes.html</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E354" s="16"/>
     </row>
@@ -34410,7 +34430,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B356" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C356" s="17"/>
       <c r="E356" s="16"/>
@@ -34425,19 +34445,19 @@
         <v>0.6</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="358" ht="15.75" spans="1:3">
       <c r="A358" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B358" s="19"/>
       <c r="C358" s="20"/>
     </row>
     <row r="359" ht="16.5" spans="1:3">
       <c r="A359" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B359" s="11"/>
       <c r="C359" s="12"/>
@@ -34452,7 +34472,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0505_instalador_de_paquetes_PIP.html</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E360" s="16"/>
     </row>
@@ -34474,7 +34494,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B362" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C362" s="17"/>
       <c r="E362" s="16"/>
@@ -34489,19 +34509,19 @@
         <v>0.6</v>
       </c>
       <c r="C363" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="364" ht="15.75" spans="1:3">
       <c r="A364" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B364" s="19"/>
       <c r="C364" s="20"/>
     </row>
     <row r="365" ht="16.5" spans="1:3">
       <c r="A365" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B365" s="11"/>
       <c r="C365" s="12"/>
@@ -34516,7 +34536,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0601_la_naturaleza_de_las_cadenas.html</v>
       </c>
       <c r="C366" s="15" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E366" s="16"/>
     </row>
@@ -34538,7 +34558,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C368" s="17"/>
       <c r="E368" s="16"/>
@@ -34553,19 +34573,19 @@
         <v>0.6</v>
       </c>
       <c r="C369" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="370" ht="15.75" spans="1:3">
       <c r="A370" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B370" s="19"/>
       <c r="C370" s="20"/>
     </row>
     <row r="371" ht="16.5" spans="1:3">
       <c r="A371" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B371" s="11"/>
       <c r="C371" s="12"/>
@@ -34580,7 +34600,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0602_errores-el_pan_diario_del_programador.html</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E372" s="16"/>
     </row>
@@ -34602,7 +34622,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C374" s="17"/>
       <c r="E374" s="16"/>
@@ -34617,19 +34637,19 @@
         <v>0.6</v>
       </c>
       <c r="C375" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="376" ht="15.75" spans="1:3">
       <c r="A376" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B376" s="19"/>
       <c r="C376" s="20"/>
     </row>
     <row r="377" ht="16.5" spans="1:3">
       <c r="A377" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B377" s="11"/>
       <c r="C377" s="12"/>
@@ -34644,7 +34664,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0701_los_fundamentos_de_la_poo.html</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E378" s="16"/>
     </row>
@@ -34666,7 +34686,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C380" s="17"/>
       <c r="E380" s="16"/>
@@ -34681,19 +34701,19 @@
         <v>0.6</v>
       </c>
       <c r="C381" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="382" ht="15.75" spans="1:3">
       <c r="A382" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B382" s="19"/>
       <c r="C382" s="20"/>
     </row>
     <row r="383" ht="16.5" spans="1:3">
       <c r="A383" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B383" s="11"/>
       <c r="C383" s="12"/>
@@ -34708,7 +34728,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0702_comparando_paradigmas_programacion_procedimental_y_orientada_a_objetos.html</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E384" s="16"/>
     </row>
@@ -34730,7 +34750,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C386" s="17"/>
       <c r="E386" s="16"/>
@@ -34745,19 +34765,19 @@
         <v>0.6</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="388" ht="15.75" spans="1:3">
       <c r="A388" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B388" s="19"/>
       <c r="C388" s="20"/>
     </row>
     <row r="389" ht="16.5" spans="1:3">
       <c r="A389" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B389" s="11"/>
       <c r="C389" s="12"/>
@@ -34772,7 +34792,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0703_poo_propiedades.html</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E390" s="16"/>
     </row>
@@ -34794,7 +34814,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C392" s="17"/>
       <c r="E392" s="16"/>
@@ -34809,19 +34829,19 @@
         <v>0.6</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="394" ht="15.75" spans="1:3">
       <c r="A394" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="20"/>
     </row>
     <row r="395" ht="16.5" spans="1:3">
       <c r="A395" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="12"/>
@@ -34836,7 +34856,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0704_poo_metodos.html</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E396" s="16"/>
     </row>
@@ -34858,7 +34878,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C398" s="17"/>
       <c r="E398" s="16"/>
@@ -34873,19 +34893,19 @@
         <v>0.6</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="400" ht="15.75" spans="1:3">
       <c r="A400" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B400" s="19"/>
       <c r="C400" s="20"/>
     </row>
     <row r="401" ht="16.5" spans="1:3">
       <c r="A401" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B401" s="11"/>
       <c r="C401" s="12"/>
@@ -34900,7 +34920,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0705_poo_herencia.html</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E402" s="16"/>
     </row>
@@ -34922,7 +34942,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C404" s="17"/>
       <c r="E404" s="16"/>
@@ -34937,19 +34957,19 @@
         <v>0.6</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="406" ht="15.75" spans="1:3">
       <c r="A406" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B406" s="19"/>
       <c r="C406" s="20"/>
     </row>
     <row r="407" ht="16.5" spans="1:3">
       <c r="A407" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B407" s="11"/>
       <c r="C407" s="12"/>
@@ -34964,7 +34984,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0706_poo_excepciones.html</v>
       </c>
       <c r="C408" s="15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E408" s="16"/>
     </row>
@@ -34986,7 +35006,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C410" s="17"/>
       <c r="E410" s="16"/>
@@ -35001,19 +35021,19 @@
         <v>0.6</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="412" ht="15.75" spans="1:3">
       <c r="A412" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B412" s="19"/>
       <c r="C412" s="20"/>
     </row>
     <row r="413" ht="16.5" spans="1:3">
       <c r="A413" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="12"/>
@@ -35028,7 +35048,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0801_iteradores,_generadores_y_cierres.html</v>
       </c>
       <c r="C414" s="15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E414" s="16"/>
     </row>
@@ -35050,7 +35070,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C416" s="17"/>
       <c r="E416" s="16"/>
@@ -35065,19 +35085,19 @@
         <v>0.6</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="418" ht="15.75" spans="1:3">
       <c r="A418" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B418" s="19"/>
       <c r="C418" s="20"/>
     </row>
     <row r="419" ht="16.5" spans="1:3">
       <c r="A419" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="12"/>
@@ -35092,7 +35112,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0802_manejo_de_archivos.html</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E420" s="16"/>
     </row>
@@ -35114,7 +35134,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C422" s="17"/>
       <c r="E422" s="16"/>
@@ -35129,19 +35149,19 @@
         <v>0.6</v>
       </c>
       <c r="C423" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="424" ht="15.75" spans="1:3">
       <c r="A424" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B424" s="19"/>
       <c r="C424" s="20"/>
     </row>
     <row r="425" ht="16.5" spans="1:3">
       <c r="A425" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="12"/>
@@ -35156,7 +35176,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0803_el_modulo_os_interactuando_con_el_sistema_operativo.html</v>
       </c>
       <c r="C426" s="15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E426" s="16"/>
     </row>
@@ -35178,7 +35198,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C428" s="17"/>
       <c r="E428" s="16"/>
@@ -35193,19 +35213,19 @@
         <v>0.6</v>
       </c>
       <c r="C429" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="430" ht="15.75" spans="1:3">
       <c r="A430" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B430" s="19"/>
       <c r="C430" s="20"/>
     </row>
     <row r="431" ht="16.5" spans="1:3">
       <c r="A431" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="12"/>
@@ -35220,7 +35240,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html</v>
       </c>
       <c r="C432" s="15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E432" s="16"/>
     </row>
@@ -35242,7 +35262,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C434" s="17"/>
       <c r="E434" s="16"/>
@@ -35257,19 +35277,19 @@
         <v>0.6</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="436" ht="15.75" spans="1:3">
       <c r="A436" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B436" s="19"/>
       <c r="C436" s="20"/>
     </row>
     <row r="437" ht="16.5" spans="1:3">
       <c r="A437" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="12"/>
@@ -35284,7 +35304,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html</v>
       </c>
       <c r="C438" s="15" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -35304,7 +35324,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C440" s="17"/>
     </row>
@@ -35318,19 +35338,19 @@
         <v>0.6</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="442" ht="15.75" spans="1:3">
       <c r="A442" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B442" s="19"/>
       <c r="C442" s="20"/>
     </row>
     <row r="443" ht="15.75" spans="1:3">
       <c r="A443" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C443" s="22"/>
     </row>
@@ -35620,13 +35640,13 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -35635,78 +35655,78 @@
         <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -35715,16 +35735,16 @@
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -35733,7 +35753,7 @@
         <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -35742,51 +35762,51 @@
         <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4"/>
       <c r="D20" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/src/Head.xlsx
+++ b/src/Head.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="308">
   <si>
     <t>Título</t>
   </si>
@@ -529,10 +529,10 @@
     <t xml:space="preserve">Título 1 </t>
   </si>
   <si>
-    <t>Indroducción</t>
+    <t>Instalación y Configuración de Node.js</t>
   </si>
   <si>
-    <t>Ejemplo de Salida</t>
+    <t>Instalar Node.js</t>
   </si>
   <si>
     <t>id</t>
@@ -577,25 +577,22 @@
     <t>Título 2</t>
   </si>
   <si>
-    <t>Alias de Git Más Usados</t>
+    <t>Instalación de un Navegador</t>
   </si>
   <si>
-    <t>Alias para comandos básicos</t>
+    <t>Verificar la Instalación</t>
   </si>
   <si>
     <t>Título 3</t>
   </si>
   <si>
-    <t>Cómo Ver los alias Configurados</t>
-  </si>
-  <si>
-    <t>Alias para Agregar y Confirmar Cambios</t>
+    <t>Crear un Nuevo Proyecto en Node.js</t>
   </si>
   <si>
     <t>Título 4</t>
   </si>
   <si>
-    <t>Configuraciones Específicas de Color</t>
+    <t>Instalar Dependencias y Paquetes</t>
   </si>
   <si>
     <t>Título 5</t>
@@ -604,34 +601,16 @@
     <t>ff</t>
   </si>
   <si>
-    <t>Personalización Avanzada de Colores</t>
-  </si>
-  <si>
-    <t>Alias para Manejar Ramas</t>
+    <t>Crear y Ejecutar un Servidor con Express</t>
   </si>
   <si>
     <t>Título 6</t>
   </si>
   <si>
-    <t>Verificación de la Configuración</t>
-  </si>
-  <si>
-    <t>Alias para Reiniciar y Limpiar Cambios</t>
-  </si>
-  <si>
     <t>Título 7</t>
   </si>
   <si>
-    <t>¿Cuándo es Necesario Ejecutar estos Comandos?</t>
-  </si>
-  <si>
-    <t>Alias Avanzados</t>
-  </si>
-  <si>
     <t>Título 8</t>
-  </si>
-  <si>
-    <t>Alias para Trabajar con Remotos</t>
   </si>
   <si>
     <t>Título 9</t>
@@ -682,13 +661,13 @@
     <t>&lt;ul&gt;</t>
   </si>
   <si>
-    <t>Después de instalar Git: Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.</t>
+    <t>Crear un archivo server.js en la carpeta del proyecto y agregar el siguiente código básico:</t>
   </si>
   <si>
-    <t>Cuando se usa una computadora compartida: Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.</t>
+    <t>Ejecutar el servidor con:</t>
   </si>
   <si>
-    <t>Al alternar entre identidades: Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.</t>
+    <t>&lt;li&gt;&lt;strong&gt;</t>
   </si>
   <si>
     <t>&lt;li&gt;&lt;span class="fw-bold"&gt;</t>
@@ -697,16 +676,13 @@
     <t>&lt;li&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve"> Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.</t>
+    <t>Hacer doble clic sobre el archivo instalador.</t>
   </si>
   <si>
-    <t>Si se han realizado cambios que no se quieren conservar.</t>
+    <t>Seguir las instrucciones del asistente de instalación, que generalmente consiste en hacer clic en "Siguiente" varias veces.</t>
   </si>
   <si>
-    <t>Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.</t>
-  </si>
-  <si>
-    <t>En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.</t>
+    <t>Finalmente, hacer clic en "Instalar" y esperar a que el proceso finalice.</t>
   </si>
   <si>
     <t>&lt;p&gt;</t>
@@ -715,10 +691,10 @@
     <t>&lt;/p&gt;</t>
   </si>
   <si>
-    <t>Los comandos de configuración inicial de Git permiten establecer parámetros globales que definen cómo Git interactúa con el usuario y cómo se registran los cambios en los repositorios. Estos comandos suelen configurarse al instalar Git por primera vez y son esenciales para garantizar un correcto funcionamiento del sistema de control de versiones.</t>
+    <t>Para instalar cualquiera de estos navegadores, primero es necesario descargar el archivo instalador desde el sitio web oficial del navegador elegido. Este archivo suele tener una extensión .exe en Windows y .dmg en macOS.</t>
   </si>
   <si>
-    <t>A continuación, se explican los comandos de configuración inicial más importantes, cuándo deben utilizarse y cómo aplicarlos correctamente.</t>
+    <t>Una vez descargado el archivo, el proceso de instalación es sencillo:</t>
   </si>
   <si>
     <t>&lt;script&gt;let tema = localStorage.getItem("theme") || "dark";window.onload = function () {if (tema === "dark") temaOscuro();if (tema === "light") temaClaro();};const cambiarTema = () =&gt; {const temaActual = localStorage.getItem("theme") || "dark";if (temaActual === "dark") {temaClaro();} else{temaOscuro();}};const temaOscuro = () =&gt; {document.querySelector("body").setAttribute("data-bs-theme", "dark");document.querySelector("#dl-icon").setAttribute("class","btn text-center d-flex bg-body-tertiary text-light");localStorage.setItem("theme", "dark");};const temaClaro = () =&gt; {document.querySelector("body").setAttribute("data-bs-theme", "light");document.querySelector("#dl-icon").setAttribute("class", "btn text-center d-flex bg-light text-dark");localStorage.setItem("theme", "light");};&lt;/script&gt;&lt;/html&gt;</t>
@@ -23210,7 +23186,7 @@
     <col min="14" max="14" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="6:14">
+    <row r="1" spans="6:14">
       <c r="F1" s="31" t="str">
         <f>""</f>
         <v/>
@@ -23234,7 +23210,7 @@
       </c>
       <c r="F2" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D2," --&gt;")</f>
-        <v>&lt;!-- Indroducción --&gt;</v>
+        <v>&lt;!-- Instalación y Configuración de Node.js --&gt;</v>
       </c>
       <c r="G2" s="35"/>
       <c r="I2" s="32" t="s">
@@ -23248,7 +23224,7 @@
       <c r="M2" s="33"/>
       <c r="N2" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L2," --&gt;")</f>
-        <v>&lt;!-- Ejemplo de Salida --&gt;</v>
+        <v>&lt;!-- Instalar Node.js --&gt;</v>
       </c>
       <c r="O2" s="35"/>
     </row>
@@ -23286,13 +23262,13 @@
       <c r="A4" s="36"/>
       <c r="F4" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D2,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Indroducción&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Instalación y Configuración de Node.js&lt;/h3&gt;</v>
       </c>
       <c r="G4" s="39"/>
       <c r="I4" s="36"/>
       <c r="N4" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L2,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Ejemplo de Salida&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Instalar Node.js&lt;/h4&gt;</v>
       </c>
       <c r="O4" s="39"/>
     </row>
@@ -23359,7 +23335,7 @@
       <c r="E8" s="31"/>
       <c r="F8" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D2," fin --&gt;")</f>
-        <v>&lt;!-- Indroducción fin --&gt;</v>
+        <v>&lt;!-- Instalación y Configuración de Node.js fin --&gt;</v>
       </c>
       <c r="G8" s="42"/>
       <c r="I8" s="41"/>
@@ -23369,7 +23345,7 @@
       <c r="M8" s="31"/>
       <c r="N8" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L2," fin --&gt;")</f>
-        <v>&lt;!-- Ejemplo de Salida fin --&gt;</v>
+        <v>&lt;!-- Instalar Node.js fin --&gt;</v>
       </c>
       <c r="O8" s="42"/>
     </row>
@@ -23407,7 +23383,7 @@
       </c>
       <c r="F10" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D10," --&gt;")</f>
-        <v>&lt;!-- Alias de Git Más Usados --&gt;</v>
+        <v>&lt;!-- Instalación de un Navegador --&gt;</v>
       </c>
       <c r="G10" s="35"/>
       <c r="I10" s="32" t="s">
@@ -23423,7 +23399,7 @@
       </c>
       <c r="N10" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L10," --&gt;")</f>
-        <v>&lt;!-- Alias para comandos básicos --&gt;</v>
+        <v>&lt;!-- Verificar la Instalación --&gt;</v>
       </c>
       <c r="O10" s="35"/>
     </row>
@@ -23461,13 +23437,13 @@
       <c r="A12" s="36"/>
       <c r="F12" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D10,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Alias de Git Más Usados&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;Instalación de un Navegador&lt;/h3&gt;</v>
       </c>
       <c r="G12" s="39"/>
       <c r="I12" s="36"/>
       <c r="N12" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L10,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias para comandos básicos&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Verificar la Instalación&lt;/h4&gt;</v>
       </c>
       <c r="O12" s="39"/>
     </row>
@@ -23534,7 +23510,7 @@
       <c r="E16" s="31"/>
       <c r="F16" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D10," fin --&gt;")</f>
-        <v>&lt;!-- Alias de Git Más Usados fin --&gt;</v>
+        <v>&lt;!-- Instalación de un Navegador fin --&gt;</v>
       </c>
       <c r="G16" s="42"/>
       <c r="I16" s="41"/>
@@ -23544,7 +23520,7 @@
       <c r="M16" s="31"/>
       <c r="N16" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L10," fin --&gt;")</f>
-        <v>&lt;!-- Alias para comandos básicos fin --&gt;</v>
+        <v>&lt;!-- Verificar la Instalación fin --&gt;</v>
       </c>
       <c r="O16" s="42"/>
     </row>
@@ -23572,13 +23548,11 @@
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
-      <c r="D18" s="34" t="s">
-        <v>151</v>
-      </c>
+      <c r="D18" s="34"/>
       <c r="E18" s="33"/>
       <c r="F18" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D18," --&gt;")</f>
-        <v>&lt;!-- Cómo Ver los alias Configurados --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="G18" s="35"/>
       <c r="I18" s="32" t="s">
@@ -23587,12 +23561,12 @@
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M18" s="33"/>
       <c r="N18" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L18," --&gt;")</f>
-        <v>&lt;!-- Alias para Agregar y Confirmar Cambios --&gt;</v>
+        <v>&lt;!-- Crear un Nuevo Proyecto en Node.js --&gt;</v>
       </c>
       <c r="O18" s="35"/>
     </row>
@@ -23630,13 +23604,13 @@
       <c r="A20" s="36"/>
       <c r="F20" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D18,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Cómo Ver los alias Configurados&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;&lt;/h3&gt;</v>
       </c>
       <c r="G20" s="39"/>
       <c r="I20" s="36"/>
       <c r="N20" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L18,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias para Agregar y Confirmar Cambios&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Crear un Nuevo Proyecto en Node.js&lt;/h4&gt;</v>
       </c>
       <c r="O20" s="39"/>
     </row>
@@ -23700,7 +23674,7 @@
       <c r="E24" s="31"/>
       <c r="F24" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D18," fin --&gt;")</f>
-        <v>&lt;!-- Cómo Ver los alias Configurados fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="G24" s="42"/>
       <c r="I24" s="41"/>
@@ -23710,7 +23684,7 @@
       <c r="M24" s="31"/>
       <c r="N24" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L18," fin --&gt;")</f>
-        <v>&lt;!-- Alias para Agregar y Confirmar Cambios fin --&gt;</v>
+        <v>&lt;!-- Crear un Nuevo Proyecto en Node.js fin --&gt;</v>
       </c>
       <c r="O24" s="42"/>
     </row>
@@ -23736,29 +23710,29 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
-      <c r="D26" s="34" t="s">
-        <v>154</v>
-      </c>
+      <c r="D26" s="34"/>
       <c r="E26" s="33"/>
       <c r="F26" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," --&gt;")</f>
-        <v>&lt;!-- Configuraciones Específicas de Color --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="G26" s="35"/>
       <c r="I26" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J26" s="33"/>
       <c r="K26" s="33"/>
-      <c r="L26" s="34"/>
+      <c r="L26" s="34" t="s">
+        <v>153</v>
+      </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L26," --&gt;")</f>
-        <v>&lt;!--  --&gt;</v>
+        <v>&lt;!-- Instalar Dependencias y Paquetes --&gt;</v>
       </c>
       <c r="O26" s="35"/>
     </row>
@@ -23796,13 +23770,13 @@
       <c r="A28" s="36"/>
       <c r="F28" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D26,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Configuraciones Específicas de Color&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;&lt;/h3&gt;</v>
       </c>
       <c r="G28" s="39"/>
       <c r="I28" s="36"/>
       <c r="N28" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L26,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Instalar Dependencias y Paquetes&lt;/h4&gt;</v>
       </c>
       <c r="O28" s="39"/>
     </row>
@@ -23869,7 +23843,7 @@
       <c r="E32" s="31"/>
       <c r="F32" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D26," fin --&gt;")</f>
-        <v>&lt;!-- Configuraciones Específicas de Color fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="G32" s="42"/>
       <c r="I32" s="41"/>
@@ -23879,7 +23853,7 @@
       <c r="M32" s="31"/>
       <c r="N32" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L26," fin --&gt;")</f>
-        <v>&lt;!--  fin --&gt;</v>
+        <v>&lt;!-- Instalar Dependencias y Paquetes fin --&gt;</v>
       </c>
       <c r="O32" s="42"/>
     </row>
@@ -23905,33 +23879,31 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="34" t="s">
-        <v>157</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D34" s="34"/>
       <c r="E34" s="33"/>
       <c r="F34" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," --&gt;")</f>
-        <v>&lt;!-- Personalización Avanzada de Colores --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="G34" s="35"/>
       <c r="I34" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J34" s="33"/>
       <c r="K34" s="33"/>
       <c r="L34" s="34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M34" s="33"/>
       <c r="N34" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L34," --&gt;")</f>
-        <v>&lt;!-- Alias para Manejar Ramas --&gt;</v>
+        <v>&lt;!-- Crear y Ejecutar un Servidor con Express --&gt;</v>
       </c>
       <c r="O34" s="35"/>
     </row>
@@ -23969,13 +23941,13 @@
       <c r="A36" s="36"/>
       <c r="F36" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D34,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Personalización Avanzada de Colores&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;&lt;/h3&gt;</v>
       </c>
       <c r="G36" s="39"/>
       <c r="I36" s="36"/>
       <c r="N36" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L34,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias para Manejar Ramas&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;Crear y Ejecutar un Servidor con Express&lt;/h4&gt;</v>
       </c>
       <c r="O36" s="39"/>
     </row>
@@ -24039,7 +24011,7 @@
       <c r="E40" s="31"/>
       <c r="F40" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D34," fin --&gt;")</f>
-        <v>&lt;!-- Personalización Avanzada de Colores fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="G40" s="42"/>
       <c r="I40" s="41"/>
@@ -24049,7 +24021,7 @@
       <c r="M40" s="31"/>
       <c r="N40" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L34," fin --&gt;")</f>
-        <v>&lt;!-- Alias para Manejar Ramas fin --&gt;</v>
+        <v>&lt;!-- Crear y Ejecutar un Servidor con Express fin --&gt;</v>
       </c>
       <c r="O40" s="42"/>
     </row>
@@ -24075,31 +24047,27 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B42" s="33"/>
       <c r="C42" s="33"/>
-      <c r="D42" s="34" t="s">
-        <v>160</v>
-      </c>
+      <c r="D42" s="34"/>
       <c r="E42" s="33"/>
       <c r="F42" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," --&gt;")</f>
-        <v>&lt;!-- Verificación de la Configuración --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="G42" s="35"/>
       <c r="I42" s="32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J42" s="33"/>
       <c r="K42" s="33"/>
-      <c r="L42" s="34" t="s">
-        <v>161</v>
-      </c>
+      <c r="L42" s="34"/>
       <c r="M42" s="33"/>
       <c r="N42" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L42," --&gt;")</f>
-        <v>&lt;!-- Alias para Reiniciar y Limpiar Cambios --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="O42" s="35"/>
     </row>
@@ -24137,13 +24105,13 @@
       <c r="A44" s="36"/>
       <c r="F44" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D42,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;Verificación de la Configuración&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;&lt;/h3&gt;</v>
       </c>
       <c r="G44" s="39"/>
       <c r="I44" s="36"/>
       <c r="N44" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L42,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias para Reiniciar y Limpiar Cambios&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;&lt;/h4&gt;</v>
       </c>
       <c r="O44" s="39"/>
     </row>
@@ -24207,7 +24175,7 @@
       <c r="E48" s="31"/>
       <c r="F48" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D42," fin --&gt;")</f>
-        <v>&lt;!-- Verificación de la Configuración fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="G48" s="42"/>
       <c r="I48" s="41"/>
@@ -24217,7 +24185,7 @@
       <c r="M48" s="31"/>
       <c r="N48" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L42," fin --&gt;")</f>
-        <v>&lt;!-- Alias para Reiniciar y Limpiar Cambios fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="O48" s="42"/>
     </row>
@@ -24243,33 +24211,29 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="32" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B50" s="33"/>
       <c r="C50" s="33"/>
-      <c r="D50" s="34" t="s">
-        <v>163</v>
-      </c>
+      <c r="D50" s="34"/>
       <c r="E50" s="33"/>
       <c r="F50" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," --&gt;")</f>
-        <v>&lt;!-- ¿Cuándo es Necesario Ejecutar estos Comandos? --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="G50" s="35"/>
       <c r="I50" s="32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J50" s="33"/>
       <c r="K50" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="L50" s="34" t="s">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="L50" s="34"/>
       <c r="M50" s="33"/>
       <c r="N50" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L50," --&gt;")</f>
-        <v>&lt;!-- Alias Avanzados --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="O50" s="35"/>
     </row>
@@ -24307,13 +24271,13 @@
       <c r="A52" s="36"/>
       <c r="F52" t="str">
         <f>CONCATENATE("&lt;h3&gt;",D50,"&lt;/h3&gt;")</f>
-        <v>&lt;h3&gt;¿Cuándo es Necesario Ejecutar estos Comandos?&lt;/h3&gt;</v>
+        <v>&lt;h3&gt;&lt;/h3&gt;</v>
       </c>
       <c r="G52" s="39"/>
       <c r="I52" s="36"/>
       <c r="N52" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L50,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias Avanzados&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;&lt;/h4&gt;</v>
       </c>
       <c r="O52" s="39"/>
     </row>
@@ -24377,7 +24341,7 @@
       <c r="E56" s="31"/>
       <c r="F56" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",D50," fin --&gt;")</f>
-        <v>&lt;!-- ¿Cuándo es Necesario Ejecutar estos Comandos? fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="G56" s="42"/>
       <c r="I56" s="41"/>
@@ -24387,7 +24351,7 @@
       <c r="M56" s="31"/>
       <c r="N56" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L50," fin --&gt;")</f>
-        <v>&lt;!-- Alias Avanzados fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="O56" s="42"/>
     </row>
@@ -24413,7 +24377,7 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="32" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B58" s="33"/>
       <c r="C58" s="33"/>
@@ -24425,17 +24389,15 @@
       </c>
       <c r="G58" s="35"/>
       <c r="I58" s="32" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J58" s="33"/>
       <c r="K58" s="33"/>
-      <c r="L58" s="34" t="s">
-        <v>166</v>
-      </c>
+      <c r="L58" s="34"/>
       <c r="M58" s="33"/>
       <c r="N58" s="33" t="str">
         <f>CONCATENATE("&lt;!-- ",L58," --&gt;")</f>
-        <v>&lt;!-- Alias para Trabajar con Remotos --&gt;</v>
+        <v>&lt;!--  --&gt;</v>
       </c>
       <c r="O58" s="35"/>
     </row>
@@ -24479,7 +24441,7 @@
       <c r="I60" s="36"/>
       <c r="N60" t="str">
         <f>CONCATENATE("&lt;h4&gt;",L58,"&lt;/h4&gt;")</f>
-        <v>&lt;h4&gt;Alias para Trabajar con Remotos&lt;/h4&gt;</v>
+        <v>&lt;h4&gt;&lt;/h4&gt;</v>
       </c>
       <c r="O60" s="39"/>
     </row>
@@ -24553,7 +24515,7 @@
       <c r="M64" s="31"/>
       <c r="N64" s="31" t="str">
         <f>CONCATENATE("&lt;!-- ",L58," fin --&gt;")</f>
-        <v>&lt;!-- Alias para Trabajar con Remotos fin --&gt;</v>
+        <v>&lt;!--  fin --&gt;</v>
       </c>
       <c r="O64" s="42"/>
     </row>
@@ -24579,7 +24541,7 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B66" s="33"/>
       <c r="C66" s="33"/>
@@ -24591,7 +24553,7 @@
       </c>
       <c r="G66" s="35"/>
       <c r="I66" s="32" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J66" s="33"/>
       <c r="K66" s="33"/>
@@ -24743,7 +24705,7 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="32" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
@@ -24755,7 +24717,7 @@
       </c>
       <c r="G74" s="35"/>
       <c r="I74" s="32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J74" s="33"/>
       <c r="K74" s="33"/>
@@ -24907,7 +24869,7 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="32" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B82" s="33"/>
       <c r="C82" s="33"/>
@@ -24919,7 +24881,7 @@
       </c>
       <c r="G82" s="35"/>
       <c r="I82" s="32" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J82" s="33"/>
       <c r="K82" s="33"/>
@@ -25071,7 +25033,7 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="32" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -25083,7 +25045,7 @@
       </c>
       <c r="G90" s="35"/>
       <c r="I90" s="32" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J90" s="33"/>
       <c r="K90" s="33"/>
@@ -25235,7 +25197,7 @@
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="32" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B98" s="33"/>
       <c r="C98" s="33"/>
@@ -25247,7 +25209,7 @@
       </c>
       <c r="G98" s="35"/>
       <c r="I98" s="32" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J98" s="33"/>
       <c r="K98" s="33"/>
@@ -25399,7 +25361,7 @@
     </row>
     <row r="106" customFormat="1" spans="1:15">
       <c r="A106" s="32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B106" s="33"/>
       <c r="C106" s="33"/>
@@ -25411,7 +25373,7 @@
       </c>
       <c r="G106" s="35"/>
       <c r="I106" s="32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J106" s="33"/>
       <c r="K106" s="33"/>
@@ -25563,7 +25525,7 @@
     </row>
     <row r="114" customFormat="1" spans="1:15">
       <c r="A114" s="32" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B114" s="33"/>
       <c r="C114" s="33"/>
@@ -25575,7 +25537,7 @@
       </c>
       <c r="G114" s="35"/>
       <c r="I114" s="32" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J114" s="33"/>
       <c r="K114" s="33"/>
@@ -25727,7 +25689,7 @@
     </row>
     <row r="122" customFormat="1" spans="1:15">
       <c r="A122" s="32" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B122" s="33"/>
       <c r="C122" s="33"/>
@@ -25739,7 +25701,7 @@
       </c>
       <c r="G122" s="35"/>
       <c r="I122" s="32" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J122" s="33"/>
       <c r="K122" s="33"/>
@@ -25891,7 +25853,7 @@
     </row>
     <row r="130" customFormat="1" spans="1:15">
       <c r="A130" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B130" s="33"/>
       <c r="C130" s="33"/>
@@ -25903,7 +25865,7 @@
       </c>
       <c r="G130" s="35"/>
       <c r="I130" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J130" s="33"/>
       <c r="K130" s="33"/>
@@ -26055,7 +26017,7 @@
     </row>
     <row r="138" customFormat="1" spans="1:15">
       <c r="A138" s="32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B138" s="33"/>
       <c r="C138" s="33"/>
@@ -26067,7 +26029,7 @@
       </c>
       <c r="G138" s="35"/>
       <c r="I138" s="32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J138" s="33"/>
       <c r="K138" s="33"/>
@@ -26219,7 +26181,7 @@
     </row>
     <row r="146" customFormat="1" spans="1:15">
       <c r="A146" s="32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B146" s="33"/>
       <c r="C146" s="33"/>
@@ -26231,7 +26193,7 @@
       </c>
       <c r="G146" s="35"/>
       <c r="I146" s="32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J146" s="33"/>
       <c r="K146" s="33"/>
@@ -26383,7 +26345,7 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B154" s="33"/>
       <c r="C154" s="33"/>
@@ -26395,7 +26357,7 @@
       </c>
       <c r="G154" s="35"/>
       <c r="I154" s="32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J154" s="33"/>
       <c r="K154" s="33"/>
@@ -26547,7 +26509,7 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B162" s="33"/>
       <c r="C162" s="33"/>
@@ -26559,7 +26521,7 @@
       </c>
       <c r="G162" s="35"/>
       <c r="I162" s="32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J162" s="33"/>
       <c r="K162" s="33"/>
@@ -26711,7 +26673,7 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B170" s="33"/>
       <c r="C170" s="33"/>
@@ -26723,7 +26685,7 @@
       </c>
       <c r="G170" s="35"/>
       <c r="I170" s="32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J170" s="33"/>
       <c r="K170" s="33"/>
@@ -26875,7 +26837,7 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="32" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B178" s="33"/>
       <c r="C178" s="33"/>
@@ -26887,7 +26849,7 @@
       </c>
       <c r="G178" s="35"/>
       <c r="I178" s="32" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J178" s="33"/>
       <c r="K178" s="33"/>
@@ -27017,10 +26979,9 @@
       </c>
       <c r="O184" s="42"/>
     </row>
-    <row r="185" ht="15"/>
     <row r="186" spans="1:15">
       <c r="A186" s="32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B186" s="33"/>
       <c r="C186" s="33"/>
@@ -27032,7 +26993,7 @@
       </c>
       <c r="G186" s="35"/>
       <c r="I186" s="32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J186" s="33"/>
       <c r="K186" s="33"/>
@@ -27184,7 +27145,7 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="32" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B194" s="33"/>
       <c r="C194" s="33"/>
@@ -27196,7 +27157,7 @@
       </c>
       <c r="G194" s="35"/>
       <c r="I194" s="32" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J194" s="33"/>
       <c r="K194" s="33"/>
@@ -27348,7 +27309,7 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="32" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B202" s="33"/>
       <c r="C202" s="33"/>
@@ -27360,7 +27321,7 @@
       </c>
       <c r="G202" s="35"/>
       <c r="I202" s="32" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J202" s="33"/>
       <c r="K202" s="33"/>
@@ -27512,7 +27473,7 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B210" s="33"/>
       <c r="C210" s="33"/>
@@ -27524,7 +27485,7 @@
       </c>
       <c r="G210" s="35"/>
       <c r="I210" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J210" s="33"/>
       <c r="K210" s="33"/>
@@ -27676,7 +27637,7 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B218" s="33"/>
       <c r="C218" s="33"/>
@@ -27688,7 +27649,7 @@
       </c>
       <c r="G218" s="35"/>
       <c r="I218" s="32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J218" s="33"/>
       <c r="K218" s="33"/>
@@ -27840,7 +27801,7 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B226" s="33"/>
       <c r="C226" s="33"/>
@@ -27852,7 +27813,7 @@
       </c>
       <c r="G226" s="35"/>
       <c r="I226" s="32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J226" s="33"/>
       <c r="K226" s="33"/>
@@ -28004,7 +27965,7 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B234" s="33"/>
       <c r="C234" s="33"/>
@@ -28016,7 +27977,7 @@
       </c>
       <c r="G234" s="35"/>
       <c r="I234" s="32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J234" s="33"/>
       <c r="K234" s="33"/>
@@ -28168,7 +28129,7 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
@@ -28180,7 +28141,7 @@
       </c>
       <c r="G242" s="35"/>
       <c r="I242" s="32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J242" s="33"/>
       <c r="K242" s="33"/>
@@ -28332,7 +28293,7 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B250" s="33"/>
       <c r="C250" s="33"/>
@@ -28344,7 +28305,7 @@
       </c>
       <c r="G250" s="35"/>
       <c r="I250" s="32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J250" s="33"/>
       <c r="K250" s="33"/>
@@ -28496,7 +28457,7 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="32" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B258" s="33"/>
       <c r="C258" s="33"/>
@@ -28508,7 +28469,7 @@
       </c>
       <c r="G258" s="35"/>
       <c r="I258" s="32" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J258" s="33"/>
       <c r="K258" s="33"/>
@@ -28654,7 +28615,7 @@
   <sheetFormatPr defaultColWidth="52.625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="0.158333333333333" style="24" customWidth="1"/>
-    <col min="6" max="6" width="52.625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="53" style="24" customWidth="1"/>
     <col min="7" max="7" width="108.375" style="25" customWidth="1"/>
     <col min="8" max="16" width="52.625" style="24" customWidth="1"/>
     <col min="17" max="17" width="52.625" style="25" customWidth="1"/>
@@ -28663,19 +28624,19 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" s="25" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G2" s="25" t="str">
         <f>A2</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="Q2" s="25" t="str">
         <f>K2</f>
@@ -28684,177 +28645,175 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="24" t="str">
-        <f t="shared" ref="A3:A19" si="0">IF(F3&lt;&gt;"",$A$20,"")</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
+        <f>IF(F3&lt;&gt;"",$A$20,"")</f>
+        <v>&lt;li&gt;&lt;strong&gt;</v>
       </c>
       <c r="B3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",LEFT(F3,FIND(":",F3,1)-1),"")</f>
-        <v>Después de instalar Git</v>
+        <v>Crear un archivo server.js en la carpeta del proyecto y agregar el siguiente código básico</v>
       </c>
       <c r="C3" s="24" t="str">
-        <f t="shared" ref="C3:C19" si="1">IF(F3&lt;&gt;"","&lt;/span&gt;","")</f>
-        <v>&lt;/span&gt;</v>
+        <f>IF(F3&lt;&gt;"","&lt;/strong&gt;","")</f>
+        <v>&lt;/strong&gt;</v>
       </c>
       <c r="D3" s="24" t="str">
         <f>IF(F3&lt;&gt;"",RIGHT(F3,LEN(F3)-FIND(":",F3,1)),"")</f>
-        <v> Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.</v>
+        <v/>
       </c>
       <c r="E3" s="24" t="str">
-        <f t="shared" ref="E3:E19" si="2">IF(F3&lt;&gt;"","&lt;/li&gt;","")</f>
+        <f t="shared" ref="E3:E19" si="0">IF(F3&lt;&gt;"","&lt;/li&gt;","")</f>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G3" s="25" t="str">
         <f>IF(F3&lt;&gt;"",CONCATENATE(A3,B3,C3,":",D3,E3),IF(F2&lt;&gt;"",F3,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Después de instalar Git&lt;/span&gt;: Es recomendable configurarlos inmediatamente tras instalar Git en el equipo.&lt;/li&gt;</v>
+        <v>&lt;li&gt;&lt;strong&gt;Crear un archivo server.js en la carpeta del proyecto y agregar el siguiente código básico&lt;/strong&gt;:&lt;/li&gt;</v>
       </c>
       <c r="K3" s="24" t="str">
-        <f t="shared" ref="K3:K19" si="3">IF(P3&lt;&gt;"",$A$20,"")</f>
+        <f t="shared" ref="K3:K19" si="1">IF(P3&lt;&gt;"",$A$20,"")</f>
         <v/>
       </c>
       <c r="L3" s="24" t="str">
-        <f t="shared" ref="L3:L19" si="4">IF(P3&lt;&gt;"",LEFT(P3,FIND(":",P3,1)-1),"")</f>
+        <f t="shared" ref="L3:L19" si="2">IF(P3&lt;&gt;"",LEFT(P3,FIND(":",P3,1)-1),"")</f>
         <v/>
       </c>
       <c r="M3" s="24" t="str">
-        <f t="shared" ref="M3:M19" si="5">IF(P3&lt;&gt;"","&lt;/span&gt;","")</f>
+        <f t="shared" ref="M3:M19" si="3">IF(P3&lt;&gt;"","&lt;/span&gt;","")</f>
         <v/>
       </c>
       <c r="N3" s="24" t="str">
-        <f t="shared" ref="N3:N19" si="6">IF(P3&lt;&gt;"",RIGHT(P3,LEN(P3)-FIND(":",P3,1)),"")</f>
+        <f t="shared" ref="N3:N19" si="4">IF(P3&lt;&gt;"",RIGHT(P3,LEN(P3)-FIND(":",P3,1)),"")</f>
         <v/>
       </c>
       <c r="O3" s="24" t="str">
-        <f t="shared" ref="O3:O19" si="7">IF(P3&lt;&gt;"","&lt;/li&gt;","")</f>
+        <f t="shared" ref="O3:O19" si="5">IF(P3&lt;&gt;"","&lt;/li&gt;","")</f>
         <v/>
       </c>
       <c r="P3" s="26"/>
       <c r="Q3" s="25" t="str">
-        <f t="shared" ref="Q3:Q20" si="8">IF(P3&lt;&gt;"",CONCATENATE(K3,L3,M3,":",N3,O3),IF(P2&lt;&gt;"",$A$21,""))</f>
+        <f t="shared" ref="Q3:Q20" si="6">IF(P3&lt;&gt;"",CONCATENATE(K3,L3,M3,":",N3,O3),IF(P2&lt;&gt;"",$A$21,""))</f>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
+        <f>IF(F4&lt;&gt;"",$A$20,"")</f>
+        <v>&lt;li&gt;&lt;strong&gt;</v>
       </c>
       <c r="B4" s="24" t="str">
-        <f t="shared" ref="B3:B19" si="9">IF(F4&lt;&gt;"",LEFT(F4,FIND(":",F4,1)-1),"")</f>
-        <v>Cuando se usa una computadora compartida</v>
+        <f>IF(F4&lt;&gt;"",LEFT(F4,FIND(":",F4,1)-1),"")</f>
+        <v>Ejecutar el servidor con</v>
       </c>
       <c r="C4" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;/span&gt;</v>
+        <f>IF(F4&lt;&gt;"","&lt;/strong&gt;","")</f>
+        <v>&lt;/strong&gt;</v>
       </c>
       <c r="D4" s="24" t="str">
         <f>IF(F4&lt;&gt;"",RIGHT(F4,LEN(F4)-FIND(":",F4,1)),"")</f>
-        <v> Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.</v>
+        <v/>
       </c>
       <c r="E4" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G4" s="25" t="str">
         <f>IF(F4&lt;&gt;"",CONCATENATE(A4,B4,C4,":",D4,E4),IF(F3&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Cuando se usa una computadora compartida&lt;/span&gt;: Si varias personas utilizan la misma máquina, cada usuario debe asegurarse de establecer su propia identidad en Git.&lt;/li&gt;</v>
+        <v>&lt;li&gt;&lt;strong&gt;Ejecutar el servidor con&lt;/strong&gt;:&lt;/li&gt;</v>
       </c>
       <c r="K4" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L4" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M4" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L4" s="24" t="str">
+      <c r="N4" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M4" s="24" t="str">
+      <c r="O4" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N4" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O4" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P4" s="26"/>
       <c r="Q4" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;</v>
+        <f t="shared" ref="A3:A19" si="7">IF(F5&lt;&gt;"",$A$20,"")</f>
+        <v/>
       </c>
       <c r="B5" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v>Al alternar entre identidades</v>
+        <f t="shared" ref="B3:B19" si="8">IF(F5&lt;&gt;"",LEFT(F5,FIND(":",F5,1)-1),"")</f>
+        <v/>
       </c>
       <c r="C5" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;/span&gt;</v>
+        <f t="shared" ref="C3:C19" si="9">IF(F5&lt;&gt;"","&lt;/span&gt;","")</f>
+        <v/>
       </c>
       <c r="D5" s="24" t="str">
         <f t="shared" ref="D3:D19" si="10">IF(F5&lt;&gt;"",RIGHT(F5,LEN(F5)-FIND(":",F5,1)),"")</f>
-        <v> Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.</v>
+        <v/>
       </c>
       <c r="E5" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;/li&gt;</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>185</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F5" s="26"/>
       <c r="G5" s="25" t="str">
         <f t="shared" ref="G5:G20" si="11">IF(F5&lt;&gt;"",CONCATENATE(A5,B5,C5,":",D5,E5),IF(F4&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;&lt;span class="fw-bold"&gt;Al alternar entre identidades&lt;/span&gt;: Si se usa Git para proyectos personales y laborales, es útil cambiar el nombre y el correo según el contexto.&lt;/li&gt;</v>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K5" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L5" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L5" s="24" t="str">
+      <c r="N5" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M5" s="24" t="str">
+      <c r="O5" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N5" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O5" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P5" s="26"/>
       <c r="Q5" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B6" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C6" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C6" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D6" s="24" t="str">
@@ -28862,51 +28821,51 @@
         <v/>
       </c>
       <c r="E6" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>&lt;/ul&gt;</v>
+        <v/>
       </c>
       <c r="K6" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L6" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M6" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L6" s="24" t="str">
+      <c r="N6" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M6" s="24" t="str">
+      <c r="O6" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N6" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O6" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P6" s="26"/>
       <c r="Q6" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B7" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C7" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C7" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D7" s="24" t="str">
@@ -28914,7 +28873,7 @@
         <v/>
       </c>
       <c r="E7" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F7" s="26"/>
@@ -28923,42 +28882,42 @@
         <v/>
       </c>
       <c r="K7" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L7" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L7" s="24" t="str">
+      <c r="N7" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M7" s="24" t="str">
+      <c r="O7" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N7" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O7" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P7" s="26"/>
       <c r="Q7" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B8" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C8" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C8" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D8" s="24" t="str">
@@ -28966,7 +28925,7 @@
         <v/>
       </c>
       <c r="E8" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F8" s="26"/>
@@ -28975,42 +28934,42 @@
         <v/>
       </c>
       <c r="K8" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L8" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M8" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L8" s="24" t="str">
+      <c r="N8" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="24" t="str">
+      <c r="O8" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N8" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O8" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P8" s="26"/>
       <c r="Q8" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B9" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C9" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C9" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D9" s="24" t="str">
@@ -29018,7 +28977,7 @@
         <v/>
       </c>
       <c r="E9" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F9" s="26"/>
@@ -29027,42 +28986,42 @@
         <v/>
       </c>
       <c r="K9" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L9" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M9" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L9" s="24" t="str">
+      <c r="N9" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M9" s="24" t="str">
+      <c r="O9" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N9" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O9" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P9" s="26"/>
       <c r="Q9" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B10" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C10" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C10" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D10" s="24" t="str">
@@ -29070,7 +29029,7 @@
         <v/>
       </c>
       <c r="E10" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F10" s="26"/>
@@ -29079,42 +29038,42 @@
         <v/>
       </c>
       <c r="K10" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L10" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M10" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L10" s="24" t="str">
+      <c r="N10" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M10" s="24" t="str">
+      <c r="O10" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N10" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O10" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P10" s="26"/>
       <c r="Q10" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B11" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C11" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C11" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D11" s="24" t="str">
@@ -29122,7 +29081,7 @@
         <v/>
       </c>
       <c r="E11" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F11" s="26"/>
@@ -29131,42 +29090,42 @@
         <v/>
       </c>
       <c r="K11" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L11" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M11" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L11" s="24" t="str">
+      <c r="N11" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M11" s="24" t="str">
+      <c r="O11" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N11" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O11" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P11" s="26"/>
       <c r="Q11" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B12" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C12" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C12" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D12" s="24" t="str">
@@ -29174,7 +29133,7 @@
         <v/>
       </c>
       <c r="E12" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F12" s="26"/>
@@ -29183,42 +29142,42 @@
         <v/>
       </c>
       <c r="K12" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L12" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M12" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L12" s="24" t="str">
+      <c r="N12" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M12" s="24" t="str">
+      <c r="O12" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N12" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O12" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P12" s="26"/>
       <c r="Q12" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B13" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C13" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C13" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D13" s="24" t="str">
@@ -29226,7 +29185,7 @@
         <v/>
       </c>
       <c r="E13" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F13" s="26"/>
@@ -29235,42 +29194,42 @@
         <v/>
       </c>
       <c r="K13" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L13" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M13" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L13" s="24" t="str">
+      <c r="N13" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M13" s="24" t="str">
+      <c r="O13" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N13" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O13" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P13" s="26"/>
       <c r="Q13" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B14" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C14" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C14" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D14" s="24" t="str">
@@ -29278,7 +29237,7 @@
         <v/>
       </c>
       <c r="E14" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F14" s="26"/>
@@ -29287,42 +29246,42 @@
         <v/>
       </c>
       <c r="K14" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L14" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M14" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L14" s="24" t="str">
+      <c r="N14" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M14" s="24" t="str">
+      <c r="O14" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N14" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O14" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P14" s="26"/>
       <c r="Q14" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B15" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C15" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C15" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D15" s="24" t="str">
@@ -29330,7 +29289,7 @@
         <v/>
       </c>
       <c r="E15" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F15" s="26"/>
@@ -29339,42 +29298,42 @@
         <v/>
       </c>
       <c r="K15" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L15" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M15" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L15" s="24" t="str">
+      <c r="N15" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M15" s="24" t="str">
+      <c r="O15" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N15" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O15" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P15" s="26"/>
       <c r="Q15" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B16" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C16" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C16" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D16" s="24" t="str">
@@ -29382,7 +29341,7 @@
         <v/>
       </c>
       <c r="E16" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F16" s="26"/>
@@ -29391,42 +29350,42 @@
         <v/>
       </c>
       <c r="K16" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L16" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M16" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L16" s="24" t="str">
+      <c r="N16" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M16" s="24" t="str">
+      <c r="O16" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N16" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O16" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P16" s="26"/>
       <c r="Q16" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B17" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C17" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C17" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D17" s="24" t="str">
@@ -29434,7 +29393,7 @@
         <v/>
       </c>
       <c r="E17" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F17" s="26"/>
@@ -29443,42 +29402,42 @@
         <v/>
       </c>
       <c r="K17" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L17" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M17" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L17" s="24" t="str">
+      <c r="N17" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M17" s="24" t="str">
+      <c r="O17" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N17" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O17" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P17" s="26"/>
       <c r="Q17" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" spans="1:17">
       <c r="A18" s="24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="B18" s="24" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="C18" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C18" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D18" s="24" t="str">
@@ -29486,7 +29445,7 @@
         <v/>
       </c>
       <c r="E18" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F18" s="26"/>
@@ -29496,42 +29455,42 @@
       </c>
       <c r="I18" s="30"/>
       <c r="K18" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L18" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M18" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L18" s="24" t="str">
+      <c r="N18" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M18" s="24" t="str">
+      <c r="O18" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N18" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O18" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P18" s="26"/>
       <c r="Q18" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="24" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="B19" s="24" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="19" ht="15" spans="1:17">
-      <c r="A19" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B19" s="24" t="str">
+      <c r="C19" s="24" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="C19" s="24" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D19" s="24" t="str">
@@ -29539,7 +29498,7 @@
         <v/>
       </c>
       <c r="E19" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F19" s="26"/>
@@ -29549,34 +29508,34 @@
       </c>
       <c r="I19"/>
       <c r="K19" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L19" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M19" s="24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L19" s="24" t="str">
+      <c r="N19" s="24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M19" s="24" t="str">
+      <c r="O19" s="24" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N19" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O19" s="24" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P19" s="27"/>
       <c r="Q19" s="25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="24" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>2</v>
@@ -29587,14 +29546,14 @@
         <v/>
       </c>
       <c r="K20" s="24" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>2</v>
       </c>
       <c r="P20" s="26"/>
     </row>
-    <row r="21" ht="15" spans="1:16">
+    <row r="21" spans="1:16">
       <c r="A21" s="24" t="s">
         <v>136</v>
       </c>
@@ -29617,19 +29576,19 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="24" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:17">
       <c r="A25" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G25" s="25" t="str">
         <f>A25</f>
         <v>&lt;ul&gt;</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="Q25" s="25" t="str">
         <f>K25</f>
@@ -29643,18 +29602,18 @@
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" ref="B26:B43" si="13">IF(F26&lt;&gt;"",CONCATENATE(A26,F26,C26),"")</f>
-        <v>&lt;li&gt; Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.&lt;/li&gt;</v>
+        <v>&lt;li&gt;Hacer doble clic sobre el archivo instalador.&lt;/li&gt;</v>
       </c>
       <c r="C26" s="24" t="str">
         <f t="shared" ref="C26:C43" si="14">IF(F26&lt;&gt;"","&lt;/li&gt;","")</f>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G26" s="25" t="str">
         <f>IF(F26&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F25&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt; Cuando se desea comenzar de nuevo con un proyecto desde un estado limpio.</v>
+        <v>&lt;li&gt;Hacer doble clic sobre el archivo instalador.</v>
       </c>
       <c r="K26" s="24" t="str">
         <f t="shared" ref="K26:K42" si="15">IF(P26&lt;&gt;"",$A$20,"")</f>
@@ -29689,18 +29648,18 @@
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;Si se han realizado cambios que no se quieren conservar.&lt;/li&gt;</v>
+        <v>&lt;li&gt;Seguir las instrucciones del asistente de instalación, que generalmente consiste en hacer clic en "Siguiente" varias veces.&lt;/li&gt;</v>
       </c>
       <c r="C27" s="24" t="str">
         <f t="shared" si="14"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G27" s="25" t="str">
         <f t="shared" ref="G26:G44" si="21">IF(F27&lt;&gt;"",CONCATENATE(A27,F27,E27),IF(F26&lt;&gt;"",$A$21,""))</f>
-        <v>&lt;li&gt;Si se han realizado cambios que no se quieren conservar.</v>
+        <v>&lt;li&gt;Seguir las instrucciones del asistente de instalación, que generalmente consiste en hacer clic en "Siguiente" varias veces.</v>
       </c>
       <c r="K27" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29735,18 +29694,18 @@
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.&lt;/li&gt;</v>
+        <v>&lt;li&gt;Finalmente, hacer clic en "Instalar" y esperar a que el proceso finalice.&lt;/li&gt;</v>
       </c>
       <c r="C28" s="24" t="str">
         <f t="shared" si="14"/>
         <v>&lt;/li&gt;</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G28" s="25" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;li&gt;Para eliminar el historial de commits y reiniciar el repositorio con un nuevo historial.</v>
+        <v>&lt;li&gt;Finalmente, hacer clic en "Instalar" y esperar a que el proceso finalice.</v>
       </c>
       <c r="K28" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29777,22 +29736,20 @@
     <row r="29" spans="1:17">
       <c r="A29" s="24" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;li&gt;</v>
+        <v/>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;li&gt;En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.&lt;/li&gt;</v>
+        <v/>
       </c>
       <c r="C29" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>&lt;/li&gt;</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>191</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F29" s="26"/>
       <c r="G29" s="25" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;li&gt;En caso de querer restablecer una rama a un estado anterior sin conservar modificaciones recientes.</v>
+        <v>&lt;/ul&gt;</v>
       </c>
       <c r="K29" s="24" t="str">
         <f t="shared" si="15"/>
@@ -29836,7 +29793,7 @@
       <c r="F30" s="26"/>
       <c r="G30" s="25" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;/ul&gt;</v>
+        <v/>
       </c>
       <c r="K30" s="24" t="str">
         <f t="shared" si="15"/>
@@ -30369,7 +30326,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" spans="1:17">
+    <row r="42" spans="1:17">
       <c r="A42" s="24" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -30437,14 +30394,14 @@
         <v/>
       </c>
       <c r="K43" s="24" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L43" s="24" t="s">
         <v>2</v>
       </c>
       <c r="P43" s="26"/>
     </row>
-    <row r="44" ht="15" spans="6:16">
+    <row r="44" spans="6:16">
       <c r="F44" s="27"/>
       <c r="G44" s="25" t="str">
         <f t="shared" si="21"/>
@@ -30463,10 +30420,10 @@
     </row>
     <row r="48" ht="15" spans="1:7">
       <c r="A48" s="24" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G48" s="25" t="str">
         <f>IF(F48&lt;&gt;"",CONCATENATE(A26,F26,E26),IF(F47&lt;&gt;"",$A$21,""))</f>
@@ -30475,20 +30432,20 @@
     </row>
     <row r="49" spans="6:7">
       <c r="F49" s="29" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G49" s="25" t="str">
         <f t="shared" ref="G49:G60" si="23">IF(F49&lt;&gt;"",CONCATENATE($A$48,F49,$B$48),"")</f>
-        <v>&lt;p&gt;Los comandos de configuración inicial de Git permiten establecer parámetros globales que definen cómo Git interactúa con el usuario y cómo se registran los cambios en los repositorios. Estos comandos suelen configurarse al instalar Git por primera vez y son esenciales para garantizar un correcto funcionamiento del sistema de control de versiones.&lt;/p&gt;</v>
+        <v>&lt;p&gt;Para instalar cualquiera de estos navegadores, primero es necesario descargar el archivo instalador desde el sitio web oficial del navegador elegido. Este archivo suele tener una extensión .exe en Windows y .dmg en macOS.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="50" spans="6:7">
       <c r="F50" s="26" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G50" s="25" t="str">
         <f t="shared" si="23"/>
-        <v>&lt;p&gt;A continuación, se explican los comandos de configuración inicial más importantes, cuándo deben utilizarse y cómo aplicarlos correctamente.&lt;/p&gt;</v>
+        <v>&lt;p&gt;Una vez descargado el archivo, el proceso de instalación es sencillo:&lt;/p&gt;</v>
       </c>
     </row>
     <row r="51" spans="6:7">
@@ -30579,7 +30536,7 @@
     <row r="66" spans="6:6">
       <c r="F66" s="26"/>
     </row>
-    <row r="67" ht="15" spans="6:6">
+    <row r="67" spans="6:6">
       <c r="F67" s="27"/>
     </row>
   </sheetData>
@@ -30647,7 +30604,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="23" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -30674,27 +30631,27 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -30709,7 +30666,7 @@
         <v>https://eduardoherreraf.github.io/</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -30731,7 +30688,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" s="16"/>
@@ -30751,21 +30708,21 @@
     </row>
     <row r="9" ht="15.75" spans="1:3">
       <c r="A9" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20"/>
     </row>
     <row r="10" ht="16.5" spans="1:3">
       <c r="A10" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -30780,7 +30737,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap.html</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -30802,7 +30759,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C14" s="17"/>
       <c r="E14" s="16"/>
@@ -30817,19 +30774,19 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
       <c r="A16" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -30844,7 +30801,7 @@
         <v>https://eduardoherreraf.github.io/git.html</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E18" s="16"/>
     </row>
@@ -30866,7 +30823,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C20" s="17"/>
       <c r="E20" s="16"/>
@@ -30881,19 +30838,19 @@
         <v>0.7</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
       <c r="A22" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="20"/>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -30908,7 +30865,7 @@
         <v>https://eduardoherreraf.github.io/javascript.html</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E24" s="16"/>
     </row>
@@ -30930,7 +30887,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C26" s="17"/>
       <c r="E26" s="16"/>
@@ -30945,19 +30902,19 @@
         <v>0.7</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
       <c r="A28" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
     </row>
     <row r="29" ht="16.5" spans="1:3">
       <c r="A29" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -30972,7 +30929,7 @@
         <v>https://eduardoherreraf.github.io/photoshop.html</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E30" s="16"/>
     </row>
@@ -30994,7 +30951,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C32" s="17"/>
       <c r="E32" s="16"/>
@@ -31009,19 +30966,19 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
       <c r="A34" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
     </row>
     <row r="35" ht="16.5" spans="1:3">
       <c r="A35" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -31036,7 +30993,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas.html</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E36" s="16"/>
     </row>
@@ -31058,7 +31015,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C38" s="17"/>
       <c r="E38" s="16"/>
@@ -31073,19 +31030,19 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
       <c r="A40" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20"/>
     </row>
     <row r="41" ht="16.5" spans="1:3">
       <c r="A41" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -31100,7 +31057,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3.html</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E42" s="16"/>
     </row>
@@ -31122,7 +31079,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C44" s="17"/>
       <c r="E44" s="16"/>
@@ -31137,19 +31094,19 @@
         <v>0.7</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
       <c r="A46" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="20"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
       <c r="A47" s="21" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31157,7 +31114,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:3">
       <c r="A48" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -31172,7 +31129,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_parcel.html</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E49" s="16"/>
     </row>
@@ -31194,7 +31151,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C51" s="17"/>
       <c r="E51" s="16"/>
@@ -31209,19 +31166,19 @@
         <v>0.6</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
       <c r="A53" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
     </row>
     <row r="54" ht="16.5" spans="1:3">
       <c r="A54" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="12"/>
@@ -31236,7 +31193,7 @@
         <v>https://eduardoherreraf.github.io/bootstrap-instalacion_de_bootstrap_v5_con_npm_y_vite.html</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E55" s="16"/>
     </row>
@@ -31258,7 +31215,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C57" s="17"/>
       <c r="E57" s="16"/>
@@ -31273,19 +31230,19 @@
         <v>0.6</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
       <c r="A59" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20"/>
     </row>
     <row r="60" ht="16.5" spans="1:5">
       <c r="A60" s="21" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -31293,7 +31250,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:3">
       <c r="A61" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="12"/>
@@ -31308,7 +31265,7 @@
         <v>https://eduardoherreraf.github.io/git-01_como_eliminar_el_ultimo_commit_de_git.html</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E62" s="16"/>
     </row>
@@ -31330,7 +31287,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C64" s="17"/>
       <c r="E64" s="16"/>
@@ -31345,19 +31302,19 @@
         <v>0.6</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
       <c r="A66" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="20"/>
     </row>
     <row r="67" ht="16.5" spans="1:3">
       <c r="A67" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="12"/>
@@ -31372,7 +31329,7 @@
         <v>https://eduardoherreraf.github.io/git-02_comandos_basicos_de_consola-terminal_cli_para_windows.html</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E68" s="16"/>
     </row>
@@ -31394,7 +31351,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C70" s="17"/>
       <c r="E70" s="16"/>
@@ -31409,19 +31366,19 @@
         <v>0.6</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
       <c r="A72" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="20"/>
     </row>
     <row r="73" ht="16.5" spans="1:3">
       <c r="A73" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
@@ -31436,7 +31393,7 @@
         <v>https://eduardoherreraf.github.io/git-03_introduccion_de_git_para_windows.html</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E74" s="16"/>
     </row>
@@ -31458,7 +31415,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C76" s="17"/>
       <c r="E76" s="16"/>
@@ -31473,19 +31430,19 @@
         <v>0.6</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
       <c r="A78" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
     </row>
     <row r="79" ht="16.5" spans="1:3">
       <c r="A79" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="12"/>
@@ -31500,7 +31457,7 @@
         <v>https://eduardoherreraf.github.io/git-04_configuracion_inicial_git.html</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E80" s="16"/>
     </row>
@@ -31522,7 +31479,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C82" s="17"/>
       <c r="E82" s="16"/>
@@ -31537,19 +31494,19 @@
         <v>0.6</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
       <c r="A84" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="20"/>
     </row>
     <row r="85" ht="16.5" spans="1:3">
       <c r="A85" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
@@ -31585,7 +31542,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C88" s="17"/>
       <c r="E88" s="16"/>
@@ -31600,27 +31557,27 @@
         <v>0.6</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E89" s="16"/>
     </row>
     <row r="90" ht="15.75" spans="1:3">
       <c r="A90" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="20"/>
     </row>
     <row r="91" ht="16.5" spans="1:3">
       <c r="A91" s="21" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B91" s="21"/>
       <c r="C91" s="21"/>
     </row>
     <row r="92" ht="16.5" spans="1:3">
       <c r="A92" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
@@ -31635,7 +31592,7 @@
         <v>https://eduardoherreraf.github.io/javascript-como_ejecutar_un_codigo_javascript.html</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E93" s="16"/>
     </row>
@@ -31657,7 +31614,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C95" s="17"/>
       <c r="E95" s="16"/>
@@ -31672,19 +31629,19 @@
         <v>0.6</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
       <c r="A97" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="20"/>
     </row>
     <row r="98" ht="16.5" spans="1:3">
       <c r="A98" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
@@ -31699,7 +31656,7 @@
         <v>https://eduardoherreraf.github.io/javascript-configurar_el_entorno_de_trabajo_javascript.html</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -31720,7 +31677,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C101" s="17"/>
       <c r="E101" s="16"/>
@@ -31735,27 +31692,27 @@
         <v>0.6</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E102" s="16"/>
     </row>
     <row r="103" ht="15.75" spans="1:3">
       <c r="A103" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="20"/>
     </row>
     <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="21" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="21"/>
     </row>
     <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="12"/>
@@ -31770,7 +31727,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-16_metadatos_y_exportacion.html</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E106" s="16"/>
     </row>
@@ -31792,7 +31749,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C108" s="17"/>
       <c r="E108" s="16"/>
@@ -31807,19 +31764,19 @@
         <v>0.6</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" ht="15.75" spans="1:3">
       <c r="A110" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="20"/>
     </row>
     <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="12"/>
@@ -31834,7 +31791,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-15_filtros_licuar.html</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E112" s="16"/>
     </row>
@@ -31856,7 +31813,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C114" s="17"/>
       <c r="E114" s="16"/>
@@ -31871,19 +31828,19 @@
         <v>0.6</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" ht="15.75" spans="1:3">
       <c r="A116" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B116" s="19"/>
       <c r="C116" s="20"/>
     </row>
     <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="12"/>
@@ -31898,7 +31855,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-14_filtros_neurales.html</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E118" s="16"/>
     </row>
@@ -31920,7 +31877,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C120" s="17"/>
       <c r="E120" s="16"/>
@@ -31935,19 +31892,19 @@
         <v>0.6</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122" ht="15.75" spans="1:3">
       <c r="A122" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="20"/>
     </row>
     <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="12"/>
@@ -31962,7 +31919,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-13_filtros.html</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E124" s="16"/>
     </row>
@@ -31984,7 +31941,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C126" s="17"/>
       <c r="E126" s="16"/>
@@ -31999,19 +31956,19 @@
         <v>0.6</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="128" ht="15.75" spans="1:3">
       <c r="A128" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B128" s="19"/>
       <c r="C128" s="20"/>
     </row>
     <row r="129" ht="16.5" spans="1:3">
       <c r="A129" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="12"/>
@@ -32026,7 +31983,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-12_formas_y_capas.html</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E130" s="16"/>
     </row>
@@ -32048,7 +32005,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C132" s="17"/>
       <c r="E132" s="16"/>
@@ -32063,19 +32020,19 @@
         <v>0.6</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:3">
       <c r="A134" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="20"/>
     </row>
     <row r="135" ht="16.5" spans="1:3">
       <c r="A135" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="12"/>
@@ -32090,7 +32047,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-11_textos.html</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E136" s="16"/>
     </row>
@@ -32112,7 +32069,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C138" s="17"/>
       <c r="E138" s="16"/>
@@ -32127,19 +32084,19 @@
         <v>0.6</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:3">
       <c r="A140" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="20"/>
     </row>
     <row r="141" ht="16.5" spans="1:3">
       <c r="A141" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="12"/>
@@ -32154,7 +32111,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-10_color_y_degradados.html</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E142" s="16"/>
     </row>
@@ -32176,7 +32133,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C144" s="17"/>
       <c r="E144" s="16"/>
@@ -32191,19 +32148,19 @@
         <v>0.6</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:3">
       <c r="A146" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B146" s="19"/>
       <c r="C146" s="20"/>
     </row>
     <row r="147" ht="16.5" spans="1:3">
       <c r="A147" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="12"/>
@@ -32218,7 +32175,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-09_uso_de_pinceles.html</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E148" s="16"/>
     </row>
@@ -32240,7 +32197,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C150" s="17"/>
       <c r="E150" s="16"/>
@@ -32255,19 +32212,19 @@
         <v>0.6</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="152" ht="15.75" spans="1:3">
       <c r="A152" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="20"/>
     </row>
     <row r="153" ht="16.5" spans="1:3">
       <c r="A153" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="12"/>
@@ -32282,7 +32239,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-08_agregar_y_quitar_objetos.html</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E154" s="16"/>
     </row>
@@ -32304,7 +32261,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C156" s="17"/>
       <c r="E156" s="16"/>
@@ -32319,19 +32276,19 @@
         <v>0.6</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" ht="15.75" spans="1:3">
       <c r="A158" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B158" s="19"/>
       <c r="C158" s="20"/>
     </row>
     <row r="159" ht="16.5" spans="1:3">
       <c r="A159" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="12"/>
@@ -32346,7 +32303,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-07_herramientas_de_seleccion.html</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E160" s="16"/>
     </row>
@@ -32368,7 +32325,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C162" s="17"/>
       <c r="E162" s="16"/>
@@ -32383,19 +32340,19 @@
         <v>0.6</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" ht="15.75" spans="1:3">
       <c r="A164" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="20"/>
     </row>
     <row r="165" ht="16.5" spans="1:3">
       <c r="A165" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="12"/>
@@ -32410,7 +32367,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-06_ajuste_tono_brillo_y_saturacion.html</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E166" s="16"/>
     </row>
@@ -32432,7 +32389,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C168" s="17"/>
       <c r="E168" s="16"/>
@@ -32447,19 +32404,19 @@
         <v>0.6</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="170" ht="15.75" spans="1:3">
       <c r="A170" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B170" s="19"/>
       <c r="C170" s="20"/>
     </row>
     <row r="171" ht="16.5" spans="1:3">
       <c r="A171" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="12"/>
@@ -32474,7 +32431,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-05_trabajo_con_capas.html</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E172" s="16"/>
     </row>
@@ -32496,7 +32453,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C174" s="17"/>
       <c r="E174" s="16"/>
@@ -32511,19 +32468,19 @@
         <v>0.6</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="176" ht="15.75" spans="1:3">
       <c r="A176" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B176" s="19"/>
       <c r="C176" s="20"/>
     </row>
     <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="12"/>
@@ -32538,7 +32495,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-04_ajuste_lienzo_resolucion.html</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E178" s="16"/>
     </row>
@@ -32560,7 +32517,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C180" s="17"/>
       <c r="E180" s="16"/>
@@ -32575,19 +32532,19 @@
         <v>0.6</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="182" ht="15.75" spans="1:3">
       <c r="A182" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="20"/>
     </row>
     <row r="183" ht="16.5" spans="1:3">
       <c r="A183" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="12"/>
@@ -32602,7 +32559,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-03_compartir_y_editar_archivos.html</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E184" s="16"/>
     </row>
@@ -32624,7 +32581,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C186" s="17"/>
       <c r="E186" s="16"/>
@@ -32639,19 +32596,19 @@
         <v>0.6</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="188" ht="15.75" spans="1:3">
       <c r="A188" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B188" s="19"/>
       <c r="C188" s="20"/>
     </row>
     <row r="189" ht="16.5" spans="1:3">
       <c r="A189" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="12"/>
@@ -32666,7 +32623,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-02_interfaz_y_area_de_trabajo.html</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E190" s="16"/>
     </row>
@@ -32688,7 +32645,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C192" s="17"/>
       <c r="E192" s="16"/>
@@ -32703,19 +32660,19 @@
         <v>0.6</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="194" ht="15.75" spans="1:3">
       <c r="A194" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B194" s="19"/>
       <c r="C194" s="20"/>
     </row>
     <row r="195" ht="16.5" spans="1:3">
       <c r="A195" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="12"/>
@@ -32730,7 +32687,7 @@
         <v>https://eduardoherreraf.github.io/photoshop-01_comenzando_un_proyecto.html</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -32751,7 +32708,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C198" s="17"/>
       <c r="E198" s="16"/>
@@ -32766,27 +32723,27 @@
         <v>0.6</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E199" s="16"/>
     </row>
     <row r="200" ht="15.75" spans="1:3">
       <c r="A200" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B200" s="19"/>
       <c r="C200" s="20"/>
     </row>
     <row r="201" ht="16.5" spans="1:3">
       <c r="A201" s="21" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B201" s="21"/>
       <c r="C201" s="21"/>
     </row>
     <row r="202" ht="16.5" spans="1:3">
       <c r="A202" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="12"/>
@@ -32801,7 +32758,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_aprender_cualquier_habilidad_facilmente_con_chatgpt.html</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E203" s="16"/>
     </row>
@@ -32823,7 +32780,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B205" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C205" s="17"/>
       <c r="E205" s="16"/>
@@ -32838,19 +32795,19 @@
         <v>0.6</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="207" ht="15.75" spans="1:3">
       <c r="A207" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B207" s="19"/>
       <c r="C207" s="20"/>
     </row>
     <row r="208" ht="16.5" spans="1:3">
       <c r="A208" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="12"/>
@@ -32865,7 +32822,7 @@
         <v>https://eduardoherreraf.github.io/otrosTemas-como_borrar_la_cache_y_archivos_basura_en_windows.html</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -32886,7 +32843,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C211" s="17"/>
       <c r="E211" s="16"/>
@@ -32901,27 +32858,27 @@
         <v>0.6</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E212" s="16"/>
     </row>
     <row r="213" ht="15.75" spans="1:3">
       <c r="A213" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B213" s="19"/>
       <c r="C213" s="20"/>
     </row>
     <row r="214" ht="16.5" spans="1:3">
       <c r="A214" s="21" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B214" s="21"/>
       <c r="C214" s="21"/>
     </row>
     <row r="215" ht="16.5" spans="1:3">
       <c r="A215" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="12"/>
@@ -32936,7 +32893,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0101_introduccion.html</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E216" s="16"/>
     </row>
@@ -32958,7 +32915,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C218" s="17"/>
       <c r="E218" s="16"/>
@@ -32973,19 +32930,19 @@
         <v>0.6</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="220" ht="15.75" spans="1:3">
       <c r="A220" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B220" s="19"/>
       <c r="C220" s="20"/>
     </row>
     <row r="221" ht="16.5" spans="1:3">
       <c r="A221" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="12"/>
@@ -33000,7 +32957,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0102_instalacion_de_python_localmente.html</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E222" s="16"/>
     </row>
@@ -33022,7 +32979,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C224" s="17"/>
       <c r="E224" s="16"/>
@@ -33037,19 +32994,19 @@
         <v>0.6</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="226" ht="15.75" spans="1:3">
       <c r="A226" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B226" s="19"/>
       <c r="C226" s="20"/>
     </row>
     <row r="227" ht="16.5" spans="1:3">
       <c r="A227" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="12"/>
@@ -33064,7 +33021,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0201_funcion_print.html</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E228" s="16"/>
     </row>
@@ -33086,7 +33043,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C230" s="17"/>
       <c r="E230" s="16"/>
@@ -33101,19 +33058,19 @@
         <v>0.6</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="232" ht="15.75" spans="1:3">
       <c r="A232" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B232" s="19"/>
       <c r="C232" s="20"/>
     </row>
     <row r="233" ht="16.5" spans="1:3">
       <c r="A233" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B233" s="11"/>
       <c r="C233" s="12"/>
@@ -33128,7 +33085,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0202_literales.html</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E234" s="16"/>
     </row>
@@ -33150,7 +33107,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C236" s="17"/>
       <c r="E236" s="16"/>
@@ -33165,19 +33122,19 @@
         <v>0.6</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="238" ht="15.75" spans="1:3">
       <c r="A238" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="20"/>
     </row>
     <row r="239" ht="16.5" spans="1:3">
       <c r="A239" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B239" s="11"/>
       <c r="C239" s="12"/>
@@ -33192,7 +33149,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0203_operadores.html</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E240" s="16"/>
     </row>
@@ -33214,7 +33171,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C242" s="17"/>
       <c r="E242" s="16"/>
@@ -33229,19 +33186,19 @@
         <v>0.6</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" ht="15.75" spans="1:3">
       <c r="A244" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B244" s="19"/>
       <c r="C244" s="20"/>
     </row>
     <row r="245" ht="16.5" spans="1:3">
       <c r="A245" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B245" s="11"/>
       <c r="C245" s="12"/>
@@ -33256,7 +33213,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0204_variables.html</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E246" s="16"/>
     </row>
@@ -33278,7 +33235,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C248" s="17"/>
       <c r="E248" s="16"/>
@@ -33293,19 +33250,19 @@
         <v>0.6</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="250" ht="15.75" spans="1:3">
       <c r="A250" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B250" s="19"/>
       <c r="C250" s="20"/>
     </row>
     <row r="251" ht="16.5" spans="1:3">
       <c r="A251" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B251" s="11"/>
       <c r="C251" s="12"/>
@@ -33320,7 +33277,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0205_comentarios.html</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E252" s="16"/>
     </row>
@@ -33342,7 +33299,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C254" s="17"/>
       <c r="E254" s="16"/>
@@ -33357,19 +33314,19 @@
         <v>0.6</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="256" ht="15.75" spans="1:3">
       <c r="A256" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B256" s="19"/>
       <c r="C256" s="20"/>
     </row>
     <row r="257" ht="16.5" spans="1:3">
       <c r="A257" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="12"/>
@@ -33384,7 +33341,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0206_interaccion_con_el_usuario.html</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E258" s="16"/>
     </row>
@@ -33406,7 +33363,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C260" s="17"/>
       <c r="E260" s="16"/>
@@ -33421,19 +33378,19 @@
         <v>0.6</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="262" ht="15.75" spans="1:3">
       <c r="A262" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B262" s="19"/>
       <c r="C262" s="20"/>
     </row>
     <row r="263" ht="16.5" spans="1:3">
       <c r="A263" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="12"/>
@@ -33448,7 +33405,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0301_operadores_de_comparacion_y_logicos_en_python.html</v>
       </c>
       <c r="C264" s="15" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E264" s="16"/>
     </row>
@@ -33470,7 +33427,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B266" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C266" s="17"/>
       <c r="E266" s="16"/>
@@ -33485,19 +33442,19 @@
         <v>0.6</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="268" ht="15.75" spans="1:3">
       <c r="A268" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B268" s="19"/>
       <c r="C268" s="20"/>
     </row>
     <row r="269" ht="16.5" spans="1:3">
       <c r="A269" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B269" s="11"/>
       <c r="C269" s="12"/>
@@ -33512,7 +33469,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0302_sentencia_if_de_control_de_flujo.html</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E270" s="16"/>
     </row>
@@ -33534,7 +33491,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B272" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C272" s="17"/>
       <c r="E272" s="16"/>
@@ -33549,19 +33506,19 @@
         <v>0.6</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="274" ht="15.75" spans="1:3">
       <c r="A274" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B274" s="19"/>
       <c r="C274" s="20"/>
     </row>
     <row r="275" ht="16.5" spans="1:3">
       <c r="A275" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B275" s="11"/>
       <c r="C275" s="12"/>
@@ -33576,7 +33533,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0303_bucles_en_python_una_guia_completa.html</v>
       </c>
       <c r="C276" s="15" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E276" s="16"/>
     </row>
@@ -33598,7 +33555,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C278" s="17"/>
       <c r="E278" s="16"/>
@@ -33613,19 +33570,19 @@
         <v>0.6</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="280" ht="15.75" spans="1:3">
       <c r="A280" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B280" s="19"/>
       <c r="C280" s="20"/>
     </row>
     <row r="281" ht="16.5" spans="1:3">
       <c r="A281" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B281" s="11"/>
       <c r="C281" s="12"/>
@@ -33640,7 +33597,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0304_operadores_logicos_y_operaciones_bit_a_bit_en_python.html</v>
       </c>
       <c r="C282" s="15" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E282" s="16"/>
     </row>
@@ -33662,7 +33619,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C284" s="17"/>
       <c r="E284" s="16"/>
@@ -33677,19 +33634,19 @@
         <v>0.6</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="286" ht="15.75" spans="1:3">
       <c r="A286" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B286" s="19"/>
       <c r="C286" s="20"/>
     </row>
     <row r="287" ht="16.5" spans="1:3">
       <c r="A287" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B287" s="11"/>
       <c r="C287" s="12"/>
@@ -33704,7 +33661,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0305_listas.html</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E288" s="16"/>
     </row>
@@ -33726,7 +33683,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B290" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C290" s="17"/>
       <c r="E290" s="16"/>
@@ -33741,19 +33698,19 @@
         <v>0.6</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="292" ht="15.75" spans="1:3">
       <c r="A292" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B292" s="19"/>
       <c r="C292" s="20"/>
     </row>
     <row r="293" ht="16.5" spans="1:3">
       <c r="A293" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B293" s="11"/>
       <c r="C293" s="12"/>
@@ -33768,7 +33725,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0306_ordenamiento_de_listas_metodo_burbuja.html</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E294" s="16"/>
     </row>
@@ -33790,7 +33747,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C296" s="17"/>
       <c r="E296" s="16"/>
@@ -33805,19 +33762,19 @@
         <v>0.6</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="298" ht="15.75" spans="1:3">
       <c r="A298" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B298" s="19"/>
       <c r="C298" s="20"/>
     </row>
     <row r="299" ht="16.5" spans="1:3">
       <c r="A299" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B299" s="11"/>
       <c r="C299" s="12"/>
@@ -33832,7 +33789,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0307_operaciones_con_listas.html</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E300" s="16"/>
     </row>
@@ -33854,7 +33811,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C302" s="17"/>
       <c r="E302" s="16"/>
@@ -33869,19 +33826,19 @@
         <v>0.6</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="304" ht="15.75" spans="1:3">
       <c r="A304" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B304" s="19"/>
       <c r="C304" s="20"/>
     </row>
     <row r="305" ht="16.5" spans="1:3">
       <c r="A305" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B305" s="11"/>
       <c r="C305" s="12"/>
@@ -33896,7 +33853,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0401_introduccion_funciones.html</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E306" s="16"/>
     </row>
@@ -33918,7 +33875,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C308" s="17"/>
       <c r="E308" s="16"/>
@@ -33933,19 +33890,19 @@
         <v>0.6</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="310" ht="15.75" spans="1:3">
       <c r="A310" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B310" s="19"/>
       <c r="C310" s="20"/>
     </row>
     <row r="311" ht="16.5" spans="1:3">
       <c r="A311" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B311" s="11"/>
       <c r="C311" s="12"/>
@@ -33960,7 +33917,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0402_como_las_funciones_se_comunican_con_su_entorno.html</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E312" s="16"/>
     </row>
@@ -33982,7 +33939,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B314" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C314" s="17"/>
       <c r="E314" s="16"/>
@@ -33997,19 +33954,19 @@
         <v>0.6</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="316" ht="15.75" spans="1:3">
       <c r="A316" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B316" s="19"/>
       <c r="C316" s="20"/>
     </row>
     <row r="317" ht="16.5" spans="1:3">
       <c r="A317" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B317" s="11"/>
       <c r="C317" s="12"/>
@@ -34024,7 +33981,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0403_retorno_de_valores_en_funciones.html</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E318" s="16"/>
     </row>
@@ -34046,7 +34003,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B320" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C320" s="17"/>
       <c r="E320" s="16"/>
@@ -34061,19 +34018,19 @@
         <v>0.6</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="322" ht="15.75" spans="1:3">
       <c r="A322" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B322" s="19"/>
       <c r="C322" s="20"/>
     </row>
     <row r="323" ht="16.5" spans="1:3">
       <c r="A323" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B323" s="11"/>
       <c r="C323" s="12"/>
@@ -34088,7 +34045,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0404_el_alcance_de_las_variables.html</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E324" s="16"/>
     </row>
@@ -34110,7 +34067,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B326" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C326" s="17"/>
       <c r="E326" s="16"/>
@@ -34125,19 +34082,19 @@
         <v>0.6</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="328" ht="15.75" spans="1:3">
       <c r="A328" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B328" s="19"/>
       <c r="C328" s="20"/>
     </row>
     <row r="329" ht="16.5" spans="1:3">
       <c r="A329" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="12"/>
@@ -34152,7 +34109,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0405_tuplas_y_diccionarios.html</v>
       </c>
       <c r="C330" s="15" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E330" s="16"/>
     </row>
@@ -34174,7 +34131,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B332" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C332" s="17"/>
       <c r="E332" s="16"/>
@@ -34189,19 +34146,19 @@
         <v>0.6</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="334" ht="15.75" spans="1:3">
       <c r="A334" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B334" s="19"/>
       <c r="C334" s="20"/>
     </row>
     <row r="335" ht="16.5" spans="1:3">
       <c r="A335" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B335" s="11"/>
       <c r="C335" s="12"/>
@@ -34216,7 +34173,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0501_introduccion_a_los_modulos.html</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E336" s="16"/>
     </row>
@@ -34238,7 +34195,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B338" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C338" s="17"/>
       <c r="E338" s="16"/>
@@ -34253,19 +34210,19 @@
         <v>0.6</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="340" ht="15.75" spans="1:3">
       <c r="A340" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B340" s="19"/>
       <c r="C340" s="20"/>
     </row>
     <row r="341" ht="16.5" spans="1:3">
       <c r="A341" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B341" s="11"/>
       <c r="C341" s="12"/>
@@ -34280,7 +34237,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0502_importacion_de_modulos.html</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E342" s="16"/>
     </row>
@@ -34302,7 +34259,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B344" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C344" s="17"/>
       <c r="E344" s="16"/>
@@ -34317,19 +34274,19 @@
         <v>0.6</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="346" ht="15.75" spans="1:3">
       <c r="A346" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B346" s="19"/>
       <c r="C346" s="20"/>
     </row>
     <row r="347" ht="16.5" spans="1:3">
       <c r="A347" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B347" s="11"/>
       <c r="C347" s="12"/>
@@ -34344,7 +34301,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0503_modulos_especializados_de_python-matematico_aleatorio_y_de_sistema.html</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E348" s="16"/>
     </row>
@@ -34366,7 +34323,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B350" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C350" s="17"/>
       <c r="E350" s="16"/>
@@ -34381,19 +34338,19 @@
         <v>0.6</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="352" ht="15.75" spans="1:3">
       <c r="A352" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B352" s="19"/>
       <c r="C352" s="20"/>
     </row>
     <row r="353" ht="16.5" spans="1:3">
       <c r="A353" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B353" s="11"/>
       <c r="C353" s="12"/>
@@ -34408,7 +34365,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0504_modulos_y_paquetes.html</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E354" s="16"/>
     </row>
@@ -34430,7 +34387,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B356" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C356" s="17"/>
       <c r="E356" s="16"/>
@@ -34445,19 +34402,19 @@
         <v>0.6</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="358" ht="15.75" spans="1:3">
       <c r="A358" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B358" s="19"/>
       <c r="C358" s="20"/>
     </row>
     <row r="359" ht="16.5" spans="1:3">
       <c r="A359" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B359" s="11"/>
       <c r="C359" s="12"/>
@@ -34472,7 +34429,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0505_instalador_de_paquetes_PIP.html</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E360" s="16"/>
     </row>
@@ -34494,7 +34451,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B362" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C362" s="17"/>
       <c r="E362" s="16"/>
@@ -34509,19 +34466,19 @@
         <v>0.6</v>
       </c>
       <c r="C363" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="364" ht="15.75" spans="1:3">
       <c r="A364" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B364" s="19"/>
       <c r="C364" s="20"/>
     </row>
     <row r="365" ht="16.5" spans="1:3">
       <c r="A365" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B365" s="11"/>
       <c r="C365" s="12"/>
@@ -34536,7 +34493,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0601_la_naturaleza_de_las_cadenas.html</v>
       </c>
       <c r="C366" s="15" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E366" s="16"/>
     </row>
@@ -34558,7 +34515,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B368" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C368" s="17"/>
       <c r="E368" s="16"/>
@@ -34573,19 +34530,19 @@
         <v>0.6</v>
       </c>
       <c r="C369" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="370" ht="15.75" spans="1:3">
       <c r="A370" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B370" s="19"/>
       <c r="C370" s="20"/>
     </row>
     <row r="371" ht="16.5" spans="1:3">
       <c r="A371" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B371" s="11"/>
       <c r="C371" s="12"/>
@@ -34600,7 +34557,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0602_errores-el_pan_diario_del_programador.html</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E372" s="16"/>
     </row>
@@ -34622,7 +34579,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C374" s="17"/>
       <c r="E374" s="16"/>
@@ -34637,19 +34594,19 @@
         <v>0.6</v>
       </c>
       <c r="C375" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="376" ht="15.75" spans="1:3">
       <c r="A376" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B376" s="19"/>
       <c r="C376" s="20"/>
     </row>
     <row r="377" ht="16.5" spans="1:3">
       <c r="A377" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B377" s="11"/>
       <c r="C377" s="12"/>
@@ -34664,7 +34621,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0701_los_fundamentos_de_la_poo.html</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E378" s="16"/>
     </row>
@@ -34686,7 +34643,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C380" s="17"/>
       <c r="E380" s="16"/>
@@ -34701,19 +34658,19 @@
         <v>0.6</v>
       </c>
       <c r="C381" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="382" ht="15.75" spans="1:3">
       <c r="A382" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B382" s="19"/>
       <c r="C382" s="20"/>
     </row>
     <row r="383" ht="16.5" spans="1:3">
       <c r="A383" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B383" s="11"/>
       <c r="C383" s="12"/>
@@ -34728,7 +34685,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0702_comparando_paradigmas_programacion_procedimental_y_orientada_a_objetos.html</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E384" s="16"/>
     </row>
@@ -34750,7 +34707,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C386" s="17"/>
       <c r="E386" s="16"/>
@@ -34765,19 +34722,19 @@
         <v>0.6</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="388" ht="15.75" spans="1:3">
       <c r="A388" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B388" s="19"/>
       <c r="C388" s="20"/>
     </row>
     <row r="389" ht="16.5" spans="1:3">
       <c r="A389" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B389" s="11"/>
       <c r="C389" s="12"/>
@@ -34792,7 +34749,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0703_poo_propiedades.html</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E390" s="16"/>
     </row>
@@ -34814,7 +34771,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C392" s="17"/>
       <c r="E392" s="16"/>
@@ -34829,19 +34786,19 @@
         <v>0.6</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="394" ht="15.75" spans="1:3">
       <c r="A394" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="20"/>
     </row>
     <row r="395" ht="16.5" spans="1:3">
       <c r="A395" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="12"/>
@@ -34856,7 +34813,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0704_poo_metodos.html</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E396" s="16"/>
     </row>
@@ -34878,7 +34835,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C398" s="17"/>
       <c r="E398" s="16"/>
@@ -34893,19 +34850,19 @@
         <v>0.6</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="400" ht="15.75" spans="1:3">
       <c r="A400" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B400" s="19"/>
       <c r="C400" s="20"/>
     </row>
     <row r="401" ht="16.5" spans="1:3">
       <c r="A401" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B401" s="11"/>
       <c r="C401" s="12"/>
@@ -34920,7 +34877,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0705_poo_herencia.html</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E402" s="16"/>
     </row>
@@ -34942,7 +34899,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C404" s="17"/>
       <c r="E404" s="16"/>
@@ -34957,19 +34914,19 @@
         <v>0.6</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="406" ht="15.75" spans="1:3">
       <c r="A406" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B406" s="19"/>
       <c r="C406" s="20"/>
     </row>
     <row r="407" ht="16.5" spans="1:3">
       <c r="A407" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B407" s="11"/>
       <c r="C407" s="12"/>
@@ -34984,7 +34941,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0706_poo_excepciones.html</v>
       </c>
       <c r="C408" s="15" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E408" s="16"/>
     </row>
@@ -35006,7 +34963,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C410" s="17"/>
       <c r="E410" s="16"/>
@@ -35021,19 +34978,19 @@
         <v>0.6</v>
       </c>
       <c r="C411" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="412" ht="15.75" spans="1:3">
       <c r="A412" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B412" s="19"/>
       <c r="C412" s="20"/>
     </row>
     <row r="413" ht="16.5" spans="1:3">
       <c r="A413" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="12"/>
@@ -35048,7 +35005,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0801_iteradores,_generadores_y_cierres.html</v>
       </c>
       <c r="C414" s="15" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E414" s="16"/>
     </row>
@@ -35070,7 +35027,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C416" s="17"/>
       <c r="E416" s="16"/>
@@ -35085,19 +35042,19 @@
         <v>0.6</v>
       </c>
       <c r="C417" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="418" ht="15.75" spans="1:3">
       <c r="A418" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B418" s="19"/>
       <c r="C418" s="20"/>
     </row>
     <row r="419" ht="16.5" spans="1:3">
       <c r="A419" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="12"/>
@@ -35112,7 +35069,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0802_manejo_de_archivos.html</v>
       </c>
       <c r="C420" s="15" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E420" s="16"/>
     </row>
@@ -35134,7 +35091,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C422" s="17"/>
       <c r="E422" s="16"/>
@@ -35149,19 +35106,19 @@
         <v>0.6</v>
       </c>
       <c r="C423" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="424" ht="15.75" spans="1:3">
       <c r="A424" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B424" s="19"/>
       <c r="C424" s="20"/>
     </row>
     <row r="425" ht="16.5" spans="1:3">
       <c r="A425" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="12"/>
@@ -35176,7 +35133,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0803_el_modulo_os_interactuando_con_el_sistema_operativo.html</v>
       </c>
       <c r="C426" s="15" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E426" s="16"/>
     </row>
@@ -35198,7 +35155,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C428" s="17"/>
       <c r="E428" s="16"/>
@@ -35213,19 +35170,19 @@
         <v>0.6</v>
       </c>
       <c r="C429" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="430" ht="15.75" spans="1:3">
       <c r="A430" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B430" s="19"/>
       <c r="C430" s="20"/>
     </row>
     <row r="431" ht="16.5" spans="1:3">
       <c r="A431" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="12"/>
@@ -35240,7 +35197,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0804_modulo_datetime_funciones_para_manejo_de_la_hora_y_la_fecha.html</v>
       </c>
       <c r="C432" s="15" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E432" s="16"/>
     </row>
@@ -35262,7 +35219,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C434" s="17"/>
       <c r="E434" s="16"/>
@@ -35277,19 +35234,19 @@
         <v>0.6</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="436" ht="15.75" spans="1:3">
       <c r="A436" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B436" s="19"/>
       <c r="C436" s="20"/>
     </row>
     <row r="437" ht="16.5" spans="1:3">
       <c r="A437" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="12"/>
@@ -35304,7 +35261,7 @@
         <v>https://eduardoherreraf.github.io/cursoPython3-0805_modulo_calendar_trabajando_con_funciones_relacionadas_con_el_calendario.html</v>
       </c>
       <c r="C438" s="15" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -35324,7 +35281,7 @@
         <v>&lt;changefreq&gt;yearly&lt;/changefreq&gt;</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C440" s="17"/>
     </row>
@@ -35338,19 +35295,19 @@
         <v>0.6</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="442" ht="15.75" spans="1:3">
       <c r="A442" s="18" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B442" s="19"/>
       <c r="C442" s="20"/>
     </row>
     <row r="443" ht="15.75" spans="1:3">
       <c r="A443" s="5" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C443" s="22"/>
     </row>
@@ -35640,13 +35597,13 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -35655,78 +35612,78 @@
         <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -35735,16 +35692,16 @@
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -35753,7 +35710,7 @@
         <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -35762,51 +35719,51 @@
         <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4"/>
       <c r="D20" s="1" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
